--- a/sql_admin/field_name_value_list_generator.xlsx
+++ b/sql_admin/field_name_value_list_generator.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Projects\SPSCC\2026.sp.capstone\SPSCC_CS490_SeniorProject_HealthAssessment\sql_admin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{099357B4-8138-4725-9450-AC87625E280F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{884E8836-6DE8-409D-8920-1ED9347A90DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-240" windowWidth="29040" windowHeight="15720" xr2:uid="{352D3FB6-20F0-4929-9B6B-26A204E9AE94}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{352D3FB6-20F0-4929-9B6B-26A204E9AE94}"/>
   </bookViews>
   <sheets>
     <sheet name="SQL Generator" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="583">
   <si>
     <t>Overall, how would you rate your health during the PAST MONTH?</t>
   </si>
@@ -1779,6 +1779,16 @@
   </si>
   <si>
     <t>'</t>
+  </si>
+  <si>
+    <t>LENGTH</t>
+  </si>
+  <si>
+    <t>START POS</t>
+  </si>
+  <si>
+    <t>END
+POS</t>
   </si>
 </sst>
 </file>
@@ -1871,7 +1881,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1888,8 +1898,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2225,16 +2241,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4521CCFA-4BCC-4776-8421-B651A3CCC5D0}">
-  <dimension ref="A1:H238"/>
+  <dimension ref="A1:K239"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="55.140625" customWidth="1"/>
     <col min="4" max="4" width="75.28515625" customWidth="1"/>
+    <col min="5" max="5" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>576</v>
       </c>
@@ -2247,11 +2266,20 @@
       <c r="D1" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="H1" s="6" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>534</v>
       </c>
@@ -2264,24 +2292,33 @@
       <c r="D2" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="E2" t="str">
-        <f>$E$1&amp;A2&amp;$E$1</f>
+      <c r="E2" s="7">
+        <v>5</v>
+      </c>
+      <c r="F2" s="7">
+        <v>1</v>
+      </c>
+      <c r="G2" s="7">
+        <v>5</v>
+      </c>
+      <c r="H2" t="str">
+        <f>$H$1&amp;A2&amp;$H$1</f>
         <v>'FORM'</v>
       </c>
-      <c r="F2" t="str">
-        <f>$E$1&amp;B2&amp;$E$1</f>
+      <c r="I2" t="str">
+        <f>$H$1&amp;B2&amp;$H$1</f>
         <v>'FORM_TYPE'</v>
       </c>
-      <c r="G2" t="str">
-        <f>$E$1&amp;SUBSTITUTE(C2, "'", "''")&amp;$E$1</f>
+      <c r="J2" t="str">
+        <f>$H$1&amp;SUBSTITUTE(C2, "'", "''")&amp;$H$1</f>
         <v>'Type of Form'</v>
       </c>
-      <c r="H2" t="str">
-        <f>"("&amp;E2&amp;","&amp;F2&amp;","&amp;G2&amp;"),"</f>
+      <c r="K2" t="str">
+        <f>"("&amp;H2&amp;","&amp;I2&amp;","&amp;J2&amp;"),"</f>
         <v>('FORM','FORM_TYPE','Type of Form'),</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>534</v>
       </c>
@@ -2294,24 +2331,33 @@
       <c r="D3" s="3" t="s">
         <v>537</v>
       </c>
-      <c r="E3" t="str">
-        <f t="shared" ref="E3:E66" si="0">$E$1&amp;A3&amp;$E$1</f>
+      <c r="E3" s="7">
+        <v>15</v>
+      </c>
+      <c r="F3" s="7">
+        <v>6</v>
+      </c>
+      <c r="G3" s="7">
+        <v>20</v>
+      </c>
+      <c r="H3" t="str">
+        <f t="shared" ref="H3:H66" si="0">$H$1&amp;A3&amp;$H$1</f>
         <v>'FORM'</v>
       </c>
-      <c r="F3" t="str">
-        <f t="shared" ref="F3:F66" si="1">$E$1&amp;B3&amp;$E$1</f>
+      <c r="I3" t="str">
+        <f t="shared" ref="I3:I66" si="1">$H$1&amp;B3&amp;$H$1</f>
         <v>'FORM_VERSION'</v>
       </c>
-      <c r="G3" t="str">
-        <f t="shared" ref="G3:G66" si="2">$E$1&amp;SUBSTITUTE(C3, "'", "''")&amp;$E$1</f>
+      <c r="J3" t="str">
+        <f t="shared" ref="J3:J66" si="2">$H$1&amp;SUBSTITUTE(C3, "'", "''")&amp;$H$1</f>
         <v>'DoD Form Version'</v>
       </c>
-      <c r="H3" t="str">
-        <f t="shared" ref="H3:H66" si="3">"("&amp;E3&amp;","&amp;F3&amp;","&amp;G3&amp;"),"</f>
+      <c r="K3" t="str">
+        <f t="shared" ref="K3:K66" si="3">"("&amp;H3&amp;","&amp;I3&amp;","&amp;J3&amp;"),"</f>
         <v>('FORM','FORM_VERSION','DoD Form Version'),</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>48</v>
       </c>
@@ -2324,24 +2370,33 @@
       <c r="D4" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E4" t="str">
+      <c r="E4" s="7">
+        <v>25</v>
+      </c>
+      <c r="F4" s="7">
+        <v>21</v>
+      </c>
+      <c r="G4" s="7">
+        <v>45</v>
+      </c>
+      <c r="H4" t="str">
         <f t="shared" si="0"/>
         <v>'DEM'</v>
       </c>
-      <c r="F4" t="str">
+      <c r="I4" t="str">
         <f t="shared" si="1"/>
         <v>'LNAME'</v>
       </c>
-      <c r="G4" t="str">
+      <c r="J4" t="str">
         <f t="shared" si="2"/>
         <v>'Last Name'</v>
       </c>
-      <c r="H4" t="str">
+      <c r="K4" t="str">
         <f t="shared" si="3"/>
         <v>('DEM','LNAME','Last Name'),</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>48</v>
       </c>
@@ -2354,24 +2409,33 @@
       <c r="D5" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E5" t="str">
+      <c r="E5" s="7">
+        <v>25</v>
+      </c>
+      <c r="F5" s="7">
+        <v>46</v>
+      </c>
+      <c r="G5" s="7">
+        <v>70</v>
+      </c>
+      <c r="H5" t="str">
         <f t="shared" si="0"/>
         <v>'DEM'</v>
       </c>
-      <c r="F5" t="str">
+      <c r="I5" t="str">
         <f t="shared" si="1"/>
         <v>'FNAME'</v>
       </c>
-      <c r="G5" t="str">
+      <c r="J5" t="str">
         <f t="shared" si="2"/>
         <v>'First Name'</v>
       </c>
-      <c r="H5" t="str">
+      <c r="K5" t="str">
         <f t="shared" si="3"/>
         <v>('DEM','FNAME','First Name'),</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>48</v>
       </c>
@@ -2384,24 +2448,33 @@
       <c r="D6" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E6" t="str">
+      <c r="E6" s="7">
+        <v>1</v>
+      </c>
+      <c r="F6" s="7">
+        <v>71</v>
+      </c>
+      <c r="G6" s="7">
+        <v>71</v>
+      </c>
+      <c r="H6" t="str">
         <f t="shared" si="0"/>
         <v>'DEM'</v>
       </c>
-      <c r="F6" t="str">
+      <c r="I6" t="str">
         <f t="shared" si="1"/>
         <v>'MI'</v>
       </c>
-      <c r="G6" t="str">
+      <c r="J6" t="str">
         <f t="shared" si="2"/>
         <v>'Middle Initial'</v>
       </c>
-      <c r="H6" t="str">
+      <c r="K6" t="str">
         <f t="shared" si="3"/>
         <v>('DEM','MI','Middle Initial'),</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>48</v>
       </c>
@@ -2414,24 +2487,33 @@
       <c r="D7" s="3">
         <v>9999999999</v>
       </c>
-      <c r="E7" t="str">
+      <c r="E7" s="7">
+        <v>10</v>
+      </c>
+      <c r="F7" s="7">
+        <v>72</v>
+      </c>
+      <c r="G7" s="7">
+        <v>81</v>
+      </c>
+      <c r="H7" t="str">
         <f t="shared" si="0"/>
         <v>'DEM'</v>
       </c>
-      <c r="F7" t="str">
+      <c r="I7" t="str">
         <f t="shared" si="1"/>
         <v>'DODID'</v>
       </c>
-      <c r="G7" t="str">
+      <c r="J7" t="str">
         <f t="shared" si="2"/>
         <v>'DoD ID number (formerly EDIPI)'</v>
       </c>
-      <c r="H7" t="str">
+      <c r="K7" t="str">
         <f t="shared" si="3"/>
         <v>('DEM','DODID','DoD ID number (formerly EDIPI)'),</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>48</v>
       </c>
@@ -2444,24 +2526,33 @@
       <c r="D8" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="E8" t="str">
+      <c r="E8" s="7">
+        <v>8</v>
+      </c>
+      <c r="F8" s="7">
+        <v>82</v>
+      </c>
+      <c r="G8" s="7">
+        <v>89</v>
+      </c>
+      <c r="H8" t="str">
         <f t="shared" si="0"/>
         <v>'DEM'</v>
       </c>
-      <c r="F8" t="str">
+      <c r="I8" t="str">
         <f t="shared" si="1"/>
         <v>'D_EVENT'</v>
       </c>
-      <c r="G8" t="str">
+      <c r="J8" t="str">
         <f t="shared" si="2"/>
         <v>'Today''s Date (date on form)'</v>
       </c>
-      <c r="H8" t="str">
+      <c r="K8" t="str">
         <f t="shared" si="3"/>
         <v>('DEM','D_EVENT','Today''s Date (date on form)'),</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>48</v>
       </c>
@@ -2474,24 +2565,33 @@
       <c r="D9" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="E9" t="str">
+      <c r="E9" s="7">
+        <v>8</v>
+      </c>
+      <c r="F9" s="7">
+        <v>90</v>
+      </c>
+      <c r="G9" s="7">
+        <v>97</v>
+      </c>
+      <c r="H9" t="str">
         <f t="shared" si="0"/>
         <v>'DEM'</v>
       </c>
-      <c r="F9" t="str">
+      <c r="I9" t="str">
         <f t="shared" si="1"/>
         <v>'DOB'</v>
       </c>
-      <c r="G9" t="str">
+      <c r="J9" t="str">
         <f t="shared" si="2"/>
         <v>'Date of Birth'</v>
       </c>
-      <c r="H9" t="str">
+      <c r="K9" t="str">
         <f t="shared" si="3"/>
         <v>('DEM','DOB','Date of Birth'),</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>48</v>
       </c>
@@ -2504,24 +2604,33 @@
       <c r="D10" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="E10" t="str">
+      <c r="E10" s="7">
+        <v>1</v>
+      </c>
+      <c r="F10" s="7">
+        <v>98</v>
+      </c>
+      <c r="G10" s="7">
+        <v>98</v>
+      </c>
+      <c r="H10" t="str">
         <f t="shared" si="0"/>
         <v>'DEM'</v>
       </c>
-      <c r="F10" t="str">
+      <c r="I10" t="str">
         <f t="shared" si="1"/>
         <v>'SEX'</v>
       </c>
-      <c r="G10" t="str">
+      <c r="J10" t="str">
         <f t="shared" si="2"/>
         <v>'Sex'</v>
       </c>
-      <c r="H10" t="str">
+      <c r="K10" t="str">
         <f t="shared" si="3"/>
         <v>('DEM','SEX','Sex'),</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>48</v>
       </c>
@@ -2534,24 +2643,33 @@
       <c r="D11" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="E11" t="str">
+      <c r="E11" s="7">
+        <v>1</v>
+      </c>
+      <c r="F11" s="7">
+        <v>99</v>
+      </c>
+      <c r="G11" s="7">
+        <v>99</v>
+      </c>
+      <c r="H11" t="str">
         <f t="shared" si="0"/>
         <v>'DEM'</v>
       </c>
-      <c r="F11" t="str">
+      <c r="I11" t="str">
         <f t="shared" si="1"/>
         <v>'FORM_SERVICE'</v>
       </c>
-      <c r="G11" t="str">
+      <c r="J11" t="str">
         <f t="shared" si="2"/>
         <v>'Service Branch'</v>
       </c>
-      <c r="H11" t="str">
+      <c r="K11" t="str">
         <f t="shared" si="3"/>
         <v>('DEM','FORM_SERVICE','Service Branch'),</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>48</v>
       </c>
@@ -2564,24 +2682,33 @@
       <c r="D12" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E12" t="str">
+      <c r="E12" s="7">
+        <v>25</v>
+      </c>
+      <c r="F12" s="7">
+        <v>100</v>
+      </c>
+      <c r="G12" s="7">
+        <v>124</v>
+      </c>
+      <c r="H12" t="str">
         <f t="shared" si="0"/>
         <v>'DEM'</v>
       </c>
-      <c r="F12" t="str">
+      <c r="I12" t="str">
         <f t="shared" si="1"/>
         <v>'SERVICE_OTHER'</v>
       </c>
-      <c r="G12" t="str">
+      <c r="J12" t="str">
         <f t="shared" si="2"/>
         <v>'Other Defense Agency'</v>
       </c>
-      <c r="H12" t="str">
+      <c r="K12" t="str">
         <f t="shared" si="3"/>
         <v>('DEM','SERVICE_OTHER','Other Defense Agency'),</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>48</v>
       </c>
@@ -2594,24 +2721,33 @@
       <c r="D13" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="E13" t="str">
+      <c r="E13" s="7">
+        <v>3</v>
+      </c>
+      <c r="F13" s="7">
+        <v>125</v>
+      </c>
+      <c r="G13" s="7">
+        <v>127</v>
+      </c>
+      <c r="H13" t="str">
         <f t="shared" si="0"/>
         <v>'DEM'</v>
       </c>
-      <c r="F13" t="str">
+      <c r="I13" t="str">
         <f t="shared" si="1"/>
         <v>'FORM_COMPONENT'</v>
       </c>
-      <c r="G13" t="str">
+      <c r="J13" t="str">
         <f t="shared" si="2"/>
         <v>'Component'</v>
       </c>
-      <c r="H13" t="str">
+      <c r="K13" t="str">
         <f t="shared" si="3"/>
         <v>('DEM','FORM_COMPONENT','Component'),</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>48</v>
       </c>
@@ -2624,24 +2760,33 @@
       <c r="D14" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="E14" t="str">
+      <c r="E14" s="7">
+        <v>3</v>
+      </c>
+      <c r="F14" s="7">
+        <v>128</v>
+      </c>
+      <c r="G14" s="7">
+        <v>130</v>
+      </c>
+      <c r="H14" t="str">
         <f t="shared" si="0"/>
         <v>'DEM'</v>
       </c>
-      <c r="F14" t="str">
+      <c r="I14" t="str">
         <f t="shared" si="1"/>
         <v>'GRADE'</v>
       </c>
-      <c r="G14" t="str">
+      <c r="J14" t="str">
         <f t="shared" si="2"/>
         <v>'Pay Grade'</v>
       </c>
-      <c r="H14" t="str">
+      <c r="K14" t="str">
         <f t="shared" si="3"/>
         <v>('DEM','GRADE','Pay Grade'),</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>48</v>
       </c>
@@ -2654,24 +2799,33 @@
       <c r="D15" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E15" t="str">
+      <c r="E15" s="7">
+        <v>25</v>
+      </c>
+      <c r="F15" s="7">
+        <v>131</v>
+      </c>
+      <c r="G15" s="7">
+        <v>155</v>
+      </c>
+      <c r="H15" t="str">
         <f t="shared" si="0"/>
         <v>'DEM'</v>
       </c>
-      <c r="F15" t="str">
+      <c r="I15" t="str">
         <f t="shared" si="1"/>
         <v>'GRADE_OTHER'</v>
       </c>
-      <c r="G15" t="str">
+      <c r="J15" t="str">
         <f t="shared" si="2"/>
         <v>'Other Grade'</v>
       </c>
-      <c r="H15" t="str">
+      <c r="K15" t="str">
         <f t="shared" si="3"/>
         <v>('DEM','GRADE_OTHER','Other Grade'),</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>48</v>
       </c>
@@ -2684,24 +2838,33 @@
       <c r="D16" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E16" t="str">
+      <c r="E16" s="7">
+        <v>75</v>
+      </c>
+      <c r="F16" s="7">
+        <v>156</v>
+      </c>
+      <c r="G16" s="7">
+        <v>230</v>
+      </c>
+      <c r="H16" t="str">
         <f t="shared" si="0"/>
         <v>'DEM'</v>
       </c>
-      <c r="F16" t="str">
+      <c r="I16" t="str">
         <f t="shared" si="1"/>
         <v>'UNIT_NAME'</v>
       </c>
-      <c r="G16" t="str">
+      <c r="J16" t="str">
         <f t="shared" si="2"/>
         <v>'Unit Name'</v>
       </c>
-      <c r="H16" t="str">
+      <c r="K16" t="str">
         <f t="shared" si="3"/>
         <v>('DEM','UNIT_NAME','Unit Name'),</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>48</v>
       </c>
@@ -2714,24 +2877,33 @@
       <c r="D17" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E17" t="str">
+      <c r="E17" s="7">
+        <v>75</v>
+      </c>
+      <c r="F17" s="7">
+        <v>231</v>
+      </c>
+      <c r="G17" s="7">
+        <v>305</v>
+      </c>
+      <c r="H17" t="str">
         <f t="shared" si="0"/>
         <v>'DEM'</v>
       </c>
-      <c r="F17" t="str">
+      <c r="I17" t="str">
         <f t="shared" si="1"/>
         <v>'UNIT_LOC'</v>
       </c>
-      <c r="G17" t="str">
+      <c r="J17" t="str">
         <f t="shared" si="2"/>
         <v>'Duty Station/Location'</v>
       </c>
-      <c r="H17" t="str">
+      <c r="K17" t="str">
         <f t="shared" si="3"/>
         <v>('DEM','UNIT_LOC','Duty Station/Location'),</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>48</v>
       </c>
@@ -2744,24 +2916,33 @@
       <c r="D18" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E18" t="str">
+      <c r="E18" s="7">
+        <v>20</v>
+      </c>
+      <c r="F18" s="7">
+        <v>306</v>
+      </c>
+      <c r="G18" s="7">
+        <v>325</v>
+      </c>
+      <c r="H18" t="str">
         <f t="shared" si="0"/>
         <v>'DEM'</v>
       </c>
-      <c r="F18" t="str">
+      <c r="I18" t="str">
         <f t="shared" si="1"/>
         <v>'PHONE'</v>
       </c>
-      <c r="G18" t="str">
+      <c r="J18" t="str">
         <f t="shared" si="2"/>
         <v>'Current Phone'</v>
       </c>
-      <c r="H18" t="str">
+      <c r="K18" t="str">
         <f t="shared" si="3"/>
         <v>('DEM','PHONE','Current Phone'),</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>48</v>
       </c>
@@ -2774,24 +2955,33 @@
       <c r="D19" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E19" t="str">
+      <c r="E19" s="7">
+        <v>20</v>
+      </c>
+      <c r="F19" s="7">
+        <v>326</v>
+      </c>
+      <c r="G19" s="7">
+        <v>345</v>
+      </c>
+      <c r="H19" t="str">
         <f t="shared" si="0"/>
         <v>'DEM'</v>
       </c>
-      <c r="F19" t="str">
+      <c r="I19" t="str">
         <f t="shared" si="1"/>
         <v>'CELL'</v>
       </c>
-      <c r="G19" t="str">
+      <c r="J19" t="str">
         <f t="shared" si="2"/>
         <v>'Current Cell Phone'</v>
       </c>
-      <c r="H19" t="str">
+      <c r="K19" t="str">
         <f t="shared" si="3"/>
         <v>('DEM','CELL','Current Cell Phone'),</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>48</v>
       </c>
@@ -2804,24 +2994,33 @@
       <c r="D20" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E20" t="str">
+      <c r="E20" s="7">
+        <v>20</v>
+      </c>
+      <c r="F20" s="7">
+        <v>346</v>
+      </c>
+      <c r="G20" s="7">
+        <v>365</v>
+      </c>
+      <c r="H20" t="str">
         <f t="shared" si="0"/>
         <v>'DEM'</v>
       </c>
-      <c r="F20" t="str">
+      <c r="I20" t="str">
         <f t="shared" si="1"/>
         <v>'DSN'</v>
       </c>
-      <c r="G20" t="str">
+      <c r="J20" t="str">
         <f t="shared" si="2"/>
         <v>'Current DSN'</v>
       </c>
-      <c r="H20" t="str">
+      <c r="K20" t="str">
         <f t="shared" si="3"/>
         <v>('DEM','DSN','Current DSN'),</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>48</v>
       </c>
@@ -2834,24 +3033,33 @@
       <c r="D21" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E21" t="str">
+      <c r="E21" s="7">
+        <v>75</v>
+      </c>
+      <c r="F21" s="7">
+        <v>366</v>
+      </c>
+      <c r="G21" s="7">
+        <v>440</v>
+      </c>
+      <c r="H21" t="str">
         <f t="shared" si="0"/>
         <v>'DEM'</v>
       </c>
-      <c r="F21" t="str">
+      <c r="I21" t="str">
         <f t="shared" si="1"/>
         <v>'EMAIL'</v>
       </c>
-      <c r="G21" t="str">
+      <c r="J21" t="str">
         <f t="shared" si="2"/>
         <v>'Current Email'</v>
       </c>
-      <c r="H21" t="str">
+      <c r="K21" t="str">
         <f t="shared" si="3"/>
         <v>('DEM','EMAIL','Current Email'),</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>48</v>
       </c>
@@ -2864,24 +3072,33 @@
       <c r="D22" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E22" t="str">
+      <c r="E22" s="7">
+        <v>60</v>
+      </c>
+      <c r="F22" s="7">
+        <v>441</v>
+      </c>
+      <c r="G22" s="7">
+        <v>500</v>
+      </c>
+      <c r="H22" t="str">
         <f t="shared" si="0"/>
         <v>'DEM'</v>
       </c>
-      <c r="F22" t="str">
+      <c r="I22" t="str">
         <f t="shared" si="1"/>
         <v>'ADDR'</v>
       </c>
-      <c r="G22" t="str">
+      <c r="J22" t="str">
         <f t="shared" si="2"/>
         <v>'Current Address'</v>
       </c>
-      <c r="H22" t="str">
+      <c r="K22" t="str">
         <f t="shared" si="3"/>
         <v>('DEM','ADDR','Current Address'),</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>48</v>
       </c>
@@ -2894,24 +3111,33 @@
       <c r="D23" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E23" t="str">
+      <c r="E23" s="7">
+        <v>25</v>
+      </c>
+      <c r="F23" s="7">
+        <v>501</v>
+      </c>
+      <c r="G23" s="7">
+        <v>525</v>
+      </c>
+      <c r="H23" t="str">
         <f t="shared" si="0"/>
         <v>'DEM'</v>
       </c>
-      <c r="F23" t="str">
+      <c r="I23" t="str">
         <f t="shared" si="1"/>
         <v>'CITY'</v>
       </c>
-      <c r="G23" t="str">
+      <c r="J23" t="str">
         <f t="shared" si="2"/>
         <v>'Current CITY'</v>
       </c>
-      <c r="H23" t="str">
+      <c r="K23" t="str">
         <f t="shared" si="3"/>
         <v>('DEM','CITY','Current CITY'),</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>48</v>
       </c>
@@ -2924,24 +3150,33 @@
       <c r="D24" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E24" t="str">
+      <c r="E24" s="7">
+        <v>2</v>
+      </c>
+      <c r="F24" s="7">
+        <v>526</v>
+      </c>
+      <c r="G24" s="7">
+        <v>527</v>
+      </c>
+      <c r="H24" t="str">
         <f t="shared" si="0"/>
         <v>'DEM'</v>
       </c>
-      <c r="F24" t="str">
+      <c r="I24" t="str">
         <f t="shared" si="1"/>
         <v>'STATE'</v>
       </c>
-      <c r="G24" t="str">
+      <c r="J24" t="str">
         <f t="shared" si="2"/>
         <v>'Current STATE'</v>
       </c>
-      <c r="H24" t="str">
+      <c r="K24" t="str">
         <f t="shared" si="3"/>
         <v>('DEM','STATE','Current STATE'),</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>48</v>
       </c>
@@ -2954,24 +3189,33 @@
       <c r="D25" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E25" t="str">
+      <c r="E25" s="7">
+        <v>10</v>
+      </c>
+      <c r="F25" s="7">
+        <v>528</v>
+      </c>
+      <c r="G25" s="7">
+        <v>537</v>
+      </c>
+      <c r="H25" t="str">
         <f t="shared" si="0"/>
         <v>'DEM'</v>
       </c>
-      <c r="F25" t="str">
+      <c r="I25" t="str">
         <f t="shared" si="1"/>
         <v>'ZIP'</v>
       </c>
-      <c r="G25" t="str">
+      <c r="J25" t="str">
         <f t="shared" si="2"/>
         <v>'Current ZIP Code'</v>
       </c>
-      <c r="H25" t="str">
+      <c r="K25" t="str">
         <f t="shared" si="3"/>
         <v>('DEM','ZIP','Current ZIP Code'),</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>48</v>
       </c>
@@ -2984,24 +3228,33 @@
       <c r="D26" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E26" t="str">
+      <c r="E26" s="7">
+        <v>50</v>
+      </c>
+      <c r="F26" s="7">
+        <v>538</v>
+      </c>
+      <c r="G26" s="7">
+        <v>587</v>
+      </c>
+      <c r="H26" t="str">
         <f t="shared" si="0"/>
         <v>'DEM'</v>
       </c>
-      <c r="F26" t="str">
+      <c r="I26" t="str">
         <f t="shared" si="1"/>
         <v>'POC_NAME'</v>
       </c>
-      <c r="G26" t="str">
+      <c r="J26" t="str">
         <f t="shared" si="2"/>
         <v>'POC Name'</v>
       </c>
-      <c r="H26" t="str">
+      <c r="K26" t="str">
         <f t="shared" si="3"/>
         <v>('DEM','POC_NAME','POC Name'),</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>48</v>
       </c>
@@ -3014,24 +3267,33 @@
       <c r="D27" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E27" t="str">
+      <c r="E27" s="7">
+        <v>20</v>
+      </c>
+      <c r="F27" s="7">
+        <v>588</v>
+      </c>
+      <c r="G27" s="7">
+        <v>607</v>
+      </c>
+      <c r="H27" t="str">
         <f t="shared" si="0"/>
         <v>'DEM'</v>
       </c>
-      <c r="F27" t="str">
+      <c r="I27" t="str">
         <f t="shared" si="1"/>
         <v>'POC_PHONE'</v>
       </c>
-      <c r="G27" t="str">
+      <c r="J27" t="str">
         <f t="shared" si="2"/>
         <v>'POC Phone'</v>
       </c>
-      <c r="H27" t="str">
+      <c r="K27" t="str">
         <f t="shared" si="3"/>
         <v>('DEM','POC_PHONE','POC Phone'),</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>48</v>
       </c>
@@ -3044,24 +3306,33 @@
       <c r="D28" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E28" t="str">
+      <c r="E28" s="7">
+        <v>75</v>
+      </c>
+      <c r="F28" s="7">
+        <v>608</v>
+      </c>
+      <c r="G28" s="7">
+        <v>682</v>
+      </c>
+      <c r="H28" t="str">
         <f t="shared" si="0"/>
         <v>'DEM'</v>
       </c>
-      <c r="F28" t="str">
+      <c r="I28" t="str">
         <f t="shared" si="1"/>
         <v>'POC_EMAIL'</v>
       </c>
-      <c r="G28" t="str">
+      <c r="J28" t="str">
         <f t="shared" si="2"/>
         <v>'POC Email'</v>
       </c>
-      <c r="H28" t="str">
+      <c r="K28" t="str">
         <f t="shared" si="3"/>
         <v>('DEM','POC_EMAIL','POC Email'),</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>48</v>
       </c>
@@ -3074,24 +3345,33 @@
       <c r="D29" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E29" t="str">
+      <c r="E29" s="7">
+        <v>60</v>
+      </c>
+      <c r="F29" s="7">
+        <v>683</v>
+      </c>
+      <c r="G29" s="7">
+        <v>742</v>
+      </c>
+      <c r="H29" t="str">
         <f t="shared" si="0"/>
         <v>'DEM'</v>
       </c>
-      <c r="F29" t="str">
+      <c r="I29" t="str">
         <f t="shared" si="1"/>
         <v>'POC_ADDR'</v>
       </c>
-      <c r="G29" t="str">
+      <c r="J29" t="str">
         <f t="shared" si="2"/>
         <v>'POC Address'</v>
       </c>
-      <c r="H29" t="str">
+      <c r="K29" t="str">
         <f t="shared" si="3"/>
         <v>('DEM','POC_ADDR','POC Address'),</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>48</v>
       </c>
@@ -3104,24 +3384,33 @@
       <c r="D30" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E30" t="str">
+      <c r="E30" s="7">
+        <v>25</v>
+      </c>
+      <c r="F30" s="7">
+        <v>743</v>
+      </c>
+      <c r="G30" s="7">
+        <v>767</v>
+      </c>
+      <c r="H30" t="str">
         <f t="shared" si="0"/>
         <v>'DEM'</v>
       </c>
-      <c r="F30" t="str">
+      <c r="I30" t="str">
         <f t="shared" si="1"/>
         <v>'POC_CITY'</v>
       </c>
-      <c r="G30" t="str">
+      <c r="J30" t="str">
         <f t="shared" si="2"/>
         <v>'POC CITY'</v>
       </c>
-      <c r="H30" t="str">
+      <c r="K30" t="str">
         <f t="shared" si="3"/>
         <v>('DEM','POC_CITY','POC CITY'),</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>48</v>
       </c>
@@ -3134,24 +3423,33 @@
       <c r="D31" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E31" t="str">
+      <c r="E31" s="7">
+        <v>2</v>
+      </c>
+      <c r="F31" s="7">
+        <v>768</v>
+      </c>
+      <c r="G31" s="7">
+        <v>769</v>
+      </c>
+      <c r="H31" t="str">
         <f t="shared" si="0"/>
         <v>'DEM'</v>
       </c>
-      <c r="F31" t="str">
+      <c r="I31" t="str">
         <f t="shared" si="1"/>
         <v>'POC_STATE'</v>
       </c>
-      <c r="G31" t="str">
+      <c r="J31" t="str">
         <f t="shared" si="2"/>
         <v>'POC STATE'</v>
       </c>
-      <c r="H31" t="str">
+      <c r="K31" t="str">
         <f t="shared" si="3"/>
         <v>('DEM','POC_STATE','POC STATE'),</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>48</v>
       </c>
@@ -3164,24 +3462,33 @@
       <c r="D32" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E32" t="str">
+      <c r="E32" s="7">
+        <v>10</v>
+      </c>
+      <c r="F32" s="7">
+        <v>770</v>
+      </c>
+      <c r="G32" s="7">
+        <v>779</v>
+      </c>
+      <c r="H32" t="str">
         <f t="shared" si="0"/>
         <v>'DEM'</v>
       </c>
-      <c r="F32" t="str">
+      <c r="I32" t="str">
         <f t="shared" si="1"/>
         <v>'POC_ZIP'</v>
       </c>
-      <c r="G32" t="str">
+      <c r="J32" t="str">
         <f t="shared" si="2"/>
         <v>'POC ZIP Code'</v>
       </c>
-      <c r="H32" t="str">
+      <c r="K32" t="str">
         <f t="shared" si="3"/>
         <v>('DEM','POC_ZIP','POC ZIP Code'),</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>48</v>
       </c>
@@ -3194,24 +3501,33 @@
       <c r="D33" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="E33" t="str">
+      <c r="E33" s="7">
+        <v>8</v>
+      </c>
+      <c r="F33" s="7">
+        <v>780</v>
+      </c>
+      <c r="G33" s="7">
+        <v>787</v>
+      </c>
+      <c r="H33" t="str">
         <f t="shared" si="0"/>
         <v>'DEM'</v>
       </c>
-      <c r="F33" t="str">
+      <c r="I33" t="str">
         <f t="shared" si="1"/>
         <v>'D_DEPLOY'</v>
       </c>
-      <c r="G33" t="str">
+      <c r="J33" t="str">
         <f t="shared" si="2"/>
         <v>'Estimated Date of deployment'</v>
       </c>
-      <c r="H33" t="str">
+      <c r="K33" t="str">
         <f t="shared" si="3"/>
         <v>('DEM','D_DEPLOY','Estimated Date of deployment'),</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>48</v>
       </c>
@@ -3224,24 +3540,33 @@
       <c r="D34" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E34" t="str">
+      <c r="E34" s="7">
+        <v>15</v>
+      </c>
+      <c r="F34" s="7">
+        <v>788</v>
+      </c>
+      <c r="G34" s="7">
+        <v>802</v>
+      </c>
+      <c r="H34" t="str">
         <f t="shared" si="0"/>
         <v>'DEM'</v>
       </c>
-      <c r="F34" t="str">
+      <c r="I34" t="str">
         <f t="shared" si="1"/>
         <v>'COUNTRY'</v>
       </c>
-      <c r="G34" t="str">
+      <c r="J34" t="str">
         <f t="shared" si="2"/>
         <v>'Country'</v>
       </c>
-      <c r="H34" t="str">
+      <c r="K34" t="str">
         <f t="shared" si="3"/>
         <v>('DEM','COUNTRY','Country'),</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>48</v>
       </c>
@@ -3254,24 +3579,33 @@
       <c r="D35" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E35" t="str">
+      <c r="E35" s="7">
+        <v>15</v>
+      </c>
+      <c r="F35" s="7">
+        <v>803</v>
+      </c>
+      <c r="G35" s="7">
+        <v>817</v>
+      </c>
+      <c r="H35" t="str">
         <f t="shared" si="0"/>
         <v>'DEM'</v>
       </c>
-      <c r="F35" t="str">
+      <c r="I35" t="str">
         <f t="shared" si="1"/>
         <v>'OPERATION_NAME'</v>
       </c>
-      <c r="G35" t="str">
+      <c r="J35" t="str">
         <f t="shared" si="2"/>
         <v>'Name of Operation'</v>
       </c>
-      <c r="H35" t="str">
+      <c r="K35" t="str">
         <f t="shared" si="3"/>
         <v>('DEM','OPERATION_NAME','Name of Operation'),</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>48</v>
       </c>
@@ -3284,24 +3618,33 @@
       <c r="D36" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="E36" t="str">
+      <c r="E36" s="7">
+        <v>1</v>
+      </c>
+      <c r="F36" s="7">
+        <v>818</v>
+      </c>
+      <c r="G36" s="7">
+        <v>818</v>
+      </c>
+      <c r="H36" t="str">
         <f t="shared" si="0"/>
         <v>'DEM'</v>
       </c>
-      <c r="F36" t="str">
+      <c r="I36" t="str">
         <f t="shared" si="1"/>
         <v>'DEPLOY_PREV'</v>
       </c>
-      <c r="G36" t="str">
+      <c r="J36" t="str">
         <f t="shared" si="2"/>
         <v>'Previous deployments'</v>
       </c>
-      <c r="H36" t="str">
+      <c r="K36" t="str">
         <f t="shared" si="3"/>
         <v>('DEM','DEPLOY_PREV','Previous deployments'),</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>48</v>
       </c>
@@ -3314,24 +3657,33 @@
       <c r="D37" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E37" t="str">
+      <c r="E37" s="7">
+        <v>15</v>
+      </c>
+      <c r="F37" s="7">
+        <v>819</v>
+      </c>
+      <c r="G37" s="7">
+        <v>833</v>
+      </c>
+      <c r="H37" t="str">
         <f t="shared" si="0"/>
         <v>'DEM'</v>
       </c>
-      <c r="F37" t="str">
+      <c r="I37" t="str">
         <f t="shared" si="1"/>
         <v>'DEP_PRIMARY'</v>
       </c>
-      <c r="G37" t="str">
+      <c r="J37" t="str">
         <f t="shared" si="2"/>
         <v>'Primary country of last deployment'</v>
       </c>
-      <c r="H37" t="str">
+      <c r="K37" t="str">
         <f t="shared" si="3"/>
         <v>('DEM','DEP_PRIMARY','Primary country of last deployment'),</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>48</v>
       </c>
@@ -3344,24 +3696,33 @@
       <c r="D38" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="E38" t="str">
+      <c r="E38" s="7">
+        <v>8</v>
+      </c>
+      <c r="F38" s="7">
+        <v>834</v>
+      </c>
+      <c r="G38" s="7">
+        <v>841</v>
+      </c>
+      <c r="H38" t="str">
         <f t="shared" si="0"/>
         <v>'DEM'</v>
       </c>
-      <c r="F38" t="str">
+      <c r="I38" t="str">
         <f t="shared" si="1"/>
         <v>'D_RET_PREV'</v>
       </c>
-      <c r="G38" t="str">
+      <c r="J38" t="str">
         <f t="shared" si="2"/>
         <v>'Date of Return from previous deployment'</v>
       </c>
-      <c r="H38" t="str">
+      <c r="K38" t="str">
         <f t="shared" si="3"/>
         <v>('DEM','D_RET_PREV','Date of Return from previous deployment'),</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>1</v>
       </c>
@@ -3374,24 +3735,33 @@
       <c r="D39" s="3" t="s">
         <v>545</v>
       </c>
-      <c r="E39" t="str">
+      <c r="E39" s="7">
+        <v>1</v>
+      </c>
+      <c r="F39" s="7">
+        <v>842</v>
+      </c>
+      <c r="G39" s="7">
+        <v>842</v>
+      </c>
+      <c r="H39" t="str">
         <f t="shared" si="0"/>
         <v>'1'</v>
       </c>
-      <c r="F39" t="str">
+      <c r="I39" t="str">
         <f t="shared" si="1"/>
         <v>'HEALTH_ASSESSMENT'</v>
       </c>
-      <c r="G39" t="str">
+      <c r="J39" t="str">
         <f t="shared" si="2"/>
         <v>'Overall, how would you rate your health during the PAST MONTH?'</v>
       </c>
-      <c r="H39" t="str">
+      <c r="K39" t="str">
         <f t="shared" si="3"/>
         <v>('1','HEALTH_ASSESSMENT','Overall, how would you rate your health during the PAST MONTH?'),</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>2</v>
       </c>
@@ -3404,24 +3774,33 @@
       <c r="D40" s="3" t="s">
         <v>546</v>
       </c>
-      <c r="E40" t="str">
+      <c r="E40" s="7">
+        <v>1</v>
+      </c>
+      <c r="F40" s="7">
+        <v>843</v>
+      </c>
+      <c r="G40" s="7">
+        <v>843</v>
+      </c>
+      <c r="H40" t="str">
         <f t="shared" si="0"/>
         <v>'2'</v>
       </c>
-      <c r="F40" t="str">
+      <c r="I40" t="str">
         <f t="shared" si="1"/>
         <v>'LIGHT_DUTY'</v>
       </c>
-      <c r="G40" t="str">
+      <c r="J40" t="str">
         <f t="shared" si="2"/>
         <v>'Are you CURRENTLY on a profile, limited duty, waiting on a MOS/Medical Retention Board (MMRB) decision, or being referred to a medical evaluation board (MEB) or physical evaluation board (PEB)?'</v>
       </c>
-      <c r="H40" t="str">
+      <c r="K40" t="str">
         <f t="shared" si="3"/>
         <v>('2','LIGHT_DUTY','Are you CURRENTLY on a profile, limited duty, waiting on a MOS/Medical Retention Board (MMRB) decision, or being referred to a medical evaluation board (MEB) or physical evaluation board (PEB)?'),</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>2</v>
       </c>
@@ -3434,24 +3813,33 @@
       <c r="D41" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E41" t="str">
+      <c r="E41" s="7">
+        <v>20</v>
+      </c>
+      <c r="F41" s="7">
+        <v>844</v>
+      </c>
+      <c r="G41" s="7">
+        <v>863</v>
+      </c>
+      <c r="H41" t="str">
         <f t="shared" si="0"/>
         <v>'2'</v>
       </c>
-      <c r="F41" t="str">
+      <c r="I41" t="str">
         <f t="shared" si="1"/>
         <v>'LIGHT_DUTY_REASON'</v>
       </c>
-      <c r="G41" t="str">
+      <c r="J41" t="str">
         <f t="shared" si="2"/>
         <v>'Reason for light duty'</v>
       </c>
-      <c r="H41" t="str">
+      <c r="K41" t="str">
         <f t="shared" si="3"/>
         <v>('2','LIGHT_DUTY_REASON','Reason for light duty'),</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>3</v>
       </c>
@@ -3464,24 +3852,33 @@
       <c r="D42" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="E42" t="str">
+      <c r="E42" s="7">
+        <v>1</v>
+      </c>
+      <c r="F42" s="7">
+        <v>864</v>
+      </c>
+      <c r="G42" s="7">
+        <v>864</v>
+      </c>
+      <c r="H42" t="str">
         <f t="shared" si="0"/>
         <v>'3'</v>
       </c>
-      <c r="F42" t="str">
+      <c r="I42" t="str">
         <f t="shared" si="1"/>
         <v>'TOBACCO'</v>
       </c>
-      <c r="G42" t="str">
+      <c r="J42" t="str">
         <f t="shared" si="2"/>
         <v>'How often do you smoke tobacco'</v>
       </c>
-      <c r="H42" t="str">
+      <c r="K42" t="str">
         <f t="shared" si="3"/>
         <v>('3','TOBACCO','How often do you smoke tobacco'),</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>4</v>
       </c>
@@ -3494,24 +3891,33 @@
       <c r="D43" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="E43" t="str">
+      <c r="E43" s="7">
+        <v>1</v>
+      </c>
+      <c r="F43" s="7">
+        <v>865</v>
+      </c>
+      <c r="G43" s="7">
+        <v>865</v>
+      </c>
+      <c r="H43" t="str">
         <f t="shared" si="0"/>
         <v>'4'</v>
       </c>
-      <c r="F43" t="str">
+      <c r="I43" t="str">
         <f t="shared" si="1"/>
         <v>'PREGNANT'</v>
       </c>
-      <c r="G43" t="str">
+      <c r="J43" t="str">
         <f t="shared" si="2"/>
         <v>'Are you pregnant or is there a chance'</v>
       </c>
-      <c r="H43" t="str">
+      <c r="K43" t="str">
         <f t="shared" si="3"/>
         <v>('4','PREGNANT','Are you pregnant or is there a chance'),</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
         <v>5</v>
       </c>
@@ -3524,24 +3930,33 @@
       <c r="D44" s="4" t="s">
         <v>549</v>
       </c>
-      <c r="E44" t="str">
+      <c r="E44" s="8">
+        <v>1</v>
+      </c>
+      <c r="F44" s="7">
+        <v>866</v>
+      </c>
+      <c r="G44" s="7">
+        <v>866</v>
+      </c>
+      <c r="H44" t="str">
         <f t="shared" si="0"/>
         <v>'5'</v>
       </c>
-      <c r="F44" t="str">
+      <c r="I44" t="str">
         <f t="shared" si="1"/>
         <v>'CONTRA_COUNSEL'</v>
       </c>
-      <c r="G44" t="str">
+      <c r="J44" t="str">
         <f t="shared" si="2"/>
         <v>'Do you wish to receive contraceptive counseling?'</v>
       </c>
-      <c r="H44" t="str">
+      <c r="K44" t="str">
         <f t="shared" si="3"/>
         <v>('5','CONTRA_COUNSEL','Do you wish to receive contraceptive counseling?'),</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>6</v>
       </c>
@@ -3554,24 +3969,33 @@
       <c r="D45" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E45" t="str">
+      <c r="E45" s="7">
+        <v>1</v>
+      </c>
+      <c r="F45" s="7">
+        <v>867</v>
+      </c>
+      <c r="G45" s="7">
+        <v>867</v>
+      </c>
+      <c r="H45" t="str">
         <f t="shared" si="0"/>
         <v>'6'</v>
       </c>
-      <c r="F45" t="str">
+      <c r="I45" t="str">
         <f t="shared" si="1"/>
         <v>'CARE_HEAD'</v>
       </c>
-      <c r="G45" t="str">
+      <c r="J45" t="str">
         <f t="shared" si="2"/>
         <v>'In the past year did you receive care for a head injury?'</v>
       </c>
-      <c r="H45" t="str">
+      <c r="K45" t="str">
         <f t="shared" si="3"/>
         <v>('6','CARE_HEAD','In the past year did you receive care for a head injury?'),</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>6</v>
       </c>
@@ -3584,24 +4008,33 @@
       <c r="D46" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E46" t="str">
+      <c r="E46" s="7">
+        <v>25</v>
+      </c>
+      <c r="F46" s="7">
+        <v>868</v>
+      </c>
+      <c r="G46" s="7">
+        <v>892</v>
+      </c>
+      <c r="H46" t="str">
         <f t="shared" si="0"/>
         <v>'6'</v>
       </c>
-      <c r="F46" t="str">
+      <c r="I46" t="str">
         <f t="shared" si="1"/>
         <v>'CARE_HEAD_TEXT'</v>
       </c>
-      <c r="G46" t="str">
+      <c r="J46" t="str">
         <f t="shared" si="2"/>
         <v>'Please Explain (head)'</v>
       </c>
-      <c r="H46" t="str">
+      <c r="K46" t="str">
         <f t="shared" si="3"/>
         <v>('6','CARE_HEAD_TEXT','Please Explain (head)'),</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>7</v>
       </c>
@@ -3614,24 +4047,33 @@
       <c r="D47" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="E47" t="str">
+      <c r="E47" s="7">
+        <v>1</v>
+      </c>
+      <c r="F47" s="7">
+        <v>893</v>
+      </c>
+      <c r="G47" s="7">
+        <v>893</v>
+      </c>
+      <c r="H47" t="str">
         <f t="shared" si="0"/>
         <v>'7'</v>
       </c>
-      <c r="F47" t="str">
+      <c r="I47" t="str">
         <f t="shared" si="1"/>
         <v>'CURRENT_MEDS'</v>
       </c>
-      <c r="G47" t="str">
+      <c r="J47" t="str">
         <f t="shared" si="2"/>
         <v>'What prescription or over-the- counter medications (including herbals/supplements) for sleep, pain, combat stress, or mental health conditions or concerns are you CURRENTLY taking?'</v>
       </c>
-      <c r="H47" t="str">
+      <c r="K47" t="str">
         <f t="shared" si="3"/>
         <v>('7','CURRENT_MEDS','What prescription or over-the- counter medications (including herbals/supplements) for sleep, pain, combat stress, or mental health conditions or concerns are you CURRENTLY taking?'),</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>7</v>
       </c>
@@ -3644,24 +4086,33 @@
       <c r="D48" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E48" t="str">
+      <c r="E48" s="7">
+        <v>100</v>
+      </c>
+      <c r="F48" s="7">
+        <v>894</v>
+      </c>
+      <c r="G48" s="7">
+        <v>993</v>
+      </c>
+      <c r="H48" t="str">
         <f t="shared" si="0"/>
         <v>'7'</v>
       </c>
-      <c r="F48" t="str">
+      <c r="I48" t="str">
         <f t="shared" si="1"/>
         <v>'CURRENT_MEDS_TEXT'</v>
       </c>
-      <c r="G48" t="str">
+      <c r="J48" t="str">
         <f t="shared" si="2"/>
         <v>'If yes, please list.'</v>
       </c>
-      <c r="H48" t="str">
+      <c r="K48" t="str">
         <f t="shared" si="3"/>
         <v>('7','CURRENT_MEDS_TEXT','If yes, please list.'),</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>8</v>
       </c>
@@ -3674,24 +4125,33 @@
       <c r="D49" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E49" t="str">
+      <c r="E49" s="7">
+        <v>1</v>
+      </c>
+      <c r="F49" s="7">
+        <v>994</v>
+      </c>
+      <c r="G49" s="7">
+        <v>994</v>
+      </c>
+      <c r="H49" t="str">
         <f t="shared" si="0"/>
         <v>'8'</v>
       </c>
-      <c r="F49" t="str">
+      <c r="I49" t="str">
         <f t="shared" si="1"/>
         <v>'CARE_MENTAL'</v>
       </c>
-      <c r="G49" t="str">
+      <c r="J49" t="str">
         <f t="shared" si="2"/>
         <v>'In the PAST YEAR did you receive care for any mental health condition or concern such as, but not limited to post traumatic stress disorder (PTSD),depression, anxiety disorder, alcohol abuse or substance abuse?'</v>
       </c>
-      <c r="H49" t="str">
+      <c r="K49" t="str">
         <f t="shared" si="3"/>
         <v>('8','CARE_MENTAL','In the PAST YEAR did you receive care for any mental health condition or concern such as, but not limited to post traumatic stress disorder (PTSD),depression, anxiety disorder, alcohol abuse or substance abuse?'),</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>8</v>
       </c>
@@ -3704,24 +4164,33 @@
       <c r="D50" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E50" t="str">
+      <c r="E50" s="7">
+        <v>100</v>
+      </c>
+      <c r="F50" s="7">
+        <v>995</v>
+      </c>
+      <c r="G50" s="7">
+        <v>1094</v>
+      </c>
+      <c r="H50" t="str">
         <f t="shared" si="0"/>
         <v>'8'</v>
       </c>
-      <c r="F50" t="str">
+      <c r="I50" t="str">
         <f t="shared" si="1"/>
         <v>'CARE_MENTAL_TEXT'</v>
       </c>
-      <c r="G50" t="str">
+      <c r="J50" t="str">
         <f t="shared" si="2"/>
         <v>'If yes, please explain'</v>
       </c>
-      <c r="H50" t="str">
+      <c r="K50" t="str">
         <f t="shared" si="3"/>
         <v>('8','CARE_MENTAL_TEXT','If yes, please explain'),</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>131</v>
       </c>
@@ -3734,24 +4203,33 @@
       <c r="D51" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="E51" t="str">
+      <c r="E51" s="7">
+        <v>1</v>
+      </c>
+      <c r="F51" s="7">
+        <v>1095</v>
+      </c>
+      <c r="G51" s="7">
+        <v>1095</v>
+      </c>
+      <c r="H51" t="str">
         <f t="shared" si="0"/>
         <v>'9a'</v>
       </c>
-      <c r="F51" t="str">
+      <c r="I51" t="str">
         <f t="shared" si="1"/>
         <v>'NOISES'</v>
       </c>
-      <c r="G51" t="str">
+      <c r="J51" t="str">
         <f t="shared" si="2"/>
         <v>'Noises in your head or ears (such as ringing, buzzing, crickets, humming, tone, etc.) Past month'</v>
       </c>
-      <c r="H51" t="str">
+      <c r="K51" t="str">
         <f t="shared" si="3"/>
         <v>('9a','NOISES','Noises in your head or ears (such as ringing, buzzing, crickets, humming, tone, etc.) Past month'),</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>133</v>
       </c>
@@ -3764,24 +4242,33 @@
       <c r="D52" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="E52" t="str">
+      <c r="E52" s="7">
+        <v>1</v>
+      </c>
+      <c r="F52" s="7">
+        <v>1096</v>
+      </c>
+      <c r="G52" s="7">
+        <v>1096</v>
+      </c>
+      <c r="H52" t="str">
         <f t="shared" si="0"/>
         <v>'9b'</v>
       </c>
-      <c r="F52" t="str">
+      <c r="I52" t="str">
         <f t="shared" si="1"/>
         <v>'HEARING'</v>
       </c>
-      <c r="G52" t="str">
+      <c r="J52" t="str">
         <f t="shared" si="2"/>
         <v>'Trouble hearing Past month'</v>
       </c>
-      <c r="H52" t="str">
+      <c r="K52" t="str">
         <f t="shared" si="3"/>
         <v>('9b','HEARING','Trouble hearing Past month'),</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>135</v>
       </c>
@@ -3794,24 +4281,33 @@
       <c r="D53" s="3" t="s">
         <v>552</v>
       </c>
-      <c r="E53" t="str">
+      <c r="E53" s="7">
+        <v>1</v>
+      </c>
+      <c r="F53" s="7">
+        <v>1097</v>
+      </c>
+      <c r="G53" s="7">
+        <v>1097</v>
+      </c>
+      <c r="H53" t="str">
         <f t="shared" si="0"/>
         <v>'10a'</v>
       </c>
-      <c r="F53" t="str">
+      <c r="I53" t="str">
         <f t="shared" si="1"/>
         <v>'ETOH_OFTEN'</v>
       </c>
-      <c r="G53" t="str">
+      <c r="J53" t="str">
         <f t="shared" si="2"/>
         <v>'How often do you have a drink containing alcohol?'</v>
       </c>
-      <c r="H53" t="str">
+      <c r="K53" t="str">
         <f t="shared" si="3"/>
         <v>('10a','ETOH_OFTEN','How often do you have a drink containing alcohol?'),</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>137</v>
       </c>
@@ -3824,24 +4320,33 @@
       <c r="D54" s="3" t="s">
         <v>553</v>
       </c>
-      <c r="E54" t="str">
+      <c r="E54" s="7">
+        <v>1</v>
+      </c>
+      <c r="F54" s="7">
+        <v>1098</v>
+      </c>
+      <c r="G54" s="7">
+        <v>1098</v>
+      </c>
+      <c r="H54" t="str">
         <f t="shared" si="0"/>
         <v>'10b'</v>
       </c>
-      <c r="F54" t="str">
+      <c r="I54" t="str">
         <f t="shared" si="1"/>
         <v>'ETOH_DAY'</v>
       </c>
-      <c r="G54" t="str">
+      <c r="J54" t="str">
         <f t="shared" si="2"/>
         <v>'How many drinks containing alcohol do you have on a typical day when you are drinking?'</v>
       </c>
-      <c r="H54" t="str">
+      <c r="K54" t="str">
         <f t="shared" si="3"/>
         <v>('10b','ETOH_DAY','How many drinks containing alcohol do you have on a typical day when you are drinking?'),</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>139</v>
       </c>
@@ -3854,24 +4359,33 @@
       <c r="D55" s="3" t="s">
         <v>554</v>
       </c>
-      <c r="E55" t="str">
+      <c r="E55" s="7">
+        <v>1</v>
+      </c>
+      <c r="F55" s="7">
+        <v>1099</v>
+      </c>
+      <c r="G55" s="7">
+        <v>1099</v>
+      </c>
+      <c r="H55" t="str">
         <f t="shared" si="0"/>
         <v>'10c'</v>
       </c>
-      <c r="F55" t="str">
+      <c r="I55" t="str">
         <f t="shared" si="1"/>
         <v>'ETOH_BINGE'</v>
       </c>
-      <c r="G55" t="str">
+      <c r="J55" t="str">
         <f t="shared" si="2"/>
         <v>'How often do you have six or more drinks on one occasion?'</v>
       </c>
-      <c r="H55" t="str">
+      <c r="K55" t="str">
         <f t="shared" si="3"/>
         <v>('10c','ETOH_BINGE','How often do you have six or more drinks on one occasion?'),</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>141</v>
       </c>
@@ -3884,24 +4398,33 @@
       <c r="D56" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E56" t="str">
+      <c r="E56" s="7">
+        <v>1</v>
+      </c>
+      <c r="F56" s="7">
+        <v>1100</v>
+      </c>
+      <c r="G56" s="7">
+        <v>1100</v>
+      </c>
+      <c r="H56" t="str">
         <f t="shared" si="0"/>
         <v>'11a'</v>
       </c>
-      <c r="F56" t="str">
+      <c r="I56" t="str">
         <f t="shared" si="1"/>
         <v>'NIGHTMARES'</v>
       </c>
-      <c r="G56" t="str">
+      <c r="J56" t="str">
         <f t="shared" si="2"/>
         <v>'Have you ever had any experience that was so frightening, horrible, or upsetting that, in the PAST MONTH, you: Have had nightmares about it or thought about it when you did not want to?'</v>
       </c>
-      <c r="H56" t="str">
+      <c r="K56" t="str">
         <f t="shared" si="3"/>
         <v>('11a','NIGHTMARES','Have you ever had any experience that was so frightening, horrible, or upsetting that, in the PAST MONTH, you: Have had nightmares about it or thought about it when you did not want to?'),</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>143</v>
       </c>
@@ -3914,24 +4437,33 @@
       <c r="D57" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E57" t="str">
+      <c r="E57" s="7">
+        <v>1</v>
+      </c>
+      <c r="F57" s="7">
+        <v>1101</v>
+      </c>
+      <c r="G57" s="7">
+        <v>1101</v>
+      </c>
+      <c r="H57" t="str">
         <f t="shared" si="0"/>
         <v>'11b'</v>
       </c>
-      <c r="F57" t="str">
+      <c r="I57" t="str">
         <f t="shared" si="1"/>
         <v>'AVOID_SITUATIONS'</v>
       </c>
-      <c r="G57" t="str">
+      <c r="J57" t="str">
         <f t="shared" si="2"/>
         <v>'Have you ever had any experience that was so frightening, horrible, or upsetting that, in the PAST MONTH, you: Tried hard not to think about it or went out of your way to avoid situations that remind you of it?'</v>
       </c>
-      <c r="H57" t="str">
+      <c r="K57" t="str">
         <f t="shared" si="3"/>
         <v>('11b','AVOID_SITUATIONS','Have you ever had any experience that was so frightening, horrible, or upsetting that, in the PAST MONTH, you: Tried hard not to think about it or went out of your way to avoid situations that remind you of it?'),</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>146</v>
       </c>
@@ -3944,24 +4476,33 @@
       <c r="D58" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E58" t="str">
+      <c r="E58" s="7">
+        <v>1</v>
+      </c>
+      <c r="F58" s="7">
+        <v>1102</v>
+      </c>
+      <c r="G58" s="7">
+        <v>1102</v>
+      </c>
+      <c r="H58" t="str">
         <f t="shared" si="0"/>
         <v>'11c'</v>
       </c>
-      <c r="F58" t="str">
+      <c r="I58" t="str">
         <f t="shared" si="1"/>
         <v>'ON_GUARD'</v>
       </c>
-      <c r="G58" t="str">
+      <c r="J58" t="str">
         <f t="shared" si="2"/>
         <v>'Have you ever had any experience that was so frightening, horrible, or upsetting that, in the PAST MONTH, you: Were constantly on guard, watchful or easily startled?'</v>
       </c>
-      <c r="H58" t="str">
+      <c r="K58" t="str">
         <f t="shared" si="3"/>
         <v>('11c','ON_GUARD','Have you ever had any experience that was so frightening, horrible, or upsetting that, in the PAST MONTH, you: Were constantly on guard, watchful or easily startled?'),</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>149</v>
       </c>
@@ -3974,24 +4515,33 @@
       <c r="D59" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E59" t="str">
+      <c r="E59" s="7">
+        <v>1</v>
+      </c>
+      <c r="F59" s="7">
+        <v>1103</v>
+      </c>
+      <c r="G59" s="7">
+        <v>1103</v>
+      </c>
+      <c r="H59" t="str">
         <f t="shared" si="0"/>
         <v>'11d'</v>
       </c>
-      <c r="F59" t="str">
+      <c r="I59" t="str">
         <f t="shared" si="1"/>
         <v>'DETACHED'</v>
       </c>
-      <c r="G59" t="str">
+      <c r="J59" t="str">
         <f t="shared" si="2"/>
         <v>'Have you ever had any experience that was so frightening, horrible, or upsetting that, in the PAST MONTH, you: Felt numb or detached from others, activities, or your surroundings?'</v>
       </c>
-      <c r="H59" t="str">
+      <c r="K59" t="str">
         <f t="shared" si="3"/>
         <v>('11d','DETACHED','Have you ever had any experience that was so frightening, horrible, or upsetting that, in the PAST MONTH, you: Felt numb or detached from others, activities, or your surroundings?'),</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>151</v>
       </c>
@@ -4004,24 +4554,33 @@
       <c r="D60" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E60" t="str">
+      <c r="E60" s="7">
+        <v>1</v>
+      </c>
+      <c r="F60" s="7">
+        <v>1104</v>
+      </c>
+      <c r="G60" s="7">
+        <v>1104</v>
+      </c>
+      <c r="H60" t="str">
         <f t="shared" si="0"/>
         <v>'11e'</v>
       </c>
-      <c r="F60" t="str">
+      <c r="I60" t="str">
         <f t="shared" si="1"/>
         <v>'BLAME'</v>
       </c>
-      <c r="G60" t="str">
+      <c r="J60" t="str">
         <f t="shared" si="2"/>
         <v>'Felt guilt or unable to stop blaming yourself or others for the event(s) or any problems the event(s) may have caused?'</v>
       </c>
-      <c r="H60" t="str">
+      <c r="K60" t="str">
         <f t="shared" si="3"/>
         <v>('11e','BLAME','Felt guilt or unable to stop blaming yourself or others for the event(s) or any problems the event(s) may have caused?'),</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>153</v>
       </c>
@@ -4034,24 +4593,33 @@
       <c r="D61" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="E61" t="str">
+      <c r="E61" s="7">
+        <v>1</v>
+      </c>
+      <c r="F61" s="7">
+        <v>1105</v>
+      </c>
+      <c r="G61" s="7">
+        <v>1105</v>
+      </c>
+      <c r="H61" t="str">
         <f t="shared" si="0"/>
         <v>'11f'</v>
       </c>
-      <c r="F61" t="str">
+      <c r="I61" t="str">
         <f t="shared" si="1"/>
         <v>'MEMORIES'</v>
       </c>
-      <c r="G61" t="str">
+      <c r="J61" t="str">
         <f t="shared" si="2"/>
         <v>'Have you been bothered by that problem in the PAST MONTH. Repeated, disturbing memories, thoughts, or images of a stressful experience from the past?'</v>
       </c>
-      <c r="H61" t="str">
+      <c r="K61" t="str">
         <f t="shared" si="3"/>
         <v>('11f','MEMORIES','Have you been bothered by that problem in the PAST MONTH. Repeated, disturbing memories, thoughts, or images of a stressful experience from the past?'),</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>155</v>
       </c>
@@ -4064,24 +4632,33 @@
       <c r="D62" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="E62" t="str">
+      <c r="E62" s="7">
+        <v>1</v>
+      </c>
+      <c r="F62" s="7">
+        <v>1106</v>
+      </c>
+      <c r="G62" s="7">
+        <v>1106</v>
+      </c>
+      <c r="H62" t="str">
         <f t="shared" si="0"/>
         <v>'11g'</v>
       </c>
-      <c r="F62" t="str">
+      <c r="I62" t="str">
         <f t="shared" si="1"/>
         <v>'DREAMS'</v>
       </c>
-      <c r="G62" t="str">
+      <c r="J62" t="str">
         <f t="shared" si="2"/>
         <v>'Have you been bothered by that problem in the PAST MONTH. Repeated, disturbing dreams of a stressful experience from the past?'</v>
       </c>
-      <c r="H62" t="str">
+      <c r="K62" t="str">
         <f t="shared" si="3"/>
         <v>('11g','DREAMS','Have you been bothered by that problem in the PAST MONTH. Repeated, disturbing dreams of a stressful experience from the past?'),</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>157</v>
       </c>
@@ -4094,24 +4671,33 @@
       <c r="D63" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="E63" t="str">
+      <c r="E63" s="7">
+        <v>1</v>
+      </c>
+      <c r="F63" s="7">
+        <v>1107</v>
+      </c>
+      <c r="G63" s="7">
+        <v>1107</v>
+      </c>
+      <c r="H63" t="str">
         <f t="shared" si="0"/>
         <v>'11h'</v>
       </c>
-      <c r="F63" t="str">
+      <c r="I63" t="str">
         <f t="shared" si="1"/>
         <v>'RELIVING'</v>
       </c>
-      <c r="G63" t="str">
+      <c r="J63" t="str">
         <f t="shared" si="2"/>
         <v>'Have you been bothered by that problem in the PAST MONTH. Suddenly acting or feeling as if a stressful experience were happening again (as if you were reliving it)?'</v>
       </c>
-      <c r="H63" t="str">
+      <c r="K63" t="str">
         <f t="shared" si="3"/>
         <v>('11h','RELIVING','Have you been bothered by that problem in the PAST MONTH. Suddenly acting or feeling as if a stressful experience were happening again (as if you were reliving it)?'),</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>160</v>
       </c>
@@ -4124,24 +4710,33 @@
       <c r="D64" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="E64" t="str">
+      <c r="E64" s="7">
+        <v>1</v>
+      </c>
+      <c r="F64" s="7">
+        <v>1108</v>
+      </c>
+      <c r="G64" s="7">
+        <v>1108</v>
+      </c>
+      <c r="H64" t="str">
         <f t="shared" si="0"/>
         <v>'11i'</v>
       </c>
-      <c r="F64" t="str">
+      <c r="I64" t="str">
         <f t="shared" si="1"/>
         <v>'UPSET'</v>
       </c>
-      <c r="G64" t="str">
+      <c r="J64" t="str">
         <f t="shared" si="2"/>
         <v>'Have you been bothered by that problem in the PAST MONTH. Feeling very upset when something reminded you of a stressful experience from the past?'</v>
       </c>
-      <c r="H64" t="str">
+      <c r="K64" t="str">
         <f t="shared" si="3"/>
         <v>('11i','UPSET','Have you been bothered by that problem in the PAST MONTH. Feeling very upset when something reminded you of a stressful experience from the past?'),</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>162</v>
       </c>
@@ -4154,24 +4749,33 @@
       <c r="D65" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="E65" t="str">
+      <c r="E65" s="7">
+        <v>1</v>
+      </c>
+      <c r="F65" s="7">
+        <v>1109</v>
+      </c>
+      <c r="G65" s="7">
+        <v>1109</v>
+      </c>
+      <c r="H65" t="str">
         <f t="shared" si="0"/>
         <v>'11j'</v>
       </c>
-      <c r="F65" t="str">
+      <c r="I65" t="str">
         <f t="shared" si="1"/>
         <v>'PHYS_REACTION'</v>
       </c>
-      <c r="G65" t="str">
+      <c r="J65" t="str">
         <f t="shared" si="2"/>
         <v>'Have you been bothered by that problem in the PAST MONTH. Having physical reactions (e.g., heart pounding, trouble breathing, or sweating) when something reminded you of a stressful experience from the past?'</v>
       </c>
-      <c r="H65" t="str">
+      <c r="K65" t="str">
         <f t="shared" si="3"/>
         <v>('11j','PHYS_REACTION','Have you been bothered by that problem in the PAST MONTH. Having physical reactions (e.g., heart pounding, trouble breathing, or sweating) when something reminded you of a stressful experience from the past?'),</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>165</v>
       </c>
@@ -4184,24 +4788,33 @@
       <c r="D66" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="E66" t="str">
+      <c r="E66" s="7">
+        <v>1</v>
+      </c>
+      <c r="F66" s="7">
+        <v>1110</v>
+      </c>
+      <c r="G66" s="7">
+        <v>1110</v>
+      </c>
+      <c r="H66" t="str">
         <f t="shared" si="0"/>
         <v>'11k'</v>
       </c>
-      <c r="F66" t="str">
+      <c r="I66" t="str">
         <f t="shared" si="1"/>
         <v>'AVOID_THINK'</v>
       </c>
-      <c r="G66" t="str">
+      <c r="J66" t="str">
         <f t="shared" si="2"/>
         <v>'Have you been bothered by that problem in the PAST MONTH. Avoid thinking about or talking about a stressful experience from the past or avoid having feelings related to it?'</v>
       </c>
-      <c r="H66" t="str">
+      <c r="K66" t="str">
         <f t="shared" si="3"/>
         <v>('11k','AVOID_THINK','Have you been bothered by that problem in the PAST MONTH. Avoid thinking about or talking about a stressful experience from the past or avoid having feelings related to it?'),</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>168</v>
       </c>
@@ -4214,24 +4827,33 @@
       <c r="D67" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="E67" t="str">
-        <f t="shared" ref="E67:E130" si="4">$E$1&amp;A67&amp;$E$1</f>
+      <c r="E67" s="7">
+        <v>1</v>
+      </c>
+      <c r="F67" s="7">
+        <v>1111</v>
+      </c>
+      <c r="G67" s="7">
+        <v>1111</v>
+      </c>
+      <c r="H67" t="str">
+        <f t="shared" ref="H67:H130" si="4">$H$1&amp;A67&amp;$H$1</f>
         <v>'11l'</v>
       </c>
-      <c r="F67" t="str">
-        <f t="shared" ref="F67:F130" si="5">$E$1&amp;B67&amp;$E$1</f>
+      <c r="I67" t="str">
+        <f t="shared" ref="I67:I130" si="5">$H$1&amp;B67&amp;$H$1</f>
         <v>'AVOID_ACTIVITIES'</v>
       </c>
-      <c r="G67" t="str">
-        <f t="shared" ref="G67:G130" si="6">$E$1&amp;SUBSTITUTE(C67, "'", "''")&amp;$E$1</f>
+      <c r="J67" t="str">
+        <f t="shared" ref="J67:J130" si="6">$H$1&amp;SUBSTITUTE(C67, "'", "''")&amp;$H$1</f>
         <v>'Have you been bothered by that problem in the PAST MONTH. Avoid activities or situations because they remind you of a stressful experience from the past?'</v>
       </c>
-      <c r="H67" t="str">
-        <f t="shared" ref="H67:H130" si="7">"("&amp;E67&amp;","&amp;F67&amp;","&amp;G67&amp;"),"</f>
+      <c r="K67" t="str">
+        <f t="shared" ref="K67:K130" si="7">"("&amp;H67&amp;","&amp;I67&amp;","&amp;J67&amp;"),"</f>
         <v>('11l','AVOID_ACTIVITIES','Have you been bothered by that problem in the PAST MONTH. Avoid activities or situations because they remind you of a stressful experience from the past?'),</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>171</v>
       </c>
@@ -4244,24 +4866,33 @@
       <c r="D68" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="E68" t="str">
+      <c r="E68" s="7">
+        <v>1</v>
+      </c>
+      <c r="F68" s="7">
+        <v>1112</v>
+      </c>
+      <c r="G68" s="7">
+        <v>1112</v>
+      </c>
+      <c r="H68" t="str">
         <f t="shared" si="4"/>
         <v>'11m'</v>
       </c>
-      <c r="F68" t="str">
+      <c r="I68" t="str">
         <f t="shared" si="5"/>
         <v>'TROUBLE_MEMORY'</v>
       </c>
-      <c r="G68" t="str">
+      <c r="J68" t="str">
         <f t="shared" si="6"/>
         <v>'Have you been bothered by that problem in the PAST MONTH. Trouble remembering important parts of a stressful experience from the past?'</v>
       </c>
-      <c r="H68" t="str">
+      <c r="K68" t="str">
         <f t="shared" si="7"/>
         <v>('11m','TROUBLE_MEMORY','Have you been bothered by that problem in the PAST MONTH. Trouble remembering important parts of a stressful experience from the past?'),</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>174</v>
       </c>
@@ -4274,24 +4905,33 @@
       <c r="D69" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="E69" t="str">
+      <c r="E69" s="7">
+        <v>1</v>
+      </c>
+      <c r="F69" s="7">
+        <v>1113</v>
+      </c>
+      <c r="G69" s="7">
+        <v>1113</v>
+      </c>
+      <c r="H69" t="str">
         <f t="shared" si="4"/>
         <v>'11n'</v>
       </c>
-      <c r="F69" t="str">
+      <c r="I69" t="str">
         <f t="shared" si="5"/>
         <v>'DISINTEREST'</v>
       </c>
-      <c r="G69" t="str">
+      <c r="J69" t="str">
         <f t="shared" si="6"/>
         <v>'Have you been bothered by that problem in the PAST MONTH. Loss of interest in things that you used to enjoy?'</v>
       </c>
-      <c r="H69" t="str">
+      <c r="K69" t="str">
         <f t="shared" si="7"/>
         <v>('11n','DISINTEREST','Have you been bothered by that problem in the PAST MONTH. Loss of interest in things that you used to enjoy?'),</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>177</v>
       </c>
@@ -4304,24 +4944,33 @@
       <c r="D70" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="E70" t="str">
+      <c r="E70" s="7">
+        <v>1</v>
+      </c>
+      <c r="F70" s="7">
+        <v>1114</v>
+      </c>
+      <c r="G70" s="7">
+        <v>1114</v>
+      </c>
+      <c r="H70" t="str">
         <f t="shared" si="4"/>
         <v>'11o'</v>
       </c>
-      <c r="F70" t="str">
+      <c r="I70" t="str">
         <f t="shared" si="5"/>
         <v>'DISTANT'</v>
       </c>
-      <c r="G70" t="str">
+      <c r="J70" t="str">
         <f t="shared" si="6"/>
         <v>'Have you been bothered by that problem in the PAST MONTH. Feeling distant or cut off from other people?'</v>
       </c>
-      <c r="H70" t="str">
+      <c r="K70" t="str">
         <f t="shared" si="7"/>
         <v>('11o','DISTANT','Have you been bothered by that problem in the PAST MONTH. Feeling distant or cut off from other people?'),</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>180</v>
       </c>
@@ -4334,24 +4983,33 @@
       <c r="D71" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="E71" t="str">
+      <c r="E71" s="7">
+        <v>1</v>
+      </c>
+      <c r="F71" s="7">
+        <v>1115</v>
+      </c>
+      <c r="G71" s="7">
+        <v>1115</v>
+      </c>
+      <c r="H71" t="str">
         <f t="shared" si="4"/>
         <v>'11p'</v>
       </c>
-      <c r="F71" t="str">
+      <c r="I71" t="str">
         <f t="shared" si="5"/>
         <v>'NUMB'</v>
       </c>
-      <c r="G71" t="str">
+      <c r="J71" t="str">
         <f t="shared" si="6"/>
         <v>'Have you been bothered by that problem in the PAST MONTH. Feeling emotionally numb or being unable to have loving feelings for those close to you?'</v>
       </c>
-      <c r="H71" t="str">
+      <c r="K71" t="str">
         <f t="shared" si="7"/>
         <v>('11p','NUMB','Have you been bothered by that problem in the PAST MONTH. Feeling emotionally numb or being unable to have loving feelings for those close to you?'),</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>182</v>
       </c>
@@ -4364,24 +5022,33 @@
       <c r="D72" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="E72" t="str">
+      <c r="E72" s="7">
+        <v>1</v>
+      </c>
+      <c r="F72" s="7">
+        <v>1116</v>
+      </c>
+      <c r="G72" s="7">
+        <v>1116</v>
+      </c>
+      <c r="H72" t="str">
         <f t="shared" si="4"/>
         <v>'11q'</v>
       </c>
-      <c r="F72" t="str">
+      <c r="I72" t="str">
         <f t="shared" si="5"/>
         <v>'DOOM'</v>
       </c>
-      <c r="G72" t="str">
+      <c r="J72" t="str">
         <f t="shared" si="6"/>
         <v>'Have you been bothered by that problem in the PAST MONTH. Feeling as if your future will somehow be cut short?'</v>
       </c>
-      <c r="H72" t="str">
+      <c r="K72" t="str">
         <f t="shared" si="7"/>
         <v>('11q','DOOM','Have you been bothered by that problem in the PAST MONTH. Feeling as if your future will somehow be cut short?'),</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>185</v>
       </c>
@@ -4394,24 +5061,33 @@
       <c r="D73" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="E73" t="str">
+      <c r="E73" s="7">
+        <v>1</v>
+      </c>
+      <c r="F73" s="7">
+        <v>1117</v>
+      </c>
+      <c r="G73" s="7">
+        <v>1117</v>
+      </c>
+      <c r="H73" t="str">
         <f t="shared" si="4"/>
         <v>'11r'</v>
       </c>
-      <c r="F73" t="str">
+      <c r="I73" t="str">
         <f t="shared" si="5"/>
         <v>'INSOMNIA'</v>
       </c>
-      <c r="G73" t="str">
+      <c r="J73" t="str">
         <f t="shared" si="6"/>
         <v>'Have you been bothered by that problem in the PAST MONTH. Trouble falling or staying asleep?'</v>
       </c>
-      <c r="H73" t="str">
+      <c r="K73" t="str">
         <f t="shared" si="7"/>
         <v>('11r','INSOMNIA','Have you been bothered by that problem in the PAST MONTH. Trouble falling or staying asleep?'),</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>188</v>
       </c>
@@ -4424,24 +5100,33 @@
       <c r="D74" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="E74" t="str">
+      <c r="E74" s="7">
+        <v>1</v>
+      </c>
+      <c r="F74" s="7">
+        <v>1118</v>
+      </c>
+      <c r="G74" s="7">
+        <v>1118</v>
+      </c>
+      <c r="H74" t="str">
         <f t="shared" si="4"/>
         <v>'11s'</v>
       </c>
-      <c r="F74" t="str">
+      <c r="I74" t="str">
         <f t="shared" si="5"/>
         <v>'ANGRY_OUTBURSTS'</v>
       </c>
-      <c r="G74" t="str">
+      <c r="J74" t="str">
         <f t="shared" si="6"/>
         <v>'Have you been bothered by that problem in the PAST MONTH. Feeling irritable or having angry outbursts?'</v>
       </c>
-      <c r="H74" t="str">
+      <c r="K74" t="str">
         <f t="shared" si="7"/>
         <v>('11s','ANGRY_OUTBURSTS','Have you been bothered by that problem in the PAST MONTH. Feeling irritable or having angry outbursts?'),</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>191</v>
       </c>
@@ -4454,24 +5139,33 @@
       <c r="D75" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="E75" t="str">
+      <c r="E75" s="7">
+        <v>1</v>
+      </c>
+      <c r="F75" s="7">
+        <v>1119</v>
+      </c>
+      <c r="G75" s="7">
+        <v>1119</v>
+      </c>
+      <c r="H75" t="str">
         <f t="shared" si="4"/>
         <v>'11t'</v>
       </c>
-      <c r="F75" t="str">
+      <c r="I75" t="str">
         <f t="shared" si="5"/>
         <v>'CONCENTRATE'</v>
       </c>
-      <c r="G75" t="str">
+      <c r="J75" t="str">
         <f t="shared" si="6"/>
         <v>'Have you been bothered by that problem in the PAST MONTH. Having difficulty concentrating?'</v>
       </c>
-      <c r="H75" t="str">
+      <c r="K75" t="str">
         <f t="shared" si="7"/>
         <v>('11t','CONCENTRATE','Have you been bothered by that problem in the PAST MONTH. Having difficulty concentrating?'),</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>193</v>
       </c>
@@ -4484,24 +5178,33 @@
       <c r="D76" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="E76" t="str">
+      <c r="E76" s="7">
+        <v>1</v>
+      </c>
+      <c r="F76" s="7">
+        <v>1120</v>
+      </c>
+      <c r="G76" s="7">
+        <v>1120</v>
+      </c>
+      <c r="H76" t="str">
         <f t="shared" si="4"/>
         <v>'11u'</v>
       </c>
-      <c r="F76" t="str">
+      <c r="I76" t="str">
         <f t="shared" si="5"/>
         <v>'WATCHFUL'</v>
       </c>
-      <c r="G76" t="str">
+      <c r="J76" t="str">
         <f t="shared" si="6"/>
         <v>'Have you been bothered by that problem in the PAST MONTH. Being “super alert” or watchful, on guard?'</v>
       </c>
-      <c r="H76" t="str">
+      <c r="K76" t="str">
         <f t="shared" si="7"/>
         <v>('11u','WATCHFUL','Have you been bothered by that problem in the PAST MONTH. Being “super alert” or watchful, on guard?'),</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>196</v>
       </c>
@@ -4514,24 +5217,33 @@
       <c r="D77" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="E77" t="str">
+      <c r="E77" s="7">
+        <v>1</v>
+      </c>
+      <c r="F77" s="7">
+        <v>1121</v>
+      </c>
+      <c r="G77" s="7">
+        <v>1121</v>
+      </c>
+      <c r="H77" t="str">
         <f t="shared" si="4"/>
         <v>'11v'</v>
       </c>
-      <c r="F77" t="str">
+      <c r="I77" t="str">
         <f t="shared" si="5"/>
         <v>'ALERT'</v>
       </c>
-      <c r="G77" t="str">
+      <c r="J77" t="str">
         <f t="shared" si="6"/>
         <v>'Have you been bothered by that problem in the PAST MONTH. Feeling jumpy or easily startled?'</v>
       </c>
-      <c r="H77" t="str">
+      <c r="K77" t="str">
         <f t="shared" si="7"/>
         <v>('11v','ALERT','Have you been bothered by that problem in the PAST MONTH. Feeling jumpy or easily startled?'),</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
         <v>198</v>
       </c>
@@ -4544,24 +5256,33 @@
       <c r="D78" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="E78" t="str">
+      <c r="E78" s="7">
+        <v>1</v>
+      </c>
+      <c r="F78" s="7">
+        <v>1122</v>
+      </c>
+      <c r="G78" s="7">
+        <v>1122</v>
+      </c>
+      <c r="H78" t="str">
         <f t="shared" si="4"/>
         <v>'11w'</v>
       </c>
-      <c r="F78" t="str">
+      <c r="I78" t="str">
         <f t="shared" si="5"/>
         <v>'LIFE_DIFFICULT'</v>
       </c>
-      <c r="G78" t="str">
+      <c r="J78" t="str">
         <f t="shared" si="6"/>
         <v>'How difficult have these problems (10f. through 10v.) made it for you to do your work, take care of things at home, or get along with other'</v>
       </c>
-      <c r="H78" t="str">
+      <c r="K78" t="str">
         <f t="shared" si="7"/>
         <v>('11w','LIFE_DIFFICULT','How difficult have these problems (10f. through 10v.) made it for you to do your work, take care of things at home, or get along with other'),</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
         <v>201</v>
       </c>
@@ -4574,24 +5295,33 @@
       <c r="D79" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="E79" t="str">
+      <c r="E79" s="7">
+        <v>1</v>
+      </c>
+      <c r="F79" s="7">
+        <v>1123</v>
+      </c>
+      <c r="G79" s="7">
+        <v>1123</v>
+      </c>
+      <c r="H79" t="str">
         <f t="shared" si="4"/>
         <v>'12a'</v>
       </c>
-      <c r="F79" t="str">
+      <c r="I79" t="str">
         <f t="shared" si="5"/>
         <v>'WEEKS_LITTLE_INTEREST'</v>
       </c>
-      <c r="G79" t="str">
+      <c r="J79" t="str">
         <f t="shared" si="6"/>
         <v>'Over the LAST 2 WEEKS, how often have you been bothered by the following problems? Little interest or pleasure in doing things'</v>
       </c>
-      <c r="H79" t="str">
+      <c r="K79" t="str">
         <f t="shared" si="7"/>
         <v>('12a','WEEKS_LITTLE_INTEREST','Over the LAST 2 WEEKS, how often have you been bothered by the following problems? Little interest or pleasure in doing things'),</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
         <v>204</v>
       </c>
@@ -4604,24 +5334,33 @@
       <c r="D80" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="E80" t="str">
+      <c r="E80" s="7">
+        <v>1</v>
+      </c>
+      <c r="F80" s="7">
+        <v>1124</v>
+      </c>
+      <c r="G80" s="7">
+        <v>1124</v>
+      </c>
+      <c r="H80" t="str">
         <f t="shared" si="4"/>
         <v>'12b'</v>
       </c>
-      <c r="F80" t="str">
+      <c r="I80" t="str">
         <f t="shared" si="5"/>
         <v>'WEEKS_DEPRESSED'</v>
       </c>
-      <c r="G80" t="str">
+      <c r="J80" t="str">
         <f t="shared" si="6"/>
         <v>'Over the LAST 2 WEEKS, how often have you been bothered by the following problems? Feeling down, depressed, or hopeless'</v>
       </c>
-      <c r="H80" t="str">
+      <c r="K80" t="str">
         <f t="shared" si="7"/>
         <v>('12b','WEEKS_DEPRESSED','Over the LAST 2 WEEKS, how often have you been bothered by the following problems? Feeling down, depressed, or hopeless'),</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
         <v>207</v>
       </c>
@@ -4634,24 +5373,33 @@
       <c r="D81" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="E81" t="str">
+      <c r="E81" s="7">
+        <v>1</v>
+      </c>
+      <c r="F81" s="7">
+        <v>1125</v>
+      </c>
+      <c r="G81" s="7">
+        <v>1125</v>
+      </c>
+      <c r="H81" t="str">
         <f t="shared" si="4"/>
         <v>'12c'</v>
       </c>
-      <c r="F81" t="str">
+      <c r="I81" t="str">
         <f t="shared" si="5"/>
         <v>'WEEKS_SLEEP'</v>
       </c>
-      <c r="G81" t="str">
+      <c r="J81" t="str">
         <f t="shared" si="6"/>
         <v>'Over the LAST 2 WEEKS, how often have you been bothered by the following problems? Trouble falling/staying asleep, sleep too much.'</v>
       </c>
-      <c r="H81" t="str">
+      <c r="K81" t="str">
         <f t="shared" si="7"/>
         <v>('12c','WEEKS_SLEEP','Over the LAST 2 WEEKS, how often have you been bothered by the following problems? Trouble falling/staying asleep, sleep too much.'),</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>210</v>
       </c>
@@ -4664,24 +5412,33 @@
       <c r="D82" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="E82" t="str">
+      <c r="E82" s="7">
+        <v>1</v>
+      </c>
+      <c r="F82" s="7">
+        <v>1126</v>
+      </c>
+      <c r="G82" s="7">
+        <v>1126</v>
+      </c>
+      <c r="H82" t="str">
         <f t="shared" si="4"/>
         <v>'12d'</v>
       </c>
-      <c r="F82" t="str">
+      <c r="I82" t="str">
         <f t="shared" si="5"/>
         <v>'WEEKS_TIRED'</v>
       </c>
-      <c r="G82" t="str">
+      <c r="J82" t="str">
         <f t="shared" si="6"/>
         <v>'Over the LAST 2 WEEKS, how often have you been bothered by the following problems? Feeling tired or having little energy'</v>
       </c>
-      <c r="H82" t="str">
+      <c r="K82" t="str">
         <f t="shared" si="7"/>
         <v>('12d','WEEKS_TIRED','Over the LAST 2 WEEKS, how often have you been bothered by the following problems? Feeling tired or having little energy'),</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>213</v>
       </c>
@@ -4694,24 +5451,33 @@
       <c r="D83" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="E83" t="str">
+      <c r="E83" s="7">
+        <v>1</v>
+      </c>
+      <c r="F83" s="7">
+        <v>1127</v>
+      </c>
+      <c r="G83" s="7">
+        <v>1127</v>
+      </c>
+      <c r="H83" t="str">
         <f t="shared" si="4"/>
         <v>'12e'</v>
       </c>
-      <c r="F83" t="str">
+      <c r="I83" t="str">
         <f t="shared" si="5"/>
         <v>'WEEKS_APPETITE'</v>
       </c>
-      <c r="G83" t="str">
+      <c r="J83" t="str">
         <f t="shared" si="6"/>
         <v>'Over the LAST 2 WEEKS, how often have you been bothered by the following problems? Poor appetite or overeating.'</v>
       </c>
-      <c r="H83" t="str">
+      <c r="K83" t="str">
         <f t="shared" si="7"/>
         <v>('12e','WEEKS_APPETITE','Over the LAST 2 WEEKS, how often have you been bothered by the following problems? Poor appetite or overeating.'),</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>216</v>
       </c>
@@ -4724,24 +5490,33 @@
       <c r="D84" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="E84" t="str">
+      <c r="E84" s="7">
+        <v>1</v>
+      </c>
+      <c r="F84" s="7">
+        <v>1128</v>
+      </c>
+      <c r="G84" s="7">
+        <v>1128</v>
+      </c>
+      <c r="H84" t="str">
         <f t="shared" si="4"/>
         <v>'12f'</v>
       </c>
-      <c r="F84" t="str">
+      <c r="I84" t="str">
         <f t="shared" si="5"/>
         <v>'WEEKS_FAILURE'</v>
       </c>
-      <c r="G84" t="str">
+      <c r="J84" t="str">
         <f t="shared" si="6"/>
         <v>'Over the LAST 2 WEEKS, how often have you been bothered by the following problems? Feeling bad about yourself – or that you are a failure or have let yourself or your family down.'</v>
       </c>
-      <c r="H84" t="str">
+      <c r="K84" t="str">
         <f t="shared" si="7"/>
         <v>('12f','WEEKS_FAILURE','Over the LAST 2 WEEKS, how often have you been bothered by the following problems? Feeling bad about yourself – or that you are a failure or have let yourself or your family down.'),</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>219</v>
       </c>
@@ -4754,24 +5529,33 @@
       <c r="D85" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="E85" t="str">
+      <c r="E85" s="7">
+        <v>1</v>
+      </c>
+      <c r="F85" s="7">
+        <v>1129</v>
+      </c>
+      <c r="G85" s="7">
+        <v>1129</v>
+      </c>
+      <c r="H85" t="str">
         <f t="shared" si="4"/>
         <v>'12g'</v>
       </c>
-      <c r="F85" t="str">
+      <c r="I85" t="str">
         <f t="shared" si="5"/>
         <v>'WEEKS_CONCENTRATE'</v>
       </c>
-      <c r="G85" t="str">
+      <c r="J85" t="str">
         <f t="shared" si="6"/>
         <v>'Over the LAST 2 WEEKS, how often have you been bothered by the following problems? Trouble concentrating on things, such as reading the newspaper or watching television.'</v>
       </c>
-      <c r="H85" t="str">
+      <c r="K85" t="str">
         <f t="shared" si="7"/>
         <v>('12g','WEEKS_CONCENTRATE','Over the LAST 2 WEEKS, how often have you been bothered by the following problems? Trouble concentrating on things, such as reading the newspaper or watching television.'),</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>222</v>
       </c>
@@ -4784,24 +5568,33 @@
       <c r="D86" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="E86" t="str">
+      <c r="E86" s="7">
+        <v>1</v>
+      </c>
+      <c r="F86" s="7">
+        <v>1130</v>
+      </c>
+      <c r="G86" s="7">
+        <v>1130</v>
+      </c>
+      <c r="H86" t="str">
         <f t="shared" si="4"/>
         <v>'12h'</v>
       </c>
-      <c r="F86" t="str">
+      <c r="I86" t="str">
         <f t="shared" si="5"/>
         <v>'WEEKS_LETHARGIC_JUMPY'</v>
       </c>
-      <c r="G86" t="str">
+      <c r="J86" t="str">
         <f t="shared" si="6"/>
         <v>'Over the LAST 2 WEEKS, how often have you been bothered by the following problems? Moving or speaking so slowly that other people could have noticed. Or the opposite – being so fidgety that you have been moving around a lot more than usual.'</v>
       </c>
-      <c r="H86" t="str">
+      <c r="K86" t="str">
         <f t="shared" si="7"/>
         <v>('12h','WEEKS_LETHARGIC_JUMPY','Over the LAST 2 WEEKS, how often have you been bothered by the following problems? Moving or speaking so slowly that other people could have noticed. Or the opposite – being so fidgety that you have been moving around a lot more than usual.'),</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
         <v>225</v>
       </c>
@@ -4814,24 +5607,33 @@
       <c r="D87" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="E87" t="str">
+      <c r="E87" s="7">
+        <v>1</v>
+      </c>
+      <c r="F87" s="7">
+        <v>1131</v>
+      </c>
+      <c r="G87" s="7">
+        <v>1131</v>
+      </c>
+      <c r="H87" t="str">
         <f t="shared" si="4"/>
         <v>'12i'</v>
       </c>
-      <c r="F87" t="str">
+      <c r="I87" t="str">
         <f t="shared" si="5"/>
         <v>'WEEKS_PROBLEMS'</v>
       </c>
-      <c r="G87" t="str">
+      <c r="J87" t="str">
         <f t="shared" si="6"/>
         <v>'How difficult have these problems (12a.through12h.) made it for you to do your work, take care of things at home, or get along with other people?'</v>
       </c>
-      <c r="H87" t="str">
+      <c r="K87" t="str">
         <f t="shared" si="7"/>
         <v>('12i','WEEKS_PROBLEMS','How difficult have these problems (12a.through12h.) made it for you to do your work, take care of things at home, or get along with other people?'),</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
         <v>227</v>
       </c>
@@ -4844,24 +5646,33 @@
       <c r="D88" s="3" t="s">
         <v>558</v>
       </c>
-      <c r="E88" t="str">
+      <c r="E88" s="7">
+        <v>1</v>
+      </c>
+      <c r="F88" s="7">
+        <v>1132</v>
+      </c>
+      <c r="G88" s="7">
+        <v>1132</v>
+      </c>
+      <c r="H88" t="str">
         <f t="shared" si="4"/>
         <v>'13a'</v>
       </c>
-      <c r="F88" t="str">
+      <c r="I88" t="str">
         <f t="shared" si="5"/>
         <v>'STRESSOR_NONE'</v>
       </c>
-      <c r="G88" t="str">
+      <c r="J88" t="str">
         <f t="shared" si="6"/>
         <v>'Over the PAST MONTH, which major life stressors, if any, have you experienced that are a cause of significant concern or make it difficult for you to do your work, take care of things at home, or get along with other people?'</v>
       </c>
-      <c r="H88" t="str">
+      <c r="K88" t="str">
         <f t="shared" si="7"/>
         <v>('13a','STRESSOR_NONE','Over the PAST MONTH, which major life stressors, if any, have you experienced that are a cause of significant concern or make it difficult for you to do your work, take care of things at home, or get along with other people?'),</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>227</v>
       </c>
@@ -4874,24 +5685,33 @@
       <c r="D89" s="3" t="s">
         <v>559</v>
       </c>
-      <c r="E89" t="str">
+      <c r="E89" s="7">
+        <v>1</v>
+      </c>
+      <c r="F89" s="7">
+        <v>1133</v>
+      </c>
+      <c r="G89" s="7">
+        <v>1133</v>
+      </c>
+      <c r="H89" t="str">
         <f t="shared" si="4"/>
         <v>'13a'</v>
       </c>
-      <c r="F89" t="str">
+      <c r="I89" t="str">
         <f t="shared" si="5"/>
         <v>'STRESSOR_LEGAL'</v>
       </c>
-      <c r="G89" t="str">
+      <c r="J89" t="str">
         <f t="shared" si="6"/>
         <v>'Legal'</v>
       </c>
-      <c r="H89" t="str">
+      <c r="K89" t="str">
         <f t="shared" si="7"/>
         <v>('13a','STRESSOR_LEGAL','Legal'),</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
         <v>227</v>
       </c>
@@ -4904,24 +5724,33 @@
       <c r="D90" s="3" t="s">
         <v>559</v>
       </c>
-      <c r="E90" t="str">
+      <c r="E90" s="7">
+        <v>1</v>
+      </c>
+      <c r="F90" s="7">
+        <v>1134</v>
+      </c>
+      <c r="G90" s="7">
+        <v>1134</v>
+      </c>
+      <c r="H90" t="str">
         <f t="shared" si="4"/>
         <v>'13a'</v>
       </c>
-      <c r="F90" t="str">
+      <c r="I90" t="str">
         <f t="shared" si="5"/>
         <v>'STRESSOR_MONEY'</v>
       </c>
-      <c r="G90" t="str">
+      <c r="J90" t="str">
         <f t="shared" si="6"/>
         <v>'Financial'</v>
       </c>
-      <c r="H90" t="str">
+      <c r="K90" t="str">
         <f t="shared" si="7"/>
         <v>('13a','STRESSOR_MONEY','Financial'),</v>
       </c>
     </row>
-    <row r="91" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
         <v>227</v>
       </c>
@@ -4934,24 +5763,33 @@
       <c r="D91" s="3" t="s">
         <v>559</v>
       </c>
-      <c r="E91" t="str">
+      <c r="E91" s="7">
+        <v>1</v>
+      </c>
+      <c r="F91" s="7">
+        <v>1135</v>
+      </c>
+      <c r="G91" s="7">
+        <v>1135</v>
+      </c>
+      <c r="H91" t="str">
         <f t="shared" si="4"/>
         <v>'13a'</v>
       </c>
-      <c r="F91" t="str">
+      <c r="I91" t="str">
         <f t="shared" si="5"/>
         <v>'STRESSOR_SPIRIT'</v>
       </c>
-      <c r="G91" t="str">
+      <c r="J91" t="str">
         <f t="shared" si="6"/>
         <v>'Spiritual'</v>
       </c>
-      <c r="H91" t="str">
+      <c r="K91" t="str">
         <f t="shared" si="7"/>
         <v>('13a','STRESSOR_SPIRIT','Spiritual'),</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
         <v>227</v>
       </c>
@@ -4964,24 +5802,33 @@
       <c r="D92" s="3" t="s">
         <v>559</v>
       </c>
-      <c r="E92" t="str">
+      <c r="E92" s="7">
+        <v>1</v>
+      </c>
+      <c r="F92" s="7">
+        <v>1136</v>
+      </c>
+      <c r="G92" s="7">
+        <v>1136</v>
+      </c>
+      <c r="H92" t="str">
         <f t="shared" si="4"/>
         <v>'13a'</v>
       </c>
-      <c r="F92" t="str">
+      <c r="I92" t="str">
         <f t="shared" si="5"/>
         <v>'STRESSOR_SUB'</v>
       </c>
-      <c r="G92" t="str">
+      <c r="J92" t="str">
         <f t="shared" si="6"/>
         <v>'Substance abuse (including alcohol)'</v>
       </c>
-      <c r="H92" t="str">
+      <c r="K92" t="str">
         <f t="shared" si="7"/>
         <v>('13a','STRESSOR_SUB','Substance abuse (including alcohol)'),</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
         <v>227</v>
       </c>
@@ -4994,24 +5841,33 @@
       <c r="D93" s="3" t="s">
         <v>559</v>
       </c>
-      <c r="E93" t="str">
+      <c r="E93" s="7">
+        <v>1</v>
+      </c>
+      <c r="F93" s="7">
+        <v>1137</v>
+      </c>
+      <c r="G93" s="7">
+        <v>1137</v>
+      </c>
+      <c r="H93" t="str">
         <f t="shared" si="4"/>
         <v>'13a'</v>
       </c>
-      <c r="F93" t="str">
+      <c r="I93" t="str">
         <f t="shared" si="5"/>
         <v>'STRESSOR_FAM'</v>
       </c>
-      <c r="G93" t="str">
+      <c r="J93" t="str">
         <f t="shared" si="6"/>
         <v>'Family/relationship'</v>
       </c>
-      <c r="H93" t="str">
+      <c r="K93" t="str">
         <f t="shared" si="7"/>
         <v>('13a','STRESSOR_FAM','Family/relationship'),</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
         <v>227</v>
       </c>
@@ -5024,24 +5880,33 @@
       <c r="D94" s="3" t="s">
         <v>559</v>
       </c>
-      <c r="E94" t="str">
+      <c r="E94" s="7">
+        <v>1</v>
+      </c>
+      <c r="F94" s="7">
+        <v>1138</v>
+      </c>
+      <c r="G94" s="7">
+        <v>1138</v>
+      </c>
+      <c r="H94" t="str">
         <f t="shared" si="4"/>
         <v>'13a'</v>
       </c>
-      <c r="F94" t="str">
+      <c r="I94" t="str">
         <f t="shared" si="5"/>
         <v>'STRESSOR_WORK'</v>
       </c>
-      <c r="G94" t="str">
+      <c r="J94" t="str">
         <f t="shared" si="6"/>
         <v>'Employment'</v>
       </c>
-      <c r="H94" t="str">
+      <c r="K94" t="str">
         <f t="shared" si="7"/>
         <v>('13a','STRESSOR_WORK','Employment'),</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
         <v>227</v>
       </c>
@@ -5054,24 +5919,33 @@
       <c r="D95" s="3" t="s">
         <v>559</v>
       </c>
-      <c r="E95" t="str">
+      <c r="E95" s="7">
+        <v>1</v>
+      </c>
+      <c r="F95" s="7">
+        <v>1139</v>
+      </c>
+      <c r="G95" s="7">
+        <v>1139</v>
+      </c>
+      <c r="H95" t="str">
         <f t="shared" si="4"/>
         <v>'13a'</v>
       </c>
-      <c r="F95" t="str">
+      <c r="I95" t="str">
         <f t="shared" si="5"/>
         <v>'STRESSOR_SLEEP'</v>
       </c>
-      <c r="G95" t="str">
+      <c r="J95" t="str">
         <f t="shared" si="6"/>
         <v>'Sleep'</v>
       </c>
-      <c r="H95" t="str">
+      <c r="K95" t="str">
         <f t="shared" si="7"/>
         <v>('13a','STRESSOR_SLEEP','Sleep'),</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
         <v>227</v>
       </c>
@@ -5084,24 +5958,33 @@
       <c r="D96" s="3" t="s">
         <v>559</v>
       </c>
-      <c r="E96" t="str">
+      <c r="E96" s="7">
+        <v>1</v>
+      </c>
+      <c r="F96" s="7">
+        <v>1140</v>
+      </c>
+      <c r="G96" s="7">
+        <v>1140</v>
+      </c>
+      <c r="H96" t="str">
         <f t="shared" si="4"/>
         <v>'13a'</v>
       </c>
-      <c r="F96" t="str">
+      <c r="I96" t="str">
         <f t="shared" si="5"/>
         <v>'STRESSOR_MH'</v>
       </c>
-      <c r="G96" t="str">
+      <c r="J96" t="str">
         <f t="shared" si="6"/>
         <v>'Behavioral health'</v>
       </c>
-      <c r="H96" t="str">
+      <c r="K96" t="str">
         <f t="shared" si="7"/>
         <v>('13a','STRESSOR_MH','Behavioral health'),</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
         <v>227</v>
       </c>
@@ -5114,24 +5997,33 @@
       <c r="D97" s="3" t="s">
         <v>559</v>
       </c>
-      <c r="E97" t="str">
+      <c r="E97" s="7">
+        <v>1</v>
+      </c>
+      <c r="F97" s="7">
+        <v>1141</v>
+      </c>
+      <c r="G97" s="7">
+        <v>1141</v>
+      </c>
+      <c r="H97" t="str">
         <f t="shared" si="4"/>
         <v>'13a'</v>
       </c>
-      <c r="F97" t="str">
+      <c r="I97" t="str">
         <f t="shared" si="5"/>
         <v>'STRESSOR_OTH'</v>
       </c>
-      <c r="G97" t="str">
+      <c r="J97" t="str">
         <f t="shared" si="6"/>
         <v>'Other'</v>
       </c>
-      <c r="H97" t="str">
+      <c r="K97" t="str">
         <f t="shared" si="7"/>
         <v>('13a','STRESSOR_OTH','Other'),</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
         <v>227</v>
       </c>
@@ -5144,24 +6036,33 @@
       <c r="D98" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E98" t="str">
+      <c r="E98" s="7">
+        <v>100</v>
+      </c>
+      <c r="F98" s="7">
+        <v>1142</v>
+      </c>
+      <c r="G98" s="7">
+        <v>1241</v>
+      </c>
+      <c r="H98" t="str">
         <f t="shared" si="4"/>
         <v>'13a'</v>
       </c>
-      <c r="F98" t="str">
+      <c r="I98" t="str">
         <f t="shared" si="5"/>
         <v>'STRESSORS_TEXT'</v>
       </c>
-      <c r="G98" t="str">
+      <c r="J98" t="str">
         <f t="shared" si="6"/>
         <v>'Please list and explain'</v>
       </c>
-      <c r="H98" t="str">
+      <c r="K98" t="str">
         <f t="shared" si="7"/>
         <v>('13a','STRESSORS_TEXT','Please list and explain'),</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
         <v>250</v>
       </c>
@@ -5174,24 +6075,33 @@
       <c r="D99" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E99" t="str">
+      <c r="E99" s="7">
+        <v>1</v>
+      </c>
+      <c r="F99" s="7">
+        <v>1242</v>
+      </c>
+      <c r="G99" s="7">
+        <v>1242</v>
+      </c>
+      <c r="H99" t="str">
         <f t="shared" si="4"/>
         <v>'13b'</v>
       </c>
-      <c r="F99" t="str">
+      <c r="I99" t="str">
         <f t="shared" si="5"/>
         <v>'STRESSORS_HELP'</v>
       </c>
-      <c r="G99" t="str">
+      <c r="J99" t="str">
         <f t="shared" si="6"/>
         <v>'Are you currently in treatment or getting professional help for this concern?'</v>
       </c>
-      <c r="H99" t="str">
+      <c r="K99" t="str">
         <f t="shared" si="7"/>
         <v>('13b','STRESSORS_HELP','Are you currently in treatment or getting professional help for this concern?'),</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
         <v>14</v>
       </c>
@@ -5204,24 +6114,33 @@
       <c r="D100" s="3" t="s">
         <v>560</v>
       </c>
-      <c r="E100" t="str">
+      <c r="E100" s="7">
+        <v>1</v>
+      </c>
+      <c r="F100" s="7">
+        <v>1243</v>
+      </c>
+      <c r="G100" s="7">
+        <v>1243</v>
+      </c>
+      <c r="H100" t="str">
         <f t="shared" si="4"/>
         <v>'14'</v>
       </c>
-      <c r="F100" t="str">
+      <c r="I100" t="str">
         <f t="shared" si="5"/>
         <v>'CONCERN_OTHER'</v>
       </c>
-      <c r="G100" t="str">
+      <c r="J100" t="str">
         <f t="shared" si="6"/>
         <v>'Are you concerned about any other health condition(s) or health risk exposures not already addressed?'</v>
       </c>
-      <c r="H100" t="str">
+      <c r="K100" t="str">
         <f t="shared" si="7"/>
         <v>('14','CONCERN_OTHER','Are you concerned about any other health condition(s) or health risk exposures not already addressed?'),</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
         <v>14</v>
       </c>
@@ -5234,24 +6153,33 @@
       <c r="D101" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E101" t="str">
+      <c r="E101" s="7">
+        <v>100</v>
+      </c>
+      <c r="F101" s="7">
+        <v>1244</v>
+      </c>
+      <c r="G101" s="7">
+        <v>1343</v>
+      </c>
+      <c r="H101" t="str">
         <f t="shared" si="4"/>
         <v>'14'</v>
       </c>
-      <c r="F101" t="str">
+      <c r="I101" t="str">
         <f t="shared" si="5"/>
         <v>'CONCERN_TEXT'</v>
       </c>
-      <c r="G101" t="str">
+      <c r="J101" t="str">
         <f t="shared" si="6"/>
         <v>'Please list and explain'</v>
       </c>
-      <c r="H101" t="str">
+      <c r="K101" t="str">
         <f t="shared" si="7"/>
         <v>('14','CONCERN_TEXT','Please list and explain'),</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="2"/>
       <c r="B102" s="3" t="s">
         <v>254</v>
@@ -5262,24 +6190,33 @@
       <c r="D102" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E102" t="str">
+      <c r="E102" s="7">
+        <v>15</v>
+      </c>
+      <c r="F102" s="7">
+        <v>1344</v>
+      </c>
+      <c r="G102" s="7">
+        <v>1358</v>
+      </c>
+      <c r="H102" t="str">
         <f t="shared" si="4"/>
         <v>''</v>
       </c>
-      <c r="F102" t="str">
+      <c r="I102" t="str">
         <f t="shared" si="5"/>
         <v>'DEPLOYING_TO_PROVIDER'</v>
       </c>
-      <c r="G102" t="str">
+      <c r="J102" t="str">
         <f t="shared" si="6"/>
         <v>'Providers input'</v>
       </c>
-      <c r="H102" t="str">
+      <c r="K102" t="str">
         <f t="shared" si="7"/>
         <v>('','DEPLOYING_TO_PROVIDER','Providers input'),</v>
       </c>
     </row>
-    <row r="103" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="2"/>
       <c r="B103" s="3" t="s">
         <v>256</v>
@@ -5290,24 +6227,33 @@
       <c r="D103" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="E103" t="str">
+      <c r="E103" s="7">
+        <v>2</v>
+      </c>
+      <c r="F103" s="7">
+        <v>1359</v>
+      </c>
+      <c r="G103" s="7">
+        <v>1360</v>
+      </c>
+      <c r="H103" t="str">
         <f t="shared" si="4"/>
         <v>''</v>
       </c>
-      <c r="F103" t="str">
+      <c r="I103" t="str">
         <f t="shared" si="5"/>
         <v>'HAS_DEPLOYED_PROVIDER'</v>
       </c>
-      <c r="G103" t="str">
+      <c r="J103" t="str">
         <f t="shared" si="6"/>
         <v>'Providers input'</v>
       </c>
-      <c r="H103" t="str">
+      <c r="K103" t="str">
         <f t="shared" si="7"/>
         <v>('','HAS_DEPLOYED_PROVIDER','Providers input'),</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="2"/>
       <c r="B104" s="3" t="s">
         <v>257</v>
@@ -5318,24 +6264,33 @@
       <c r="D104" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="E104" t="str">
+      <c r="E104" s="7">
+        <v>8</v>
+      </c>
+      <c r="F104" s="7">
+        <v>1361</v>
+      </c>
+      <c r="G104" s="7">
+        <v>1368</v>
+      </c>
+      <c r="H104" t="str">
         <f t="shared" si="4"/>
         <v>''</v>
       </c>
-      <c r="F104" t="str">
+      <c r="I104" t="str">
         <f t="shared" si="5"/>
         <v>'LAST_RETURNED_PROVIDER'</v>
       </c>
-      <c r="G104" t="str">
+      <c r="J104" t="str">
         <f t="shared" si="6"/>
         <v>'Providers input'</v>
       </c>
-      <c r="H104" t="str">
+      <c r="K104" t="str">
         <f t="shared" si="7"/>
         <v>('','LAST_RETURNED_PROVIDER','Providers input'),</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
         <v>258</v>
       </c>
@@ -5348,24 +6303,33 @@
       <c r="D105" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="E105" t="str">
+      <c r="E105" s="7">
+        <v>1</v>
+      </c>
+      <c r="F105" s="7">
+        <v>1369</v>
+      </c>
+      <c r="G105" s="7">
+        <v>1369</v>
+      </c>
+      <c r="H105" t="str">
         <f t="shared" si="4"/>
         <v>'HP1'</v>
       </c>
-      <c r="F105" t="str">
+      <c r="I105" t="str">
         <f t="shared" si="5"/>
         <v>'SELF_HEALTH_FOLLOWUP'</v>
       </c>
-      <c r="G105" t="str">
+      <c r="J105" t="str">
         <f t="shared" si="6"/>
         <v>'Self health rating'</v>
       </c>
-      <c r="H105" t="str">
+      <c r="K105" t="str">
         <f t="shared" si="7"/>
         <v>('HP1','SELF_HEALTH_FOLLOWUP','Self health rating'),</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
         <v>258</v>
       </c>
@@ -5378,24 +6342,33 @@
       <c r="D106" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E106" t="str">
+      <c r="E106" s="7">
+        <v>100</v>
+      </c>
+      <c r="F106" s="7">
+        <v>1370</v>
+      </c>
+      <c r="G106" s="7">
+        <v>1469</v>
+      </c>
+      <c r="H106" t="str">
         <f t="shared" si="4"/>
         <v>'HP1'</v>
       </c>
-      <c r="F106" t="str">
+      <c r="I106" t="str">
         <f t="shared" si="5"/>
         <v>'SELF_HEALTH_DEPLOYER'</v>
       </c>
-      <c r="G106" t="str">
+      <c r="J106" t="str">
         <f t="shared" si="6"/>
         <v>'Self health rating Deployers Response'</v>
       </c>
-      <c r="H106" t="str">
+      <c r="K106" t="str">
         <f t="shared" si="7"/>
         <v>('HP1','SELF_HEALTH_DEPLOYER','Self health rating Deployers Response'),</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
         <v>258</v>
       </c>
@@ -5408,24 +6381,33 @@
       <c r="D107" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E107" t="str">
+      <c r="E107" s="7">
+        <v>100</v>
+      </c>
+      <c r="F107" s="7">
+        <v>1470</v>
+      </c>
+      <c r="G107" s="7">
+        <v>1569</v>
+      </c>
+      <c r="H107" t="str">
         <f t="shared" si="4"/>
         <v>'HP1'</v>
       </c>
-      <c r="F107" t="str">
+      <c r="I107" t="str">
         <f t="shared" si="5"/>
         <v>'SELF_HEALTH_PROVIDER'</v>
       </c>
-      <c r="G107" t="str">
+      <c r="J107" t="str">
         <f t="shared" si="6"/>
         <v>'Self health rating Providers comments'</v>
       </c>
-      <c r="H107" t="str">
+      <c r="K107" t="str">
         <f t="shared" si="7"/>
         <v>('HP1','SELF_HEALTH_PROVIDER','Self health rating Providers comments'),</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
         <v>258</v>
       </c>
@@ -5438,24 +6420,33 @@
       <c r="D108" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="E108" t="str">
+      <c r="E108" s="7">
+        <v>1</v>
+      </c>
+      <c r="F108" s="7">
+        <v>1570</v>
+      </c>
+      <c r="G108" s="7">
+        <v>1570</v>
+      </c>
+      <c r="H108" t="str">
         <f t="shared" si="4"/>
         <v>'HP1'</v>
       </c>
-      <c r="F108" t="str">
+      <c r="I108" t="str">
         <f t="shared" si="5"/>
         <v>'MEB_FOLLOWUP'</v>
       </c>
-      <c r="G108" t="str">
+      <c r="J108" t="str">
         <f t="shared" si="6"/>
         <v>'MEB or PEB'</v>
       </c>
-      <c r="H108" t="str">
+      <c r="K108" t="str">
         <f t="shared" si="7"/>
         <v>('HP1','MEB_FOLLOWUP','MEB or PEB'),</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
         <v>258</v>
       </c>
@@ -5468,24 +6459,33 @@
       <c r="D109" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E109" t="str">
+      <c r="E109" s="7">
+        <v>100</v>
+      </c>
+      <c r="F109" s="7">
+        <v>1571</v>
+      </c>
+      <c r="G109" s="7">
+        <v>1670</v>
+      </c>
+      <c r="H109" t="str">
         <f t="shared" si="4"/>
         <v>'HP1'</v>
       </c>
-      <c r="F109" t="str">
+      <c r="I109" t="str">
         <f t="shared" si="5"/>
         <v>'MEB_DEPLOYER'</v>
       </c>
-      <c r="G109" t="str">
+      <c r="J109" t="str">
         <f t="shared" si="6"/>
         <v>'MEB or PEB'</v>
       </c>
-      <c r="H109" t="str">
+      <c r="K109" t="str">
         <f t="shared" si="7"/>
         <v>('HP1','MEB_DEPLOYER','MEB or PEB'),</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
         <v>258</v>
       </c>
@@ -5498,24 +6498,33 @@
       <c r="D110" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E110" t="str">
+      <c r="E110" s="7">
+        <v>100</v>
+      </c>
+      <c r="F110" s="7">
+        <v>1671</v>
+      </c>
+      <c r="G110" s="7">
+        <v>1770</v>
+      </c>
+      <c r="H110" t="str">
         <f t="shared" si="4"/>
         <v>'HP1'</v>
       </c>
-      <c r="F110" t="str">
+      <c r="I110" t="str">
         <f t="shared" si="5"/>
         <v>'MEB_PROVIDER'</v>
       </c>
-      <c r="G110" t="str">
+      <c r="J110" t="str">
         <f t="shared" si="6"/>
         <v>'MEB or PEB'</v>
       </c>
-      <c r="H110" t="str">
+      <c r="K110" t="str">
         <f t="shared" si="7"/>
         <v>('HP1','MEB_PROVIDER','MEB or PEB'),</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
         <v>258</v>
       </c>
@@ -5528,24 +6537,33 @@
       <c r="D111" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="E111" t="str">
+      <c r="E111" s="7">
+        <v>1</v>
+      </c>
+      <c r="F111" s="7">
+        <v>1771</v>
+      </c>
+      <c r="G111" s="7">
+        <v>1771</v>
+      </c>
+      <c r="H111" t="str">
         <f t="shared" si="4"/>
         <v>'HP1'</v>
       </c>
-      <c r="F111" t="str">
+      <c r="I111" t="str">
         <f t="shared" si="5"/>
         <v>'MDM_FOLLOWUP'</v>
       </c>
-      <c r="G111" t="str">
+      <c r="J111" t="str">
         <f t="shared" si="6"/>
         <v>'Medical, dental, or mental health concern'</v>
       </c>
-      <c r="H111" t="str">
+      <c r="K111" t="str">
         <f t="shared" si="7"/>
         <v>('HP1','MDM_FOLLOWUP','Medical, dental, or mental health concern'),</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
         <v>258</v>
       </c>
@@ -5558,24 +6576,33 @@
       <c r="D112" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E112" t="str">
+      <c r="E112" s="7">
+        <v>100</v>
+      </c>
+      <c r="F112" s="7">
+        <v>1772</v>
+      </c>
+      <c r="G112" s="7">
+        <v>1871</v>
+      </c>
+      <c r="H112" t="str">
         <f t="shared" si="4"/>
         <v>'HP1'</v>
       </c>
-      <c r="F112" t="str">
+      <c r="I112" t="str">
         <f t="shared" si="5"/>
         <v>'MDM_DEPLOYER'</v>
       </c>
-      <c r="G112" t="str">
+      <c r="J112" t="str">
         <f t="shared" si="6"/>
         <v>'Medical, dental, or mental health concern'</v>
       </c>
-      <c r="H112" t="str">
+      <c r="K112" t="str">
         <f t="shared" si="7"/>
         <v>('HP1','MDM_DEPLOYER','Medical, dental, or mental health concern'),</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
         <v>258</v>
       </c>
@@ -5588,24 +6615,33 @@
       <c r="D113" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E113" t="str">
+      <c r="E113" s="7">
+        <v>100</v>
+      </c>
+      <c r="F113" s="7">
+        <v>1872</v>
+      </c>
+      <c r="G113" s="7">
+        <v>1971</v>
+      </c>
+      <c r="H113" t="str">
         <f t="shared" si="4"/>
         <v>'HP1'</v>
       </c>
-      <c r="F113" t="str">
+      <c r="I113" t="str">
         <f t="shared" si="5"/>
         <v>'MDM_PROVIDER'</v>
       </c>
-      <c r="G113" t="str">
+      <c r="J113" t="str">
         <f t="shared" si="6"/>
         <v>'Medical, dental, or mental health concern'</v>
       </c>
-      <c r="H113" t="str">
+      <c r="K113" t="str">
         <f t="shared" si="7"/>
         <v>('HP1','MDM_PROVIDER','Medical, dental, or mental health concern'),</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
         <v>258</v>
       </c>
@@ -5618,24 +6654,33 @@
       <c r="D114" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="E114" t="str">
+      <c r="E114" s="7">
+        <v>1</v>
+      </c>
+      <c r="F114" s="7">
+        <v>1972</v>
+      </c>
+      <c r="G114" s="7">
+        <v>1972</v>
+      </c>
+      <c r="H114" t="str">
         <f t="shared" si="4"/>
         <v>'HP1'</v>
       </c>
-      <c r="F114" t="str">
+      <c r="I114" t="str">
         <f t="shared" si="5"/>
         <v>'PREGNANT_FOLLOWUP'</v>
       </c>
-      <c r="G114" t="str">
+      <c r="J114" t="str">
         <f t="shared" si="6"/>
         <v>'I am or may be pregnant'</v>
       </c>
-      <c r="H114" t="str">
+      <c r="K114" t="str">
         <f t="shared" si="7"/>
         <v>('HP1','PREGNANT_FOLLOWUP','I am or may be pregnant'),</v>
       </c>
     </row>
-    <row r="115" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
         <v>258</v>
       </c>
@@ -5648,24 +6693,33 @@
       <c r="D115" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E115" t="str">
+      <c r="E115" s="7">
+        <v>100</v>
+      </c>
+      <c r="F115" s="7">
+        <v>1973</v>
+      </c>
+      <c r="G115" s="7">
+        <v>2072</v>
+      </c>
+      <c r="H115" t="str">
         <f t="shared" si="4"/>
         <v>'HP1'</v>
       </c>
-      <c r="F115" t="str">
+      <c r="I115" t="str">
         <f t="shared" si="5"/>
         <v>'PREGNANT_DEPLOYER'</v>
       </c>
-      <c r="G115" t="str">
+      <c r="J115" t="str">
         <f t="shared" si="6"/>
         <v>'I am or may be pregnant'</v>
       </c>
-      <c r="H115" t="str">
+      <c r="K115" t="str">
         <f t="shared" si="7"/>
         <v>('HP1','PREGNANT_DEPLOYER','I am or may be pregnant'),</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
         <v>258</v>
       </c>
@@ -5678,24 +6732,33 @@
       <c r="D116" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E116" t="str">
+      <c r="E116" s="7">
+        <v>100</v>
+      </c>
+      <c r="F116" s="7">
+        <v>2073</v>
+      </c>
+      <c r="G116" s="7">
+        <v>2172</v>
+      </c>
+      <c r="H116" t="str">
         <f t="shared" si="4"/>
         <v>'HP1'</v>
       </c>
-      <c r="F116" t="str">
+      <c r="I116" t="str">
         <f t="shared" si="5"/>
         <v>'PREGNANT_PROVIDER'</v>
       </c>
-      <c r="G116" t="str">
+      <c r="J116" t="str">
         <f t="shared" si="6"/>
         <v>'I am or may be pregnant'</v>
       </c>
-      <c r="H116" t="str">
+      <c r="K116" t="str">
         <f t="shared" si="7"/>
         <v>('HP1','PREGNANT_PROVIDER','I am or may be pregnant'),</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
         <v>258</v>
       </c>
@@ -5708,24 +6771,33 @@
       <c r="D117" s="4" t="s">
         <v>562</v>
       </c>
-      <c r="E117" t="str">
+      <c r="E117" s="8">
+        <v>1</v>
+      </c>
+      <c r="F117" s="7">
+        <v>2173</v>
+      </c>
+      <c r="G117" s="7">
+        <v>2173</v>
+      </c>
+      <c r="H117" t="str">
         <f t="shared" si="4"/>
         <v>'HP1'</v>
       </c>
-      <c r="F117" t="str">
+      <c r="I117" t="str">
         <f t="shared" si="5"/>
         <v>'DELIVERED6_FOLLOWUP'</v>
       </c>
-      <c r="G117" t="str">
+      <c r="J117" t="str">
         <f t="shared" si="6"/>
         <v>'Pregnant or just delivered within the past 6-months'</v>
       </c>
-      <c r="H117" t="str">
+      <c r="K117" t="str">
         <f t="shared" si="7"/>
         <v>('HP1','DELIVERED6_FOLLOWUP','Pregnant or just delivered within the past 6-months'),</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
         <v>258</v>
       </c>
@@ -5738,24 +6810,33 @@
       <c r="D118" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="E118" t="str">
+      <c r="E118" s="8">
+        <v>100</v>
+      </c>
+      <c r="F118" s="7">
+        <v>2174</v>
+      </c>
+      <c r="G118" s="7">
+        <v>2273</v>
+      </c>
+      <c r="H118" t="str">
         <f t="shared" si="4"/>
         <v>'HP1'</v>
       </c>
-      <c r="F118" t="str">
+      <c r="I118" t="str">
         <f t="shared" si="5"/>
         <v>'DELIVERED6_DEPLOYER'</v>
       </c>
-      <c r="G118" t="str">
+      <c r="J118" t="str">
         <f t="shared" si="6"/>
         <v>'Pregnant or just delivered within the past 6-months'</v>
       </c>
-      <c r="H118" t="str">
+      <c r="K118" t="str">
         <f t="shared" si="7"/>
         <v>('HP1','DELIVERED6_DEPLOYER','Pregnant or just delivered within the past 6-months'),</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
         <v>258</v>
       </c>
@@ -5768,24 +6849,33 @@
       <c r="D119" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="E119" t="str">
+      <c r="E119" s="8">
+        <v>100</v>
+      </c>
+      <c r="F119" s="7">
+        <v>2274</v>
+      </c>
+      <c r="G119" s="7">
+        <v>2373</v>
+      </c>
+      <c r="H119" t="str">
         <f t="shared" si="4"/>
         <v>'HP1'</v>
       </c>
-      <c r="F119" t="str">
+      <c r="I119" t="str">
         <f t="shared" si="5"/>
         <v>'DELIVERED6_PROVIDER'</v>
       </c>
-      <c r="G119" t="str">
+      <c r="J119" t="str">
         <f t="shared" si="6"/>
         <v>'Pregnant or just delivered within the past 6-months'</v>
       </c>
-      <c r="H119" t="str">
+      <c r="K119" t="str">
         <f t="shared" si="7"/>
         <v>('HP1','DELIVERED6_PROVIDER','Pregnant or just delivered within the past 6-months'),</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
         <v>258</v>
       </c>
@@ -5798,24 +6888,33 @@
       <c r="D120" s="4" t="s">
         <v>562</v>
       </c>
-      <c r="E120" t="str">
+      <c r="E120" s="8">
+        <v>1</v>
+      </c>
+      <c r="F120" s="7">
+        <v>2374</v>
+      </c>
+      <c r="G120" s="7">
+        <v>2374</v>
+      </c>
+      <c r="H120" t="str">
         <f t="shared" si="4"/>
         <v>'HP1'</v>
       </c>
-      <c r="F120" t="str">
+      <c r="I120" t="str">
         <f t="shared" si="5"/>
         <v>'DELIVERED12_FOLLOWUP'</v>
       </c>
-      <c r="G120" t="str">
+      <c r="J120" t="str">
         <f t="shared" si="6"/>
         <v>'Pregnant and delivered 6 ~ 12 months ago'</v>
       </c>
-      <c r="H120" t="str">
+      <c r="K120" t="str">
         <f t="shared" si="7"/>
         <v>('HP1','DELIVERED12_FOLLOWUP','Pregnant and delivered 6 ~ 12 months ago'),</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
         <v>258</v>
       </c>
@@ -5828,24 +6927,33 @@
       <c r="D121" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="E121" t="str">
+      <c r="E121" s="8">
+        <v>100</v>
+      </c>
+      <c r="F121" s="7">
+        <v>2375</v>
+      </c>
+      <c r="G121" s="7">
+        <v>2474</v>
+      </c>
+      <c r="H121" t="str">
         <f t="shared" si="4"/>
         <v>'HP1'</v>
       </c>
-      <c r="F121" t="str">
+      <c r="I121" t="str">
         <f t="shared" si="5"/>
         <v>'DELIVERED12_DEPLOYER'</v>
       </c>
-      <c r="G121" t="str">
+      <c r="J121" t="str">
         <f t="shared" si="6"/>
         <v>'Pregnant and delivered 6 ~ 12 months ago'</v>
       </c>
-      <c r="H121" t="str">
+      <c r="K121" t="str">
         <f t="shared" si="7"/>
         <v>('HP1','DELIVERED12_DEPLOYER','Pregnant and delivered 6 ~ 12 months ago'),</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="4" t="s">
         <v>258</v>
       </c>
@@ -5858,24 +6966,33 @@
       <c r="D122" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="E122" t="str">
+      <c r="E122" s="8">
+        <v>100</v>
+      </c>
+      <c r="F122" s="7">
+        <v>2475</v>
+      </c>
+      <c r="G122" s="7">
+        <v>2574</v>
+      </c>
+      <c r="H122" t="str">
         <f t="shared" si="4"/>
         <v>'HP1'</v>
       </c>
-      <c r="F122" t="str">
+      <c r="I122" t="str">
         <f t="shared" si="5"/>
         <v>'DELIVERED12_PROVIDER'</v>
       </c>
-      <c r="G122" t="str">
+      <c r="J122" t="str">
         <f t="shared" si="6"/>
         <v>'Pregnant and delivered 6 ~ 12 months ago'</v>
       </c>
-      <c r="H122" t="str">
+      <c r="K122" t="str">
         <f t="shared" si="7"/>
         <v>('HP1','DELIVERED12_PROVIDER','Pregnant and delivered 6 ~ 12 months ago'),</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="4" t="s">
         <v>258</v>
       </c>
@@ -5888,24 +7005,33 @@
       <c r="D123" s="4" t="s">
         <v>562</v>
       </c>
-      <c r="E123" t="str">
+      <c r="E123" s="8">
+        <v>1</v>
+      </c>
+      <c r="F123" s="7">
+        <v>2575</v>
+      </c>
+      <c r="G123" s="7">
+        <v>2575</v>
+      </c>
+      <c r="H123" t="str">
         <f t="shared" si="4"/>
         <v>'HP1'</v>
       </c>
-      <c r="F123" t="str">
+      <c r="I123" t="str">
         <f t="shared" si="5"/>
         <v>'DELIVERED00_FOLLOWUP'</v>
       </c>
-      <c r="G123" t="str">
+      <c r="J123" t="str">
         <f t="shared" si="6"/>
         <v>'Not pregnant or delivered in past 12 months'</v>
       </c>
-      <c r="H123" t="str">
+      <c r="K123" t="str">
         <f t="shared" si="7"/>
         <v>('HP1','DELIVERED00_FOLLOWUP','Not pregnant or delivered in past 12 months'),</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="4" t="s">
         <v>258</v>
       </c>
@@ -5918,24 +7044,33 @@
       <c r="D124" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="E124" t="str">
+      <c r="E124" s="8">
+        <v>100</v>
+      </c>
+      <c r="F124" s="7">
+        <v>2576</v>
+      </c>
+      <c r="G124" s="7">
+        <v>2675</v>
+      </c>
+      <c r="H124" t="str">
         <f t="shared" si="4"/>
         <v>'HP1'</v>
       </c>
-      <c r="F124" t="str">
+      <c r="I124" t="str">
         <f t="shared" si="5"/>
         <v>'DELIVERED00_DEPLOYER'</v>
       </c>
-      <c r="G124" t="str">
+      <c r="J124" t="str">
         <f t="shared" si="6"/>
         <v>'Not pregnant or delivered in past 12 months'</v>
       </c>
-      <c r="H124" t="str">
+      <c r="K124" t="str">
         <f t="shared" si="7"/>
         <v>('HP1','DELIVERED00_DEPLOYER','Not pregnant or delivered in past 12 months'),</v>
       </c>
     </row>
-    <row r="125" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="4" t="s">
         <v>258</v>
       </c>
@@ -5948,24 +7083,33 @@
       <c r="D125" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="E125" t="str">
+      <c r="E125" s="8">
+        <v>100</v>
+      </c>
+      <c r="F125" s="7">
+        <v>2676</v>
+      </c>
+      <c r="G125" s="7">
+        <v>2775</v>
+      </c>
+      <c r="H125" t="str">
         <f t="shared" si="4"/>
         <v>'HP1'</v>
       </c>
-      <c r="F125" t="str">
+      <c r="I125" t="str">
         <f t="shared" si="5"/>
         <v>'DELIVERED00_PROVIDER'</v>
       </c>
-      <c r="G125" t="str">
+      <c r="J125" t="str">
         <f t="shared" si="6"/>
         <v>'Not pregnant or delivered in past 12 months'</v>
       </c>
-      <c r="H125" t="str">
+      <c r="K125" t="str">
         <f t="shared" si="7"/>
         <v>('HP1','DELIVERED00_PROVIDER','Not pregnant or delivered in past 12 months'),</v>
       </c>
     </row>
-    <row r="126" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="4" t="s">
         <v>258</v>
       </c>
@@ -5978,24 +7122,33 @@
       <c r="D126" s="4" t="s">
         <v>562</v>
       </c>
-      <c r="E126" t="str">
+      <c r="E126" s="8">
+        <v>1</v>
+      </c>
+      <c r="F126" s="7">
+        <v>2776</v>
+      </c>
+      <c r="G126" s="7">
+        <v>2776</v>
+      </c>
+      <c r="H126" t="str">
         <f t="shared" si="4"/>
         <v>'HP1'</v>
       </c>
-      <c r="F126" t="str">
+      <c r="I126" t="str">
         <f t="shared" si="5"/>
         <v>'CONTRA_COUNSEL_FOLLOWUP'</v>
       </c>
-      <c r="G126" t="str">
+      <c r="J126" t="str">
         <f t="shared" si="6"/>
         <v>'Contraceptive counseling'</v>
       </c>
-      <c r="H126" t="str">
+      <c r="K126" t="str">
         <f t="shared" si="7"/>
         <v>('HP1','CONTRA_COUNSEL_FOLLOWUP','Contraceptive counseling'),</v>
       </c>
     </row>
-    <row r="127" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="4" t="s">
         <v>258</v>
       </c>
@@ -6008,24 +7161,33 @@
       <c r="D127" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="E127" t="str">
+      <c r="E127" s="8">
+        <v>100</v>
+      </c>
+      <c r="F127" s="7">
+        <v>2777</v>
+      </c>
+      <c r="G127" s="7">
+        <v>2876</v>
+      </c>
+      <c r="H127" t="str">
         <f t="shared" si="4"/>
         <v>'HP1'</v>
       </c>
-      <c r="F127" t="str">
+      <c r="I127" t="str">
         <f t="shared" si="5"/>
         <v>'CONTRA_COUNSEL_DEPLOYER'</v>
       </c>
-      <c r="G127" t="str">
+      <c r="J127" t="str">
         <f t="shared" si="6"/>
         <v>'Contraceptive counseling'</v>
       </c>
-      <c r="H127" t="str">
+      <c r="K127" t="str">
         <f t="shared" si="7"/>
         <v>('HP1','CONTRA_COUNSEL_DEPLOYER','Contraceptive counseling'),</v>
       </c>
     </row>
-    <row r="128" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="4" t="s">
         <v>258</v>
       </c>
@@ -6038,24 +7200,33 @@
       <c r="D128" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="E128" t="str">
+      <c r="E128" s="8">
+        <v>100</v>
+      </c>
+      <c r="F128" s="7">
+        <v>2877</v>
+      </c>
+      <c r="G128" s="7">
+        <v>2976</v>
+      </c>
+      <c r="H128" t="str">
         <f t="shared" si="4"/>
         <v>'HP1'</v>
       </c>
-      <c r="F128" t="str">
+      <c r="I128" t="str">
         <f t="shared" si="5"/>
         <v>'CONTRA_COUNSEL_PROVIDER'</v>
       </c>
-      <c r="G128" t="str">
+      <c r="J128" t="str">
         <f t="shared" si="6"/>
         <v>'Contraceptive counseling'</v>
       </c>
-      <c r="H128" t="str">
+      <c r="K128" t="str">
         <f t="shared" si="7"/>
         <v>('HP1','CONTRA_COUNSEL_PROVIDER','Contraceptive counseling'),</v>
       </c>
     </row>
-    <row r="129" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
         <v>258</v>
       </c>
@@ -6068,24 +7239,33 @@
       <c r="D129" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="E129" t="str">
+      <c r="E129" s="7">
+        <v>1</v>
+      </c>
+      <c r="F129" s="7">
+        <v>2977</v>
+      </c>
+      <c r="G129" s="7">
+        <v>2977</v>
+      </c>
+      <c r="H129" t="str">
         <f t="shared" si="4"/>
         <v>'HP1'</v>
       </c>
-      <c r="F129" t="str">
+      <c r="I129" t="str">
         <f t="shared" si="5"/>
         <v>'HEAD_FOLLOWUP'</v>
       </c>
-      <c r="G129" t="str">
+      <c r="J129" t="str">
         <f t="shared" si="6"/>
         <v>'Head injury'</v>
       </c>
-      <c r="H129" t="str">
+      <c r="K129" t="str">
         <f t="shared" si="7"/>
         <v>('HP1','HEAD_FOLLOWUP','Head injury'),</v>
       </c>
     </row>
-    <row r="130" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
         <v>258</v>
       </c>
@@ -6098,24 +7278,33 @@
       <c r="D130" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E130" t="str">
+      <c r="E130" s="7">
+        <v>100</v>
+      </c>
+      <c r="F130" s="7">
+        <v>2978</v>
+      </c>
+      <c r="G130" s="7">
+        <v>3077</v>
+      </c>
+      <c r="H130" t="str">
         <f t="shared" si="4"/>
         <v>'HP1'</v>
       </c>
-      <c r="F130" t="str">
+      <c r="I130" t="str">
         <f t="shared" si="5"/>
         <v>'HEAD_DEPLOYER'</v>
       </c>
-      <c r="G130" t="str">
+      <c r="J130" t="str">
         <f t="shared" si="6"/>
         <v>'Head injury'</v>
       </c>
-      <c r="H130" t="str">
+      <c r="K130" t="str">
         <f t="shared" si="7"/>
         <v>('HP1','HEAD_DEPLOYER','Head injury'),</v>
       </c>
     </row>
-    <row r="131" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
         <v>258</v>
       </c>
@@ -6128,24 +7317,33 @@
       <c r="D131" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E131" t="str">
-        <f t="shared" ref="E131:E194" si="8">$E$1&amp;A131&amp;$E$1</f>
+      <c r="E131" s="7">
+        <v>100</v>
+      </c>
+      <c r="F131" s="7">
+        <v>3078</v>
+      </c>
+      <c r="G131" s="7">
+        <v>3177</v>
+      </c>
+      <c r="H131" t="str">
+        <f t="shared" ref="H131:H194" si="8">$H$1&amp;A131&amp;$H$1</f>
         <v>'HP1'</v>
       </c>
-      <c r="F131" t="str">
-        <f t="shared" ref="F131:F194" si="9">$E$1&amp;B131&amp;$E$1</f>
+      <c r="I131" t="str">
+        <f t="shared" ref="I131:I194" si="9">$H$1&amp;B131&amp;$H$1</f>
         <v>'HEAD_PROVIDER'</v>
       </c>
-      <c r="G131" t="str">
-        <f t="shared" ref="G131:G194" si="10">$E$1&amp;SUBSTITUTE(C131, "'", "''")&amp;$E$1</f>
+      <c r="J131" t="str">
+        <f t="shared" ref="J131:J194" si="10">$H$1&amp;SUBSTITUTE(C131, "'", "''")&amp;$H$1</f>
         <v>'Head injury'</v>
       </c>
-      <c r="H131" t="str">
-        <f t="shared" ref="H131:H194" si="11">"("&amp;E131&amp;","&amp;F131&amp;","&amp;G131&amp;"),"</f>
+      <c r="K131" t="str">
+        <f t="shared" ref="K131:K194" si="11">"("&amp;H131&amp;","&amp;I131&amp;","&amp;J131&amp;"),"</f>
         <v>('HP1','HEAD_PROVIDER','Head injury'),</v>
       </c>
     </row>
-    <row r="132" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
         <v>258</v>
       </c>
@@ -6158,24 +7356,33 @@
       <c r="D132" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="E132" t="str">
+      <c r="E132" s="7">
+        <v>1</v>
+      </c>
+      <c r="F132" s="7">
+        <v>3178</v>
+      </c>
+      <c r="G132" s="7">
+        <v>3178</v>
+      </c>
+      <c r="H132" t="str">
         <f t="shared" si="8"/>
         <v>'HP1'</v>
       </c>
-      <c r="F132" t="str">
+      <c r="I132" t="str">
         <f t="shared" si="9"/>
         <v>'MED_FOLLOWUP'</v>
       </c>
-      <c r="G132" t="str">
+      <c r="J132" t="str">
         <f t="shared" si="10"/>
         <v>'Medications'</v>
       </c>
-      <c r="H132" t="str">
+      <c r="K132" t="str">
         <f t="shared" si="11"/>
         <v>('HP1','MED_FOLLOWUP','Medications'),</v>
       </c>
     </row>
-    <row r="133" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
         <v>258</v>
       </c>
@@ -6188,24 +7395,33 @@
       <c r="D133" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E133" t="str">
+      <c r="E133" s="7">
+        <v>100</v>
+      </c>
+      <c r="F133" s="7">
+        <v>3179</v>
+      </c>
+      <c r="G133" s="7">
+        <v>3278</v>
+      </c>
+      <c r="H133" t="str">
         <f t="shared" si="8"/>
         <v>'HP1'</v>
       </c>
-      <c r="F133" t="str">
+      <c r="I133" t="str">
         <f t="shared" si="9"/>
         <v>'MED_DEPLOYER'</v>
       </c>
-      <c r="G133" t="str">
+      <c r="J133" t="str">
         <f t="shared" si="10"/>
         <v>'Medications'</v>
       </c>
-      <c r="H133" t="str">
+      <c r="K133" t="str">
         <f t="shared" si="11"/>
         <v>('HP1','MED_DEPLOYER','Medications'),</v>
       </c>
     </row>
-    <row r="134" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
         <v>258</v>
       </c>
@@ -6218,24 +7434,33 @@
       <c r="D134" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E134" t="str">
+      <c r="E134" s="7">
+        <v>100</v>
+      </c>
+      <c r="F134" s="7">
+        <v>3279</v>
+      </c>
+      <c r="G134" s="7">
+        <v>3378</v>
+      </c>
+      <c r="H134" t="str">
         <f t="shared" si="8"/>
         <v>'HP1'</v>
       </c>
-      <c r="F134" t="str">
+      <c r="I134" t="str">
         <f t="shared" si="9"/>
         <v>'MED_PROVIDER'</v>
       </c>
-      <c r="G134" t="str">
+      <c r="J134" t="str">
         <f t="shared" si="10"/>
         <v>'Medications'</v>
       </c>
-      <c r="H134" t="str">
+      <c r="K134" t="str">
         <f t="shared" si="11"/>
         <v>('HP1','MED_PROVIDER','Medications'),</v>
       </c>
     </row>
-    <row r="135" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
         <v>258</v>
       </c>
@@ -6248,24 +7473,33 @@
       <c r="D135" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="E135" t="str">
+      <c r="E135" s="7">
+        <v>1</v>
+      </c>
+      <c r="F135" s="7">
+        <v>3379</v>
+      </c>
+      <c r="G135" s="7">
+        <v>3379</v>
+      </c>
+      <c r="H135" t="str">
         <f t="shared" si="8"/>
         <v>'HP1'</v>
       </c>
-      <c r="F135" t="str">
+      <c r="I135" t="str">
         <f t="shared" si="9"/>
         <v>'HX_MH_FOLLOWUP'</v>
       </c>
-      <c r="G135" t="str">
+      <c r="J135" t="str">
         <f t="shared" si="10"/>
         <v>'History of mental Health Care'</v>
       </c>
-      <c r="H135" t="str">
+      <c r="K135" t="str">
         <f t="shared" si="11"/>
         <v>('HP1','HX_MH_FOLLOWUP','History of mental Health Care'),</v>
       </c>
     </row>
-    <row r="136" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
         <v>258</v>
       </c>
@@ -6278,24 +7512,33 @@
       <c r="D136" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E136" t="str">
+      <c r="E136" s="7">
+        <v>100</v>
+      </c>
+      <c r="F136" s="7">
+        <v>3380</v>
+      </c>
+      <c r="G136" s="7">
+        <v>3479</v>
+      </c>
+      <c r="H136" t="str">
         <f t="shared" si="8"/>
         <v>'HP1'</v>
       </c>
-      <c r="F136" t="str">
+      <c r="I136" t="str">
         <f t="shared" si="9"/>
         <v>'HX_MH_DEPLOYER'</v>
       </c>
-      <c r="G136" t="str">
+      <c r="J136" t="str">
         <f t="shared" si="10"/>
         <v>'History of mental Health Care'</v>
       </c>
-      <c r="H136" t="str">
+      <c r="K136" t="str">
         <f t="shared" si="11"/>
         <v>('HP1','HX_MH_DEPLOYER','History of mental Health Care'),</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
         <v>258</v>
       </c>
@@ -6308,24 +7551,33 @@
       <c r="D137" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E137" t="str">
+      <c r="E137" s="7">
+        <v>100</v>
+      </c>
+      <c r="F137" s="7">
+        <v>3480</v>
+      </c>
+      <c r="G137" s="7">
+        <v>3579</v>
+      </c>
+      <c r="H137" t="str">
         <f t="shared" si="8"/>
         <v>'HP1'</v>
       </c>
-      <c r="F137" t="str">
+      <c r="I137" t="str">
         <f t="shared" si="9"/>
         <v>'HX_MH_PROVIDER'</v>
       </c>
-      <c r="G137" t="str">
+      <c r="J137" t="str">
         <f t="shared" si="10"/>
         <v>'History of mental Health Care'</v>
       </c>
-      <c r="H137" t="str">
+      <c r="K137" t="str">
         <f t="shared" si="11"/>
         <v>('HP1','HX_MH_PROVIDER','History of mental Health Care'),</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
         <v>305</v>
       </c>
@@ -6338,24 +7590,33 @@
       <c r="D138" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E138" t="str">
+      <c r="E138" s="7">
+        <v>1</v>
+      </c>
+      <c r="F138" s="7">
+        <v>3580</v>
+      </c>
+      <c r="G138" s="7">
+        <v>3580</v>
+      </c>
+      <c r="H138" t="str">
         <f t="shared" si="8"/>
         <v>'HP2a'</v>
       </c>
-      <c r="F138" t="str">
+      <c r="I138" t="str">
         <f t="shared" si="9"/>
         <v>'HEARING_REPORTED'</v>
       </c>
-      <c r="G138" t="str">
+      <c r="J138" t="str">
         <f t="shared" si="10"/>
         <v>'Did deployer mark he/she bothered by noises in ears or trouble hearing'</v>
       </c>
-      <c r="H138" t="str">
+      <c r="K138" t="str">
         <f t="shared" si="11"/>
         <v>('HP2a','HEARING_REPORTED','Did deployer mark he/she bothered by noises in ears or trouble hearing'),</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
         <v>308</v>
       </c>
@@ -6368,24 +7629,33 @@
       <c r="D139" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E139" t="str">
+      <c r="E139" s="7">
+        <v>1</v>
+      </c>
+      <c r="F139" s="7">
+        <v>3581</v>
+      </c>
+      <c r="G139" s="7">
+        <v>3581</v>
+      </c>
+      <c r="H139" t="str">
         <f t="shared" si="8"/>
         <v>'HP2b'</v>
       </c>
-      <c r="F139" t="str">
+      <c r="I139" t="str">
         <f t="shared" si="9"/>
         <v>'REF_HEARING'</v>
       </c>
-      <c r="G139" t="str">
+      <c r="J139" t="str">
         <f t="shared" si="10"/>
         <v>'Is referral indicated for hearing problem'</v>
       </c>
-      <c r="H139" t="str">
+      <c r="K139" t="str">
         <f t="shared" si="11"/>
         <v>('HP2b','REF_HEARING','Is referral indicated for hearing problem'),</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
         <v>308</v>
       </c>
@@ -6398,24 +7668,33 @@
       <c r="D140" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="E140" t="str">
+      <c r="E140" s="7">
+        <v>1</v>
+      </c>
+      <c r="F140" s="7">
+        <v>3582</v>
+      </c>
+      <c r="G140" s="7">
+        <v>3582</v>
+      </c>
+      <c r="H140" t="str">
         <f t="shared" si="8"/>
         <v>'HP2b'</v>
       </c>
-      <c r="F140" t="str">
+      <c r="I140" t="str">
         <f t="shared" si="9"/>
         <v>'REF_HEARING_NEG'</v>
       </c>
-      <c r="G140" t="str">
+      <c r="J140" t="str">
         <f t="shared" si="10"/>
         <v>'Why not referred'</v>
       </c>
-      <c r="H140" t="str">
+      <c r="K140" t="str">
         <f t="shared" si="11"/>
         <v>('HP2b','REF_HEARING_NEG','Why not referred'),</v>
       </c>
     </row>
-    <row r="141" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
         <v>308</v>
       </c>
@@ -6428,24 +7707,33 @@
       <c r="D141" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E141" t="str">
+      <c r="E141" s="7">
+        <v>50</v>
+      </c>
+      <c r="F141" s="7">
+        <v>3583</v>
+      </c>
+      <c r="G141" s="7">
+        <v>3632</v>
+      </c>
+      <c r="H141" t="str">
         <f t="shared" si="8"/>
         <v>'HP2b'</v>
       </c>
-      <c r="F141" t="str">
+      <c r="I141" t="str">
         <f t="shared" si="9"/>
         <v>'REF_HEARING_TEXT'</v>
       </c>
-      <c r="G141" t="str">
+      <c r="J141" t="str">
         <f t="shared" si="10"/>
         <v>'Other reason for referral'</v>
       </c>
-      <c r="H141" t="str">
+      <c r="K141" t="str">
         <f t="shared" si="11"/>
         <v>('HP2b','REF_HEARING_TEXT','Other reason for referral'),</v>
       </c>
     </row>
-    <row r="142" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
         <v>315</v>
       </c>
@@ -6458,24 +7746,33 @@
       <c r="D142" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="E142" t="str">
+      <c r="E142" s="7">
+        <v>2</v>
+      </c>
+      <c r="F142" s="7">
+        <v>3633</v>
+      </c>
+      <c r="G142" s="7">
+        <v>3634</v>
+      </c>
+      <c r="H142" t="str">
         <f t="shared" si="8"/>
         <v>'HP3a'</v>
       </c>
-      <c r="F142" t="str">
+      <c r="I142" t="str">
         <f t="shared" si="9"/>
         <v>'AUDITC_SCREEN'</v>
       </c>
-      <c r="G142" t="str">
+      <c r="J142" t="str">
         <f t="shared" si="10"/>
         <v>'Deployer''s AUDIT-C screening score'</v>
       </c>
-      <c r="H142" t="str">
+      <c r="K142" t="str">
         <f t="shared" si="11"/>
         <v>('HP3a','AUDITC_SCREEN','Deployer''s AUDIT-C screening score'),</v>
       </c>
     </row>
-    <row r="143" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
         <v>315</v>
       </c>
@@ -6488,24 +7785,33 @@
       <c r="D143" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="E143" t="str">
+      <c r="E143" s="7">
+        <v>2</v>
+      </c>
+      <c r="F143" s="7">
+        <v>3635</v>
+      </c>
+      <c r="G143" s="7">
+        <v>3636</v>
+      </c>
+      <c r="H143" t="str">
         <f t="shared" si="8"/>
         <v>'HP3a'</v>
       </c>
-      <c r="F143" t="str">
+      <c r="I143" t="str">
         <f t="shared" si="9"/>
         <v>'ETOH_WEEK_PROVIDER'</v>
       </c>
-      <c r="G143" t="str">
+      <c r="J143" t="str">
         <f t="shared" si="10"/>
         <v>'Number of drinks per week'</v>
       </c>
-      <c r="H143" t="str">
+      <c r="K143" t="str">
         <f t="shared" si="11"/>
         <v>('HP3a','ETOH_WEEK_PROVIDER','Number of drinks per week'),</v>
       </c>
     </row>
-    <row r="144" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="3" t="s">
         <v>315</v>
       </c>
@@ -6518,24 +7824,33 @@
       <c r="D144" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="E144" t="str">
+      <c r="E144" s="7">
+        <v>2</v>
+      </c>
+      <c r="F144" s="7">
+        <v>3637</v>
+      </c>
+      <c r="G144" s="7">
+        <v>3638</v>
+      </c>
+      <c r="H144" t="str">
         <f t="shared" si="8"/>
         <v>'HP3a'</v>
       </c>
-      <c r="F144" t="str">
+      <c r="I144" t="str">
         <f t="shared" si="9"/>
         <v>'ETOH_TOTAL_PROVIDER'</v>
       </c>
-      <c r="G144" t="str">
+      <c r="J144" t="str">
         <f t="shared" si="10"/>
         <v>'Number of drinks per occasion'</v>
       </c>
-      <c r="H144" t="str">
+      <c r="K144" t="str">
         <f t="shared" si="11"/>
         <v>('HP3a','ETOH_TOTAL_PROVIDER','Number of drinks per occasion'),</v>
       </c>
     </row>
-    <row r="145" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
         <v>321</v>
       </c>
@@ -6548,24 +7863,33 @@
       <c r="D145" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E145" t="str">
+      <c r="E145" s="7">
+        <v>1</v>
+      </c>
+      <c r="F145" s="7">
+        <v>3639</v>
+      </c>
+      <c r="G145" s="7">
+        <v>3639</v>
+      </c>
+      <c r="H145" t="str">
         <f t="shared" si="8"/>
         <v>'HP3b'</v>
       </c>
-      <c r="F145" t="str">
+      <c r="I145" t="str">
         <f t="shared" si="9"/>
         <v>'REF_ETOH'</v>
       </c>
-      <c r="G145" t="str">
+      <c r="J145" t="str">
         <f t="shared" si="10"/>
         <v>'Referral indicated for evaluation ETOH'</v>
       </c>
-      <c r="H145" t="str">
+      <c r="K145" t="str">
         <f t="shared" si="11"/>
         <v>('HP3b','REF_ETOH','Referral indicated for evaluation ETOH'),</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
         <v>321</v>
       </c>
@@ -6578,24 +7902,33 @@
       <c r="D146" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="E146" t="str">
+      <c r="E146" s="7">
+        <v>1</v>
+      </c>
+      <c r="F146" s="7">
+        <v>3640</v>
+      </c>
+      <c r="G146" s="7">
+        <v>3640</v>
+      </c>
+      <c r="H146" t="str">
         <f t="shared" si="8"/>
         <v>'HP3b'</v>
       </c>
-      <c r="F146" t="str">
+      <c r="I146" t="str">
         <f t="shared" si="9"/>
         <v>'REF_ETOH_NEG'</v>
       </c>
-      <c r="G146" t="str">
+      <c r="J146" t="str">
         <f t="shared" si="10"/>
         <v>'Reason for no referral'</v>
       </c>
-      <c r="H146" t="str">
+      <c r="K146" t="str">
         <f t="shared" si="11"/>
         <v>('HP3b','REF_ETOH_NEG','Reason for no referral'),</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
         <v>321</v>
       </c>
@@ -6608,24 +7941,33 @@
       <c r="D147" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E147" t="str">
+      <c r="E147" s="7">
+        <v>50</v>
+      </c>
+      <c r="F147" s="7">
+        <v>3641</v>
+      </c>
+      <c r="G147" s="7">
+        <v>3690</v>
+      </c>
+      <c r="H147" t="str">
         <f t="shared" si="8"/>
         <v>'HP3b'</v>
       </c>
-      <c r="F147" t="str">
+      <c r="I147" t="str">
         <f t="shared" si="9"/>
         <v>'REF_ETOH_TEXT'</v>
       </c>
-      <c r="G147" t="str">
+      <c r="J147" t="str">
         <f t="shared" si="10"/>
         <v>'Other reason for referral'</v>
       </c>
-      <c r="H147" t="str">
+      <c r="K147" t="str">
         <f t="shared" si="11"/>
         <v>('HP3b','REF_ETOH_TEXT','Other reason for referral'),</v>
       </c>
     </row>
-    <row r="148" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="3" t="s">
         <v>327</v>
       </c>
@@ -6638,24 +7980,33 @@
       <c r="D148" s="3" t="s">
         <v>565</v>
       </c>
-      <c r="E148" t="str">
+      <c r="E148" s="7">
+        <v>1</v>
+      </c>
+      <c r="F148" s="7">
+        <v>3691</v>
+      </c>
+      <c r="G148" s="7">
+        <v>3691</v>
+      </c>
+      <c r="H148" t="str">
         <f t="shared" si="8"/>
         <v>'HP4a'</v>
       </c>
-      <c r="F148" t="str">
+      <c r="I148" t="str">
         <f t="shared" si="9"/>
         <v>'PTSD_REPORTED'</v>
       </c>
-      <c r="G148" t="str">
+      <c r="J148" t="str">
         <f t="shared" si="10"/>
         <v>'Did deployer mark yes on three or more of questions 10a. through 10e?'</v>
       </c>
-      <c r="H148" t="str">
+      <c r="K148" t="str">
         <f t="shared" si="11"/>
         <v>('HP4a','PTSD_REPORTED','Did deployer mark yes on three or more of questions 10a. through 10e?'),</v>
       </c>
     </row>
-    <row r="149" spans="1:8" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
         <v>330</v>
       </c>
@@ -6668,24 +8019,33 @@
       <c r="D149" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="E149" t="str">
+      <c r="E149" s="7">
+        <v>2</v>
+      </c>
+      <c r="F149" s="7">
+        <v>3692</v>
+      </c>
+      <c r="G149" s="7">
+        <v>3693</v>
+      </c>
+      <c r="H149" t="str">
         <f t="shared" si="8"/>
         <v>'HP4b'</v>
       </c>
-      <c r="F149" t="str">
+      <c r="I149" t="str">
         <f t="shared" si="9"/>
         <v>'PCLC_SCORE'</v>
       </c>
-      <c r="G149" t="str">
+      <c r="J149" t="str">
         <f t="shared" si="10"/>
         <v>'If yes, deployer’s responses to questions 10f. through 10v. resulted in a PCL-C score of and the deployer’s response to level of impairment with life events (10w.) is indicated in the table below'</v>
       </c>
-      <c r="H149" t="str">
+      <c r="K149" t="str">
         <f t="shared" si="11"/>
         <v>('HP4b','PCLC_SCORE','If yes, deployer’s responses to questions 10f. through 10v. resulted in a PCL-C score of and the deployer’s response to level of impairment with life events (10w.) is indicated in the table below'),</v>
       </c>
     </row>
-    <row r="150" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="3" t="s">
         <v>330</v>
       </c>
@@ -6698,24 +8058,33 @@
       <c r="D150" s="3" t="s">
         <v>559</v>
       </c>
-      <c r="E150" t="str">
+      <c r="E150" s="7">
+        <v>1</v>
+      </c>
+      <c r="F150" s="7">
+        <v>3694</v>
+      </c>
+      <c r="G150" s="7">
+        <v>3694</v>
+      </c>
+      <c r="H150" t="str">
         <f t="shared" si="8"/>
         <v>'HP4b'</v>
       </c>
-      <c r="F150" t="str">
+      <c r="I150" t="str">
         <f t="shared" si="9"/>
         <v>'PCLC_INCOMPLETE'</v>
       </c>
-      <c r="G150" t="str">
+      <c r="J150" t="str">
         <f t="shared" si="10"/>
         <v>'10f. through 10w. were not answered or are incomplete'</v>
       </c>
-      <c r="H150" t="str">
+      <c r="K150" t="str">
         <f t="shared" si="11"/>
         <v>('HP4b','PCLC_INCOMPLETE','10f. through 10w. were not answered or are incomplete'),</v>
       </c>
     </row>
-    <row r="151" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
         <v>330</v>
       </c>
@@ -6728,24 +8097,33 @@
       <c r="D151" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="E151" t="str">
+      <c r="E151" s="7">
+        <v>1</v>
+      </c>
+      <c r="F151" s="7">
+        <v>3695</v>
+      </c>
+      <c r="G151" s="7">
+        <v>3695</v>
+      </c>
+      <c r="H151" t="str">
         <f t="shared" si="8"/>
         <v>'HP4b'</v>
       </c>
-      <c r="F151" t="str">
+      <c r="I151" t="str">
         <f t="shared" si="9"/>
         <v>'PCLC_MATRIX'</v>
       </c>
-      <c r="G151" t="str">
+      <c r="J151" t="str">
         <f t="shared" si="10"/>
         <v>'PTSD Intervention Matrix, Self-Reported Level of Functioning'</v>
       </c>
-      <c r="H151" t="str">
+      <c r="K151" t="str">
         <f t="shared" si="11"/>
         <v>('HP4b','PCLC_MATRIX','PTSD Intervention Matrix, Self-Reported Level of Functioning'),</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
         <v>337</v>
       </c>
@@ -6758,24 +8136,33 @@
       <c r="D152" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E152" t="str">
+      <c r="E152" s="7">
+        <v>1</v>
+      </c>
+      <c r="F152" s="7">
+        <v>3696</v>
+      </c>
+      <c r="G152" s="7">
+        <v>3696</v>
+      </c>
+      <c r="H152" t="str">
         <f t="shared" si="8"/>
         <v>'HP4c'</v>
       </c>
-      <c r="F152" t="str">
+      <c r="I152" t="str">
         <f t="shared" si="9"/>
         <v>'REF_PTSD'</v>
       </c>
-      <c r="G152" t="str">
+      <c r="J152" t="str">
         <f t="shared" si="10"/>
         <v>'Referral indicated for PTSD'</v>
       </c>
-      <c r="H152" t="str">
+      <c r="K152" t="str">
         <f t="shared" si="11"/>
         <v>('HP4c','REF_PTSD','Referral indicated for PTSD'),</v>
       </c>
     </row>
-    <row r="153" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
         <v>337</v>
       </c>
@@ -6788,24 +8175,33 @@
       <c r="D153" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="E153" t="str">
+      <c r="E153" s="7">
+        <v>1</v>
+      </c>
+      <c r="F153" s="7">
+        <v>3697</v>
+      </c>
+      <c r="G153" s="7">
+        <v>3697</v>
+      </c>
+      <c r="H153" t="str">
         <f t="shared" si="8"/>
         <v>'HP4c'</v>
       </c>
-      <c r="F153" t="str">
+      <c r="I153" t="str">
         <f t="shared" si="9"/>
         <v>'REF_PTSD_NEG'</v>
       </c>
-      <c r="G153" t="str">
+      <c r="J153" t="str">
         <f t="shared" si="10"/>
         <v>'Reason for no referral'</v>
       </c>
-      <c r="H153" t="str">
+      <c r="K153" t="str">
         <f t="shared" si="11"/>
         <v>('HP4c','REF_PTSD_NEG','Reason for no referral'),</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="3" t="s">
         <v>337</v>
       </c>
@@ -6818,24 +8214,33 @@
       <c r="D154" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E154" t="str">
+      <c r="E154" s="7">
+        <v>50</v>
+      </c>
+      <c r="F154" s="7">
+        <v>3698</v>
+      </c>
+      <c r="G154" s="7">
+        <v>3747</v>
+      </c>
+      <c r="H154" t="str">
         <f t="shared" si="8"/>
         <v>'HP4c'</v>
       </c>
-      <c r="F154" t="str">
+      <c r="I154" t="str">
         <f t="shared" si="9"/>
         <v>'REF_PTSD_TEXT'</v>
       </c>
-      <c r="G154" t="str">
+      <c r="J154" t="str">
         <f t="shared" si="10"/>
         <v>'Other reason for referral'</v>
       </c>
-      <c r="H154" t="str">
+      <c r="K154" t="str">
         <f t="shared" si="11"/>
         <v>('HP4c','REF_PTSD_TEXT','Other reason for referral'),</v>
       </c>
     </row>
-    <row r="155" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
         <v>342</v>
       </c>
@@ -6848,24 +8253,33 @@
       <c r="D155" s="3" t="s">
         <v>565</v>
       </c>
-      <c r="E155" t="str">
+      <c r="E155" s="7">
+        <v>1</v>
+      </c>
+      <c r="F155" s="7">
+        <v>3748</v>
+      </c>
+      <c r="G155" s="7">
+        <v>3748</v>
+      </c>
+      <c r="H155" t="str">
         <f t="shared" si="8"/>
         <v>'HP5a'</v>
       </c>
-      <c r="F155" t="str">
+      <c r="I155" t="str">
         <f t="shared" si="9"/>
         <v>'DEPRESSION_REPORTED'</v>
       </c>
-      <c r="G155" t="str">
+      <c r="J155" t="str">
         <f t="shared" si="10"/>
         <v>'Did deployer mark “More than half the days” or “Nearly every day” on question 11a. or 11b.?'</v>
       </c>
-      <c r="H155" t="str">
+      <c r="K155" t="str">
         <f t="shared" si="11"/>
         <v>('HP5a','DEPRESSION_REPORTED','Did deployer mark “More than half the days” or “Nearly every day” on question 11a. or 11b.?'),</v>
       </c>
     </row>
-    <row r="156" spans="1:8" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="3" t="s">
         <v>345</v>
       </c>
@@ -6878,24 +8292,33 @@
       <c r="D156" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="E156" t="str">
+      <c r="E156" s="7">
+        <v>2</v>
+      </c>
+      <c r="F156" s="7">
+        <v>3749</v>
+      </c>
+      <c r="G156" s="7">
+        <v>3750</v>
+      </c>
+      <c r="H156" t="str">
         <f t="shared" si="8"/>
         <v>'HP5b'</v>
       </c>
-      <c r="F156" t="str">
+      <c r="I156" t="str">
         <f t="shared" si="9"/>
         <v>'PHQ8_SCORE'</v>
       </c>
-      <c r="G156" t="str">
+      <c r="J156" t="str">
         <f t="shared" si="10"/>
         <v>'If yes, deployer’s responses to questions 11a. through 11h. resulted in a total PHQ-8 score of and the deployer’s response to level of impairment with life events (11i.) is indicated in the table below.'</v>
       </c>
-      <c r="H156" t="str">
+      <c r="K156" t="str">
         <f t="shared" si="11"/>
         <v>('HP5b','PHQ8_SCORE','If yes, deployer’s responses to questions 11a. through 11h. resulted in a total PHQ-8 score of and the deployer’s response to level of impairment with life events (11i.) is indicated in the table below.'),</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
         <v>345</v>
       </c>
@@ -6908,24 +8331,33 @@
       <c r="D157" s="3" t="s">
         <v>559</v>
       </c>
-      <c r="E157" t="str">
+      <c r="E157" s="7">
+        <v>1</v>
+      </c>
+      <c r="F157" s="7">
+        <v>3751</v>
+      </c>
+      <c r="G157" s="7">
+        <v>3751</v>
+      </c>
+      <c r="H157" t="str">
         <f t="shared" si="8"/>
         <v>'HP5b'</v>
       </c>
-      <c r="F157" t="str">
+      <c r="I157" t="str">
         <f t="shared" si="9"/>
         <v>'PHQ8_INCOMPLETE'</v>
       </c>
-      <c r="G157" t="str">
+      <c r="J157" t="str">
         <f t="shared" si="10"/>
         <v>'11c. through 11i. were not answered or incomplete.'</v>
       </c>
-      <c r="H157" t="str">
+      <c r="K157" t="str">
         <f t="shared" si="11"/>
         <v>('HP5b','PHQ8_INCOMPLETE','11c. through 11i. were not answered or incomplete.'),</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="3" t="s">
         <v>345</v>
       </c>
@@ -6938,24 +8370,33 @@
       <c r="D158" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="E158" t="str">
+      <c r="E158" s="7">
+        <v>1</v>
+      </c>
+      <c r="F158" s="7">
+        <v>3752</v>
+      </c>
+      <c r="G158" s="7">
+        <v>3752</v>
+      </c>
+      <c r="H158" t="str">
         <f t="shared" si="8"/>
         <v>'HP5b'</v>
       </c>
-      <c r="F158" t="str">
+      <c r="I158" t="str">
         <f t="shared" si="9"/>
         <v>'PHQ8_MATRIX'</v>
       </c>
-      <c r="G158" t="str">
+      <c r="J158" t="str">
         <f t="shared" si="10"/>
         <v>'Depression Intervention Matrix, Self-Reported Level of Functioning'</v>
       </c>
-      <c r="H158" t="str">
+      <c r="K158" t="str">
         <f t="shared" si="11"/>
         <v>('HP5b','PHQ8_MATRIX','Depression Intervention Matrix, Self-Reported Level of Functioning'),</v>
       </c>
     </row>
-    <row r="159" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
         <v>352</v>
       </c>
@@ -6968,24 +8409,33 @@
       <c r="D159" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E159" t="str">
+      <c r="E159" s="7">
+        <v>1</v>
+      </c>
+      <c r="F159" s="7">
+        <v>3753</v>
+      </c>
+      <c r="G159" s="7">
+        <v>3753</v>
+      </c>
+      <c r="H159" t="str">
         <f t="shared" si="8"/>
         <v>'HP5c'</v>
       </c>
-      <c r="F159" t="str">
+      <c r="I159" t="str">
         <f t="shared" si="9"/>
         <v>'REF_DEPRESSION'</v>
       </c>
-      <c r="G159" t="str">
+      <c r="J159" t="str">
         <f t="shared" si="10"/>
         <v>'Referral for depression education'</v>
       </c>
-      <c r="H159" t="str">
+      <c r="K159" t="str">
         <f t="shared" si="11"/>
         <v>('HP5c','REF_DEPRESSION','Referral for depression education'),</v>
       </c>
     </row>
-    <row r="160" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="3" t="s">
         <v>352</v>
       </c>
@@ -6998,24 +8448,33 @@
       <c r="D160" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="E160" t="str">
+      <c r="E160" s="7">
+        <v>1</v>
+      </c>
+      <c r="F160" s="7">
+        <v>3754</v>
+      </c>
+      <c r="G160" s="7">
+        <v>3754</v>
+      </c>
+      <c r="H160" t="str">
         <f t="shared" si="8"/>
         <v>'HP5c'</v>
       </c>
-      <c r="F160" t="str">
+      <c r="I160" t="str">
         <f t="shared" si="9"/>
         <v>'REF_DEPRESSION_NEG'</v>
       </c>
-      <c r="G160" t="str">
+      <c r="J160" t="str">
         <f t="shared" si="10"/>
         <v>'Reason for no referral'</v>
       </c>
-      <c r="H160" t="str">
+      <c r="K160" t="str">
         <f t="shared" si="11"/>
         <v>('HP5c','REF_DEPRESSION_NEG','Reason for no referral'),</v>
       </c>
     </row>
-    <row r="161" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="s">
         <v>352</v>
       </c>
@@ -7028,24 +8487,33 @@
       <c r="D161" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E161" t="str">
+      <c r="E161" s="7">
+        <v>50</v>
+      </c>
+      <c r="F161" s="7">
+        <v>3755</v>
+      </c>
+      <c r="G161" s="7">
+        <v>3804</v>
+      </c>
+      <c r="H161" t="str">
         <f t="shared" si="8"/>
         <v>'HP5c'</v>
       </c>
-      <c r="F161" t="str">
+      <c r="I161" t="str">
         <f t="shared" si="9"/>
         <v>'REF_DEPRESSION_TEXT'</v>
       </c>
-      <c r="G161" t="str">
+      <c r="J161" t="str">
         <f t="shared" si="10"/>
         <v>'Other reason for referral'</v>
       </c>
-      <c r="H161" t="str">
+      <c r="K161" t="str">
         <f t="shared" si="11"/>
         <v>('HP5c','REF_DEPRESSION_TEXT','Other reason for referral'),</v>
       </c>
     </row>
-    <row r="162" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="3" t="s">
         <v>357</v>
       </c>
@@ -7058,24 +8526,33 @@
       <c r="D162" s="3" t="s">
         <v>565</v>
       </c>
-      <c r="E162" t="str">
+      <c r="E162" s="7">
+        <v>1</v>
+      </c>
+      <c r="F162" s="7">
+        <v>3805</v>
+      </c>
+      <c r="G162" s="7">
+        <v>3805</v>
+      </c>
+      <c r="H162" t="str">
         <f t="shared" si="8"/>
         <v>'HP6a'</v>
       </c>
-      <c r="F162" t="str">
+      <c r="I162" t="str">
         <f t="shared" si="9"/>
         <v>'STRESSORS_REPORTED'</v>
       </c>
-      <c r="G162" t="str">
+      <c r="J162" t="str">
         <f t="shared" si="10"/>
         <v>'Did deployer mark they have a concern or a difficulty with a major life stressor?'</v>
       </c>
-      <c r="H162" t="str">
+      <c r="K162" t="str">
         <f t="shared" si="11"/>
         <v>('HP6a','STRESSORS_REPORTED','Did deployer mark they have a concern or a difficulty with a major life stressor?'),</v>
       </c>
     </row>
-    <row r="163" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
         <v>357</v>
       </c>
@@ -7088,24 +8565,33 @@
       <c r="D163" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E163" t="str">
+      <c r="E163" s="7">
+        <v>50</v>
+      </c>
+      <c r="F163" s="7">
+        <v>3806</v>
+      </c>
+      <c r="G163" s="7">
+        <v>3855</v>
+      </c>
+      <c r="H163" t="str">
         <f t="shared" si="8"/>
         <v>'HP6a'</v>
       </c>
-      <c r="F163" t="str">
+      <c r="I163" t="str">
         <f t="shared" si="9"/>
         <v>'STRESSORS_DEPLOYERS_CONCERN'</v>
       </c>
-      <c r="G163" t="str">
+      <c r="J163" t="str">
         <f t="shared" si="10"/>
         <v>'Deployer''s Concern'</v>
       </c>
-      <c r="H163" t="str">
+      <c r="K163" t="str">
         <f t="shared" si="11"/>
         <v>('HP6a','STRESSORS_DEPLOYERS_CONCERN','Deployer''s Concern'),</v>
       </c>
     </row>
-    <row r="164" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="3" t="s">
         <v>361</v>
       </c>
@@ -7118,24 +8604,33 @@
       <c r="D164" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E164" t="str">
+      <c r="E164" s="7">
+        <v>100</v>
+      </c>
+      <c r="F164" s="7">
+        <v>3856</v>
+      </c>
+      <c r="G164" s="7">
+        <v>3955</v>
+      </c>
+      <c r="H164" t="str">
         <f t="shared" si="8"/>
         <v>'HP6b'</v>
       </c>
-      <c r="F164" t="str">
+      <c r="I164" t="str">
         <f t="shared" si="9"/>
         <v>'STRESSORS_COMMENTS'</v>
       </c>
-      <c r="G164" t="str">
+      <c r="J164" t="str">
         <f t="shared" si="10"/>
         <v>'If yes, ask additional questions to determine level of problem:'</v>
       </c>
-      <c r="H164" t="str">
+      <c r="K164" t="str">
         <f t="shared" si="11"/>
         <v>('HP6b','STRESSORS_COMMENTS','If yes, ask additional questions to determine level of problem:'),</v>
       </c>
     </row>
-    <row r="165" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="5" t="s">
         <v>363</v>
       </c>
@@ -7148,24 +8643,33 @@
       <c r="D165" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E165" t="str">
+      <c r="E165" s="7">
+        <v>1</v>
+      </c>
+      <c r="F165" s="7">
+        <v>3956</v>
+      </c>
+      <c r="G165" s="7">
+        <v>3956</v>
+      </c>
+      <c r="H165" t="str">
         <f t="shared" si="8"/>
         <v>'HP6c'</v>
       </c>
-      <c r="F165" t="str">
+      <c r="I165" t="str">
         <f t="shared" si="9"/>
         <v>'REF_STRESSORS'</v>
       </c>
-      <c r="G165" t="str">
+      <c r="J165" t="str">
         <f t="shared" si="10"/>
         <v>'Referral for STRESSORS'</v>
       </c>
-      <c r="H165" t="str">
+      <c r="K165" t="str">
         <f t="shared" si="11"/>
         <v>('HP6c','REF_STRESSORS','Referral for STRESSORS'),</v>
       </c>
     </row>
-    <row r="166" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="3" t="s">
         <v>363</v>
       </c>
@@ -7178,24 +8682,33 @@
       <c r="D166" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="E166" t="str">
+      <c r="E166" s="7">
+        <v>1</v>
+      </c>
+      <c r="F166" s="7">
+        <v>3957</v>
+      </c>
+      <c r="G166" s="7">
+        <v>3957</v>
+      </c>
+      <c r="H166" t="str">
         <f t="shared" si="8"/>
         <v>'HP6c'</v>
       </c>
-      <c r="F166" t="str">
+      <c r="I166" t="str">
         <f t="shared" si="9"/>
         <v>'REF_STRESSORS_NEG'</v>
       </c>
-      <c r="G166" t="str">
+      <c r="J166" t="str">
         <f t="shared" si="10"/>
         <v>'Reason for no referral'</v>
       </c>
-      <c r="H166" t="str">
+      <c r="K166" t="str">
         <f t="shared" si="11"/>
         <v>('HP6c','REF_STRESSORS_NEG','Reason for no referral'),</v>
       </c>
     </row>
-    <row r="167" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
         <v>363</v>
       </c>
@@ -7208,24 +8721,33 @@
       <c r="D167" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E167" t="str">
+      <c r="E167" s="7">
+        <v>50</v>
+      </c>
+      <c r="F167" s="7">
+        <v>3958</v>
+      </c>
+      <c r="G167" s="7">
+        <v>4007</v>
+      </c>
+      <c r="H167" t="str">
         <f t="shared" si="8"/>
         <v>'HP6c'</v>
       </c>
-      <c r="F167" t="str">
+      <c r="I167" t="str">
         <f t="shared" si="9"/>
         <v>'REF_STRESSORS_OTHER'</v>
       </c>
-      <c r="G167" t="str">
+      <c r="J167" t="str">
         <f t="shared" si="10"/>
         <v>'Other reason for referral'</v>
       </c>
-      <c r="H167" t="str">
+      <c r="K167" t="str">
         <f t="shared" si="11"/>
         <v>('HP6c','REF_STRESSORS_OTHER','Other reason for referral'),</v>
       </c>
     </row>
-    <row r="168" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="3" t="s">
         <v>368</v>
       </c>
@@ -7238,24 +8760,33 @@
       <c r="D168" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E168" t="str">
+      <c r="E168" s="7">
+        <v>1</v>
+      </c>
+      <c r="F168" s="7">
+        <v>4008</v>
+      </c>
+      <c r="G168" s="7">
+        <v>4008</v>
+      </c>
+      <c r="H168" t="str">
         <f t="shared" si="8"/>
         <v>'HP7a'</v>
       </c>
-      <c r="F168" t="str">
+      <c r="I168" t="str">
         <f t="shared" si="9"/>
         <v>'SUICIDE_A'</v>
       </c>
-      <c r="G168" t="str">
+      <c r="J168" t="str">
         <f t="shared" si="10"/>
         <v>'Over the PAST MONTH, have you wished you were dead or wished you could go to sleep and not wake up?'</v>
       </c>
-      <c r="H168" t="str">
+      <c r="K168" t="str">
         <f t="shared" si="11"/>
         <v>('HP7a','SUICIDE_A','Over the PAST MONTH, have you wished you were dead or wished you could go to sleep and not wake up?'),</v>
       </c>
     </row>
-    <row r="169" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
         <v>371</v>
       </c>
@@ -7268,24 +8799,33 @@
       <c r="D169" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E169" t="str">
+      <c r="E169" s="7">
+        <v>1</v>
+      </c>
+      <c r="F169" s="7">
+        <v>4009</v>
+      </c>
+      <c r="G169" s="7">
+        <v>4009</v>
+      </c>
+      <c r="H169" t="str">
         <f t="shared" si="8"/>
         <v>'HP7b'</v>
       </c>
-      <c r="F169" t="str">
+      <c r="I169" t="str">
         <f t="shared" si="9"/>
         <v>'SUICIDE_B'</v>
       </c>
-      <c r="G169" t="str">
+      <c r="J169" t="str">
         <f t="shared" si="10"/>
         <v>'Have you actually had any thoughts of killing yourself?'</v>
       </c>
-      <c r="H169" t="str">
+      <c r="K169" t="str">
         <f t="shared" si="11"/>
         <v>('HP7b','SUICIDE_B','Have you actually had any thoughts of killing yourself?'),</v>
       </c>
     </row>
-    <row r="170" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="3" t="s">
         <v>374</v>
       </c>
@@ -7298,24 +8838,33 @@
       <c r="D170" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E170" t="str">
+      <c r="E170" s="7">
+        <v>1</v>
+      </c>
+      <c r="F170" s="7">
+        <v>4010</v>
+      </c>
+      <c r="G170" s="7">
+        <v>4010</v>
+      </c>
+      <c r="H170" t="str">
         <f t="shared" si="8"/>
         <v>'HP7c'</v>
       </c>
-      <c r="F170" t="str">
+      <c r="I170" t="str">
         <f t="shared" si="9"/>
         <v>'SUICIDE_C'</v>
       </c>
-      <c r="G170" t="str">
+      <c r="J170" t="str">
         <f t="shared" si="10"/>
         <v>'Over the PAST MONTH, have you been thinking about how you might do this?'</v>
       </c>
-      <c r="H170" t="str">
+      <c r="K170" t="str">
         <f t="shared" si="11"/>
         <v>('HP7c','SUICIDE_C','Over the PAST MONTH, have you been thinking about how you might do this?'),</v>
       </c>
     </row>
-    <row r="171" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
         <v>377</v>
       </c>
@@ -7328,24 +8877,33 @@
       <c r="D171" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E171" t="str">
+      <c r="E171" s="7">
+        <v>1</v>
+      </c>
+      <c r="F171" s="7">
+        <v>4011</v>
+      </c>
+      <c r="G171" s="7">
+        <v>4011</v>
+      </c>
+      <c r="H171" t="str">
         <f t="shared" si="8"/>
         <v>'HP7d'</v>
       </c>
-      <c r="F171" t="str">
+      <c r="I171" t="str">
         <f t="shared" si="9"/>
         <v>'SUICIDE_D'</v>
       </c>
-      <c r="G171" t="str">
+      <c r="J171" t="str">
         <f t="shared" si="10"/>
         <v>'Over the PAST MONTH, have you had these thoughts and had some intention of acting on them?'</v>
       </c>
-      <c r="H171" t="str">
+      <c r="K171" t="str">
         <f t="shared" si="11"/>
         <v>('HP7d','SUICIDE_D','Over the PAST MONTH, have you had these thoughts and had some intention of acting on them?'),</v>
       </c>
     </row>
-    <row r="172" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="3" t="s">
         <v>380</v>
       </c>
@@ -7358,24 +8916,33 @@
       <c r="D172" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E172" t="str">
+      <c r="E172" s="7">
+        <v>1</v>
+      </c>
+      <c r="F172" s="7">
+        <v>4012</v>
+      </c>
+      <c r="G172" s="7">
+        <v>4012</v>
+      </c>
+      <c r="H172" t="str">
         <f t="shared" si="8"/>
         <v>'HP7e1'</v>
       </c>
-      <c r="F172" t="str">
+      <c r="I172" t="str">
         <f t="shared" si="9"/>
         <v>'SUICIDE_E1'</v>
       </c>
-      <c r="G172" t="str">
+      <c r="J172" t="str">
         <f t="shared" si="10"/>
         <v>'Over the PAST MONTH, have you started to work out or worked out the details of how to kill yourself?'</v>
       </c>
-      <c r="H172" t="str">
+      <c r="K172" t="str">
         <f t="shared" si="11"/>
         <v>('HP7e1','SUICIDE_E1','Over the PAST MONTH, have you started to work out or worked out the details of how to kill yourself?'),</v>
       </c>
     </row>
-    <row r="173" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="s">
         <v>383</v>
       </c>
@@ -7388,24 +8955,33 @@
       <c r="D173" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E173" t="str">
+      <c r="E173" s="7">
+        <v>1</v>
+      </c>
+      <c r="F173" s="7">
+        <v>4013</v>
+      </c>
+      <c r="G173" s="7">
+        <v>4013</v>
+      </c>
+      <c r="H173" t="str">
         <f t="shared" si="8"/>
         <v>'HP7e2'</v>
       </c>
-      <c r="F173" t="str">
+      <c r="I173" t="str">
         <f t="shared" si="9"/>
         <v>'SUICIDE_E2'</v>
       </c>
-      <c r="G173" t="str">
+      <c r="J173" t="str">
         <f t="shared" si="10"/>
         <v>'At any time in the PAST MONTH, did you intend to carry out this plan?'</v>
       </c>
-      <c r="H173" t="str">
+      <c r="K173" t="str">
         <f t="shared" si="11"/>
         <v>('HP7e2','SUICIDE_E2','At any time in the PAST MONTH, did you intend to carry out this plan?'),</v>
       </c>
     </row>
-    <row r="174" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="3" t="s">
         <v>386</v>
       </c>
@@ -7418,24 +8994,33 @@
       <c r="D174" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E174" t="str">
+      <c r="E174" s="7">
+        <v>1</v>
+      </c>
+      <c r="F174" s="7">
+        <v>4014</v>
+      </c>
+      <c r="G174" s="7">
+        <v>4014</v>
+      </c>
+      <c r="H174" t="str">
         <f t="shared" si="8"/>
         <v>'HP7f1'</v>
       </c>
-      <c r="F174" t="str">
+      <c r="I174" t="str">
         <f t="shared" si="9"/>
         <v>'SUICIDE_F1'</v>
       </c>
-      <c r="G174" t="str">
+      <c r="J174" t="str">
         <f t="shared" si="10"/>
         <v>'In your lifetime, have you ever done anything, started to do anything, or prepared to do anything to end your life?'</v>
       </c>
-      <c r="H174" t="str">
+      <c r="K174" t="str">
         <f t="shared" si="11"/>
         <v>('HP7f1','SUICIDE_F1','In your lifetime, have you ever done anything, started to do anything, or prepared to do anything to end your life?'),</v>
       </c>
     </row>
-    <row r="175" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="3" t="s">
         <v>389</v>
       </c>
@@ -7448,24 +9033,33 @@
       <c r="D175" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E175" t="str">
+      <c r="E175" s="7">
+        <v>1</v>
+      </c>
+      <c r="F175" s="7">
+        <v>4015</v>
+      </c>
+      <c r="G175" s="7">
+        <v>4015</v>
+      </c>
+      <c r="H175" t="str">
         <f t="shared" si="8"/>
         <v>'HP7f2'</v>
       </c>
-      <c r="F175" t="str">
+      <c r="I175" t="str">
         <f t="shared" si="9"/>
         <v>'SUICIDE_F2'</v>
       </c>
-      <c r="G175" t="str">
+      <c r="J175" t="str">
         <f t="shared" si="10"/>
         <v>'Was this within the past three months?'</v>
       </c>
-      <c r="H175" t="str">
+      <c r="K175" t="str">
         <f t="shared" si="11"/>
         <v>('HP7f2','SUICIDE_F2','Was this within the past three months?'),</v>
       </c>
     </row>
-    <row r="176" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="3" t="s">
         <v>392</v>
       </c>
@@ -7478,24 +9072,33 @@
       <c r="D176" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E176" t="str">
+      <c r="E176" s="7">
+        <v>100</v>
+      </c>
+      <c r="F176" s="7">
+        <v>4016</v>
+      </c>
+      <c r="G176" s="7">
+        <v>4115</v>
+      </c>
+      <c r="H176" t="str">
         <f t="shared" si="8"/>
         <v>'HP7g'</v>
       </c>
-      <c r="F176" t="str">
+      <c r="I176" t="str">
         <f t="shared" si="9"/>
         <v>'SUICIDE_G_TEXT'</v>
       </c>
-      <c r="G176" t="str">
+      <c r="J176" t="str">
         <f t="shared" si="10"/>
         <v>'Conduct further risk assessment'</v>
       </c>
-      <c r="H176" t="str">
+      <c r="K176" t="str">
         <f t="shared" si="11"/>
         <v>('HP7g','SUICIDE_G_TEXT','Conduct further risk assessment'),</v>
       </c>
     </row>
-    <row r="177" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="s">
         <v>395</v>
       </c>
@@ -7508,24 +9111,33 @@
       <c r="D177" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E177" t="str">
+      <c r="E177" s="7">
+        <v>1</v>
+      </c>
+      <c r="F177" s="7">
+        <v>4116</v>
+      </c>
+      <c r="G177" s="7">
+        <v>4116</v>
+      </c>
+      <c r="H177" t="str">
         <f t="shared" si="8"/>
         <v>'HP7h'</v>
       </c>
-      <c r="F177" t="str">
+      <c r="I177" t="str">
         <f t="shared" si="9"/>
         <v>'SUICIDE_RISK'</v>
       </c>
-      <c r="G177" t="str">
+      <c r="J177" t="str">
         <f t="shared" si="10"/>
         <v>'Does deployer pose a current risk for harm to self?'</v>
       </c>
-      <c r="H177" t="str">
+      <c r="K177" t="str">
         <f t="shared" si="11"/>
         <v>('HP7h','SUICIDE_RISK','Does deployer pose a current risk for harm to self?'),</v>
       </c>
     </row>
-    <row r="178" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="3" t="s">
         <v>397</v>
       </c>
@@ -7538,24 +9150,33 @@
       <c r="D178" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E178" t="str">
+      <c r="E178" s="7">
+        <v>1</v>
+      </c>
+      <c r="F178" s="7">
+        <v>4117</v>
+      </c>
+      <c r="G178" s="7">
+        <v>4117</v>
+      </c>
+      <c r="H178" t="str">
         <f t="shared" si="8"/>
         <v>'HP8a'</v>
       </c>
-      <c r="F178" t="str">
+      <c r="I178" t="str">
         <f t="shared" si="9"/>
         <v>'VIOLENCE'</v>
       </c>
-      <c r="G178" t="str">
+      <c r="J178" t="str">
         <f t="shared" si="10"/>
         <v>'Over the past month have you had thoughts or concerns that you might hurt or lose control with someone?”'</v>
       </c>
-      <c r="H178" t="str">
+      <c r="K178" t="str">
         <f t="shared" si="11"/>
         <v>('HP8a','VIOLENCE','Over the past month have you had thoughts or concerns that you might hurt or lose control with someone?”'),</v>
       </c>
     </row>
-    <row r="179" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
         <v>397</v>
       </c>
@@ -7568,24 +9189,33 @@
       <c r="D179" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E179" t="str">
+      <c r="E179" s="7">
+        <v>100</v>
+      </c>
+      <c r="F179" s="7">
+        <v>4118</v>
+      </c>
+      <c r="G179" s="7">
+        <v>4217</v>
+      </c>
+      <c r="H179" t="str">
         <f t="shared" si="8"/>
         <v>'HP8a'</v>
       </c>
-      <c r="F179" t="str">
+      <c r="I179" t="str">
         <f t="shared" si="9"/>
         <v>'VIOLENCE_TEXT'</v>
       </c>
-      <c r="G179" t="str">
+      <c r="J179" t="str">
         <f t="shared" si="10"/>
         <v>'Comments on violence/harm eval'</v>
       </c>
-      <c r="H179" t="str">
+      <c r="K179" t="str">
         <f t="shared" si="11"/>
         <v>('HP8a','VIOLENCE_TEXT','Comments on violence/harm eval'),</v>
       </c>
     </row>
-    <row r="180" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="3" t="s">
         <v>402</v>
       </c>
@@ -7598,24 +9228,33 @@
       <c r="D180" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E180" t="str">
+      <c r="E180" s="7">
+        <v>1</v>
+      </c>
+      <c r="F180" s="7">
+        <v>4218</v>
+      </c>
+      <c r="G180" s="7">
+        <v>4218</v>
+      </c>
+      <c r="H180" t="str">
         <f t="shared" si="8"/>
         <v>'HP8b'</v>
       </c>
-      <c r="F180" t="str">
+      <c r="I180" t="str">
         <f t="shared" si="9"/>
         <v>'VIOLENCE_RISK'</v>
       </c>
-      <c r="G180" t="str">
+      <c r="J180" t="str">
         <f t="shared" si="10"/>
         <v>'Does member pose a current risk to others?'</v>
       </c>
-      <c r="H180" t="str">
+      <c r="K180" t="str">
         <f t="shared" si="11"/>
         <v>('HP8b','VIOLENCE_RISK','Does member pose a current risk to others?'),</v>
       </c>
     </row>
-    <row r="181" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
         <v>402</v>
       </c>
@@ -7628,24 +9267,33 @@
       <c r="D181" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E181" t="str">
+      <c r="E181" s="7">
+        <v>100</v>
+      </c>
+      <c r="F181" s="7">
+        <v>4219</v>
+      </c>
+      <c r="G181" s="7">
+        <v>4318</v>
+      </c>
+      <c r="H181" t="str">
         <f t="shared" si="8"/>
         <v>'HP8b'</v>
       </c>
-      <c r="F181" t="str">
+      <c r="I181" t="str">
         <f t="shared" si="9"/>
         <v>'VIOLENCE_RISK_TEXT'</v>
       </c>
-      <c r="G181" t="str">
+      <c r="J181" t="str">
         <f t="shared" si="10"/>
         <v>'Explain 8B'</v>
       </c>
-      <c r="H181" t="str">
+      <c r="K181" t="str">
         <f t="shared" si="11"/>
         <v>('HP8b','VIOLENCE_RISK_TEXT','Explain 8B'),</v>
       </c>
     </row>
-    <row r="182" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="3" t="s">
         <v>406</v>
       </c>
@@ -7658,24 +9306,33 @@
       <c r="D182" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="E182" t="str">
+      <c r="E182" s="7">
+        <v>1</v>
+      </c>
+      <c r="F182" s="7">
+        <v>4319</v>
+      </c>
+      <c r="G182" s="7">
+        <v>4319</v>
+      </c>
+      <c r="H182" t="str">
         <f t="shared" si="8"/>
         <v>'HP9'</v>
       </c>
-      <c r="F182" t="str">
+      <c r="I182" t="str">
         <f t="shared" si="9"/>
         <v>'MED_HX_REV'</v>
       </c>
-      <c r="G182" t="str">
+      <c r="J182" t="str">
         <f t="shared" si="10"/>
         <v>'Medical History Review'</v>
       </c>
-      <c r="H182" t="str">
+      <c r="K182" t="str">
         <f t="shared" si="11"/>
         <v>('HP9','MED_HX_REV','Medical History Review'),</v>
       </c>
     </row>
-    <row r="183" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
         <v>409</v>
       </c>
@@ -7688,24 +9345,33 @@
       <c r="D183" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E183" t="str">
+      <c r="E183" s="7">
+        <v>250</v>
+      </c>
+      <c r="F183" s="7">
+        <v>4320</v>
+      </c>
+      <c r="G183" s="7">
+        <v>4569</v>
+      </c>
+      <c r="H183" t="str">
         <f t="shared" si="8"/>
         <v>'HP9a'</v>
       </c>
-      <c r="F183" t="str">
+      <c r="I183" t="str">
         <f t="shared" si="9"/>
         <v>'SIGNIF_FDN'</v>
       </c>
-      <c r="G183" t="str">
+      <c r="J183" t="str">
         <f t="shared" si="10"/>
         <v>'Significant findings'</v>
       </c>
-      <c r="H183" t="str">
+      <c r="K183" t="str">
         <f t="shared" si="11"/>
         <v>('HP9a','SIGNIF_FDN','Significant findings'),</v>
       </c>
     </row>
-    <row r="184" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="3" t="s">
         <v>412</v>
       </c>
@@ -7718,24 +9384,33 @@
       <c r="D184" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E184" t="str">
+      <c r="E184" s="7">
+        <v>1</v>
+      </c>
+      <c r="F184" s="7">
+        <v>4570</v>
+      </c>
+      <c r="G184" s="7">
+        <v>4570</v>
+      </c>
+      <c r="H184" t="str">
         <f t="shared" si="8"/>
         <v>'HP9b'</v>
       </c>
-      <c r="F184" t="str">
+      <c r="I184" t="str">
         <f t="shared" si="9"/>
         <v>'MED_LIMIT_DEPLOY'</v>
       </c>
-      <c r="G184" t="str">
+      <c r="J184" t="str">
         <f t="shared" si="10"/>
         <v>'Evidence of deployment limiting condition'</v>
       </c>
-      <c r="H184" t="str">
+      <c r="K184" t="str">
         <f t="shared" si="11"/>
         <v>('HP9b','MED_LIMIT_DEPLOY','Evidence of deployment limiting condition'),</v>
       </c>
     </row>
-    <row r="185" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
         <v>415</v>
       </c>
@@ -7748,24 +9423,33 @@
       <c r="D185" s="3" t="s">
         <v>559</v>
       </c>
-      <c r="E185" t="str">
+      <c r="E185" s="7">
+        <v>1</v>
+      </c>
+      <c r="F185" s="7">
+        <v>4571</v>
+      </c>
+      <c r="G185" s="7">
+        <v>4571</v>
+      </c>
+      <c r="H185" t="str">
         <f t="shared" si="8"/>
         <v>'HP10'</v>
       </c>
-      <c r="F185" t="str">
+      <c r="I185" t="str">
         <f t="shared" si="9"/>
         <v>'DEP_DEC_FORM'</v>
       </c>
-      <c r="G185" t="str">
+      <c r="J185" t="str">
         <f t="shared" si="10"/>
         <v>'Deployer declined to complete form'</v>
       </c>
-      <c r="H185" t="str">
+      <c r="K185" t="str">
         <f t="shared" si="11"/>
         <v>('HP10','DEP_DEC_FORM','Deployer declined to complete form'),</v>
       </c>
     </row>
-    <row r="186" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
         <v>415</v>
       </c>
@@ -7778,24 +9462,33 @@
       <c r="D186" s="3" t="s">
         <v>559</v>
       </c>
-      <c r="E186" t="str">
+      <c r="E186" s="7">
+        <v>1</v>
+      </c>
+      <c r="F186" s="7">
+        <v>4572</v>
+      </c>
+      <c r="G186" s="7">
+        <v>4572</v>
+      </c>
+      <c r="H186" t="str">
         <f t="shared" si="8"/>
         <v>'HP10'</v>
       </c>
-      <c r="F186" t="str">
+      <c r="I186" t="str">
         <f t="shared" si="9"/>
         <v>'DEP_DEC_ASSESS'</v>
       </c>
-      <c r="G186" t="str">
+      <c r="J186" t="str">
         <f t="shared" si="10"/>
         <v>'Deployer declined to complete interview'</v>
       </c>
-      <c r="H186" t="str">
+      <c r="K186" t="str">
         <f t="shared" si="11"/>
         <v>('HP10','DEP_DEC_ASSESS','Deployer declined to complete interview'),</v>
       </c>
     </row>
-    <row r="187" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
         <v>419</v>
       </c>
@@ -7808,24 +9501,33 @@
       <c r="D187" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="E187" t="str">
+      <c r="E187" s="7">
+        <v>1</v>
+      </c>
+      <c r="F187" s="7">
+        <v>4573</v>
+      </c>
+      <c r="G187" s="7">
+        <v>4573</v>
+      </c>
+      <c r="H187" t="str">
         <f t="shared" si="8"/>
         <v>'HP11a'</v>
       </c>
-      <c r="F187" t="str">
+      <c r="I187" t="str">
         <f t="shared" si="9"/>
         <v>'REFER_NONE'</v>
       </c>
-      <c r="G187" t="str">
+      <c r="J187" t="str">
         <f t="shared" si="10"/>
         <v>'No concerns identified'</v>
       </c>
-      <c r="H187" t="str">
+      <c r="K187" t="str">
         <f t="shared" si="11"/>
         <v>('HP11a','REFER_NONE','No concerns identified'),</v>
       </c>
     </row>
-    <row r="188" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="3" t="s">
         <v>422</v>
       </c>
@@ -7838,24 +9540,33 @@
       <c r="D188" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E188" t="str">
+      <c r="E188" s="7">
+        <v>1</v>
+      </c>
+      <c r="F188" s="7">
+        <v>4574</v>
+      </c>
+      <c r="G188" s="7">
+        <v>4574</v>
+      </c>
+      <c r="H188" t="str">
         <f t="shared" si="8"/>
         <v>'HP11b'</v>
       </c>
-      <c r="F188" t="str">
+      <c r="I188" t="str">
         <f t="shared" si="9"/>
         <v>'REFER_PH'</v>
       </c>
-      <c r="G188" t="str">
+      <c r="J188" t="str">
         <f t="shared" si="10"/>
         <v>'Concerns identified: Physical health'</v>
       </c>
-      <c r="H188" t="str">
+      <c r="K188" t="str">
         <f t="shared" si="11"/>
         <v>('HP11b','REFER_PH','Concerns identified: Physical health'),</v>
       </c>
     </row>
-    <row r="189" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
         <v>425</v>
       </c>
@@ -7868,24 +9579,33 @@
       <c r="D189" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E189" t="str">
+      <c r="E189" s="7">
+        <v>1</v>
+      </c>
+      <c r="F189" s="7">
+        <v>4575</v>
+      </c>
+      <c r="G189" s="7">
+        <v>4575</v>
+      </c>
+      <c r="H189" t="str">
         <f t="shared" si="8"/>
         <v>'HP11c'</v>
       </c>
-      <c r="F189" t="str">
+      <c r="I189" t="str">
         <f t="shared" si="9"/>
         <v>'REFER_DENTAL'</v>
       </c>
-      <c r="G189" t="str">
+      <c r="J189" t="str">
         <f t="shared" si="10"/>
         <v>'Concerns identified: Dental health'</v>
       </c>
-      <c r="H189" t="str">
+      <c r="K189" t="str">
         <f t="shared" si="11"/>
         <v>('HP11c','REFER_DENTAL','Concerns identified: Dental health'),</v>
       </c>
     </row>
-    <row r="190" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="3" t="s">
         <v>428</v>
       </c>
@@ -7898,24 +9618,33 @@
       <c r="D190" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E190" t="str">
+      <c r="E190" s="7">
+        <v>1</v>
+      </c>
+      <c r="F190" s="7">
+        <v>4576</v>
+      </c>
+      <c r="G190" s="7">
+        <v>4576</v>
+      </c>
+      <c r="H190" t="str">
         <f t="shared" si="8"/>
         <v>'HP11d'</v>
       </c>
-      <c r="F190" t="str">
+      <c r="I190" t="str">
         <f t="shared" si="9"/>
         <v>'REFER_ETOH'</v>
       </c>
-      <c r="G190" t="str">
+      <c r="J190" t="str">
         <f t="shared" si="10"/>
         <v>'Concerns identified: Alcohol use'</v>
       </c>
-      <c r="H190" t="str">
+      <c r="K190" t="str">
         <f t="shared" si="11"/>
         <v>('HP11d','REFER_ETOH','Concerns identified: Alcohol use'),</v>
       </c>
     </row>
-    <row r="191" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="3" t="s">
         <v>431</v>
       </c>
@@ -7928,24 +9657,33 @@
       <c r="D191" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E191" t="str">
+      <c r="E191" s="7">
+        <v>1</v>
+      </c>
+      <c r="F191" s="7">
+        <v>4577</v>
+      </c>
+      <c r="G191" s="7">
+        <v>4577</v>
+      </c>
+      <c r="H191" t="str">
         <f t="shared" si="8"/>
         <v>'HP11e'</v>
       </c>
-      <c r="F191" t="str">
+      <c r="I191" t="str">
         <f t="shared" si="9"/>
         <v>'REFER_PTSD'</v>
       </c>
-      <c r="G191" t="str">
+      <c r="J191" t="str">
         <f t="shared" si="10"/>
         <v>'Concerns identified: PTSD symptoms'</v>
       </c>
-      <c r="H191" t="str">
+      <c r="K191" t="str">
         <f t="shared" si="11"/>
         <v>('HP11e','REFER_PTSD','Concerns identified: PTSD symptoms'),</v>
       </c>
     </row>
-    <row r="192" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="3" t="s">
         <v>434</v>
       </c>
@@ -7958,24 +9696,33 @@
       <c r="D192" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E192" t="str">
+      <c r="E192" s="7">
+        <v>1</v>
+      </c>
+      <c r="F192" s="7">
+        <v>4578</v>
+      </c>
+      <c r="G192" s="7">
+        <v>4578</v>
+      </c>
+      <c r="H192" t="str">
         <f t="shared" si="8"/>
         <v>'HP11f'</v>
       </c>
-      <c r="F192" t="str">
+      <c r="I192" t="str">
         <f t="shared" si="9"/>
         <v>'REFER_DEPRESSION'</v>
       </c>
-      <c r="G192" t="str">
+      <c r="J192" t="str">
         <f t="shared" si="10"/>
         <v>'Concerns identified: Depression symptoms'</v>
       </c>
-      <c r="H192" t="str">
+      <c r="K192" t="str">
         <f t="shared" si="11"/>
         <v>('HP11f','REFER_DEPRESSION','Concerns identified: Depression symptoms'),</v>
       </c>
     </row>
-    <row r="193" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
         <v>437</v>
       </c>
@@ -7988,24 +9735,33 @@
       <c r="D193" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E193" t="str">
+      <c r="E193" s="7">
+        <v>1</v>
+      </c>
+      <c r="F193" s="7">
+        <v>4579</v>
+      </c>
+      <c r="G193" s="7">
+        <v>4579</v>
+      </c>
+      <c r="H193" t="str">
         <f t="shared" si="8"/>
         <v>'HP11g'</v>
       </c>
-      <c r="F193" t="str">
+      <c r="I193" t="str">
         <f t="shared" si="9"/>
         <v>'REFER_MH'</v>
       </c>
-      <c r="G193" t="str">
+      <c r="J193" t="str">
         <f t="shared" si="10"/>
         <v>'Concerns identified: Mental health symptoms'</v>
       </c>
-      <c r="H193" t="str">
+      <c r="K193" t="str">
         <f t="shared" si="11"/>
         <v>('HP11g','REFER_MH','Concerns identified: Mental health symptoms'),</v>
       </c>
     </row>
-    <row r="194" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="3" t="s">
         <v>440</v>
       </c>
@@ -8018,24 +9774,33 @@
       <c r="D194" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E194" t="str">
+      <c r="E194" s="7">
+        <v>1</v>
+      </c>
+      <c r="F194" s="7">
+        <v>4580</v>
+      </c>
+      <c r="G194" s="7">
+        <v>4580</v>
+      </c>
+      <c r="H194" t="str">
         <f t="shared" si="8"/>
         <v>'HP11h'</v>
       </c>
-      <c r="F194" t="str">
+      <c r="I194" t="str">
         <f t="shared" si="9"/>
         <v>'REFER_HARM'</v>
       </c>
-      <c r="G194" t="str">
+      <c r="J194" t="str">
         <f t="shared" si="10"/>
         <v>'Concerns identified: Risk of self-harm'</v>
       </c>
-      <c r="H194" t="str">
+      <c r="K194" t="str">
         <f t="shared" si="11"/>
         <v>('HP11h','REFER_HARM','Concerns identified: Risk of self-harm'),</v>
       </c>
     </row>
-    <row r="195" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
         <v>443</v>
       </c>
@@ -8048,24 +9813,33 @@
       <c r="D195" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E195" t="str">
-        <f t="shared" ref="E195:E238" si="12">$E$1&amp;A195&amp;$E$1</f>
+      <c r="E195" s="7">
+        <v>1</v>
+      </c>
+      <c r="F195" s="7">
+        <v>4581</v>
+      </c>
+      <c r="G195" s="7">
+        <v>4581</v>
+      </c>
+      <c r="H195" t="str">
+        <f t="shared" ref="H195:H238" si="12">$H$1&amp;A195&amp;$H$1</f>
         <v>'HP11i'</v>
       </c>
-      <c r="F195" t="str">
-        <f t="shared" ref="F195:F238" si="13">$E$1&amp;B195&amp;$E$1</f>
+      <c r="I195" t="str">
+        <f t="shared" ref="I195:I238" si="13">$H$1&amp;B195&amp;$H$1</f>
         <v>'REFER_VIOLENCE'</v>
       </c>
-      <c r="G195" t="str">
-        <f t="shared" ref="G195:G238" si="14">$E$1&amp;SUBSTITUTE(C195, "'", "''")&amp;$E$1</f>
+      <c r="J195" t="str">
+        <f t="shared" ref="J195:J238" si="14">$H$1&amp;SUBSTITUTE(C195, "'", "''")&amp;$H$1</f>
         <v>'Concerns identified: Risk of violence'</v>
       </c>
-      <c r="H195" t="str">
-        <f t="shared" ref="H195:H238" si="15">"("&amp;E195&amp;","&amp;F195&amp;","&amp;G195&amp;"),"</f>
+      <c r="K195" t="str">
+        <f t="shared" ref="K195:K238" si="15">"("&amp;H195&amp;","&amp;I195&amp;","&amp;J195&amp;"),"</f>
         <v>('HP11i','REFER_VIOLENCE','Concerns identified: Risk of violence'),</v>
       </c>
     </row>
-    <row r="196" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="3" t="s">
         <v>446</v>
       </c>
@@ -8078,24 +9852,33 @@
       <c r="D196" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="E196" t="str">
+      <c r="E196" s="7">
+        <v>1</v>
+      </c>
+      <c r="F196" s="7">
+        <v>4582</v>
+      </c>
+      <c r="G196" s="7">
+        <v>4582</v>
+      </c>
+      <c r="H196" t="str">
         <f t="shared" si="12"/>
         <v>'HP11j'</v>
       </c>
-      <c r="F196" t="str">
+      <c r="I196" t="str">
         <f t="shared" si="13"/>
         <v>'REFER_OTHER'</v>
       </c>
-      <c r="G196" t="str">
+      <c r="J196" t="str">
         <f t="shared" si="14"/>
         <v>'Concerns identified: Other'</v>
       </c>
-      <c r="H196" t="str">
+      <c r="K196" t="str">
         <f t="shared" si="15"/>
         <v>('HP11j','REFER_OTHER','Concerns identified: Other'),</v>
       </c>
     </row>
-    <row r="197" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
         <v>446</v>
       </c>
@@ -8108,24 +9891,33 @@
       <c r="D197" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E197" t="str">
+      <c r="E197" s="7">
+        <v>50</v>
+      </c>
+      <c r="F197" s="7">
+        <v>4583</v>
+      </c>
+      <c r="G197" s="7">
+        <v>4632</v>
+      </c>
+      <c r="H197" t="str">
         <f t="shared" si="12"/>
         <v>'HP11j'</v>
       </c>
-      <c r="F197" t="str">
+      <c r="I197" t="str">
         <f t="shared" si="13"/>
         <v>'REFER_OTHER_TEXT'</v>
       </c>
-      <c r="G197" t="str">
+      <c r="J197" t="str">
         <f t="shared" si="14"/>
         <v>'Concerns identified: Other (list)'</v>
       </c>
-      <c r="H197" t="str">
+      <c r="K197" t="str">
         <f t="shared" si="15"/>
         <v>('HP11j','REFER_OTHER_TEXT','Concerns identified: Other (list)'),</v>
       </c>
     </row>
-    <row r="198" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="3" t="s">
         <v>451</v>
       </c>
@@ -8138,24 +9930,33 @@
       <c r="D198" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="E198" t="str">
+      <c r="E198" s="7">
+        <v>1</v>
+      </c>
+      <c r="F198" s="7">
+        <v>4633</v>
+      </c>
+      <c r="G198" s="7">
+        <v>4633</v>
+      </c>
+      <c r="H198" t="str">
         <f t="shared" si="12"/>
         <v>'HP12a'</v>
       </c>
-      <c r="F198" t="str">
+      <c r="I198" t="str">
         <f t="shared" si="13"/>
         <v>'REFTIME_PRIMARY'</v>
       </c>
-      <c r="G198" t="str">
+      <c r="J198" t="str">
         <f t="shared" si="14"/>
         <v>'Referral indicated - Primary Care, Family Practice, Internal Medicine'</v>
       </c>
-      <c r="H198" t="str">
+      <c r="K198" t="str">
         <f t="shared" si="15"/>
         <v>('HP12a','REFTIME_PRIMARY','Referral indicated - Primary Care, Family Practice, Internal Medicine'),</v>
       </c>
     </row>
-    <row r="199" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="3" t="s">
         <v>454</v>
       </c>
@@ -8168,24 +9969,33 @@
       <c r="D199" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="E199" t="str">
+      <c r="E199" s="7">
+        <v>1</v>
+      </c>
+      <c r="F199" s="7">
+        <v>4634</v>
+      </c>
+      <c r="G199" s="7">
+        <v>4634</v>
+      </c>
+      <c r="H199" t="str">
         <f t="shared" si="12"/>
         <v>'HP12b'</v>
       </c>
-      <c r="F199" t="str">
+      <c r="I199" t="str">
         <f t="shared" si="13"/>
         <v>'REFTIME_MENTAL_PRIMARY'</v>
       </c>
-      <c r="G199" t="str">
+      <c r="J199" t="str">
         <f t="shared" si="14"/>
         <v>'Referral indicated - Behavioral Health in Primary Care'</v>
       </c>
-      <c r="H199" t="str">
+      <c r="K199" t="str">
         <f t="shared" si="15"/>
         <v>('HP12b','REFTIME_MENTAL_PRIMARY','Referral indicated - Behavioral Health in Primary Care'),</v>
       </c>
     </row>
-    <row r="200" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="3" t="s">
         <v>457</v>
       </c>
@@ -8198,24 +10008,33 @@
       <c r="D200" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="E200" t="str">
+      <c r="E200" s="7">
+        <v>1</v>
+      </c>
+      <c r="F200" s="7">
+        <v>4635</v>
+      </c>
+      <c r="G200" s="7">
+        <v>4635</v>
+      </c>
+      <c r="H200" t="str">
         <f t="shared" si="12"/>
         <v>'HP12c'</v>
       </c>
-      <c r="F200" t="str">
+      <c r="I200" t="str">
         <f t="shared" si="13"/>
         <v>'REFTIME_MENTAL_SPECIAL'</v>
       </c>
-      <c r="G200" t="str">
+      <c r="J200" t="str">
         <f t="shared" si="14"/>
         <v>'Referral indicated - Mental Health'</v>
       </c>
-      <c r="H200" t="str">
+      <c r="K200" t="str">
         <f t="shared" si="15"/>
         <v>('HP12c','REFTIME_MENTAL_SPECIAL','Referral indicated - Mental Health'),</v>
       </c>
     </row>
-    <row r="201" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
         <v>460</v>
       </c>
@@ -8228,24 +10047,33 @@
       <c r="D201" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="E201" t="str">
+      <c r="E201" s="7">
+        <v>1</v>
+      </c>
+      <c r="F201" s="7">
+        <v>4636</v>
+      </c>
+      <c r="G201" s="7">
+        <v>4636</v>
+      </c>
+      <c r="H201" t="str">
         <f t="shared" si="12"/>
         <v>'HP12d'</v>
       </c>
-      <c r="F201" t="str">
+      <c r="I201" t="str">
         <f t="shared" si="13"/>
         <v>'REFTIME_DENTAL'</v>
       </c>
-      <c r="G201" t="str">
+      <c r="J201" t="str">
         <f t="shared" si="14"/>
         <v>'Referral indicated - Dental'</v>
       </c>
-      <c r="H201" t="str">
+      <c r="K201" t="str">
         <f t="shared" si="15"/>
         <v>('HP12d','REFTIME_DENTAL','Referral indicated - Dental'),</v>
       </c>
     </row>
-    <row r="202" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="3" t="s">
         <v>463</v>
       </c>
@@ -8258,24 +10086,33 @@
       <c r="D202" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="E202" t="str">
+      <c r="E202" s="7">
+        <v>1</v>
+      </c>
+      <c r="F202" s="7">
+        <v>4637</v>
+      </c>
+      <c r="G202" s="7">
+        <v>4637</v>
+      </c>
+      <c r="H202" t="str">
         <f t="shared" si="12"/>
         <v>'HP12e'</v>
       </c>
-      <c r="F202" t="str">
+      <c r="I202" t="str">
         <f t="shared" si="13"/>
         <v>'REFTIME_OTHER_SPEC'</v>
       </c>
-      <c r="G202" t="str">
+      <c r="J202" t="str">
         <f t="shared" si="14"/>
         <v>'Referral indicated - Other specialty care'</v>
       </c>
-      <c r="H202" t="str">
+      <c r="K202" t="str">
         <f t="shared" si="15"/>
         <v>('HP12e','REFTIME_OTHER_SPEC','Referral indicated - Other specialty care'),</v>
       </c>
     </row>
-    <row r="203" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
         <v>463</v>
       </c>
@@ -8288,24 +10125,33 @@
       <c r="D203" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="E203" t="str">
+      <c r="E203" s="7">
+        <v>1</v>
+      </c>
+      <c r="F203" s="7">
+        <v>4638</v>
+      </c>
+      <c r="G203" s="7">
+        <v>4638</v>
+      </c>
+      <c r="H203" t="str">
         <f t="shared" si="12"/>
         <v>'HP12e'</v>
       </c>
-      <c r="F203" t="str">
+      <c r="I203" t="str">
         <f t="shared" si="13"/>
         <v>'REFTIME_AUDIOLOGY'</v>
       </c>
-      <c r="G203" t="str">
+      <c r="J203" t="str">
         <f t="shared" si="14"/>
         <v>'Referral indicated - Audiology'</v>
       </c>
-      <c r="H203" t="str">
+      <c r="K203" t="str">
         <f t="shared" si="15"/>
         <v>('HP12e','REFTIME_AUDIOLOGY','Referral indicated - Audiology'),</v>
       </c>
     </row>
-    <row r="204" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="3" t="s">
         <v>463</v>
       </c>
@@ -8318,24 +10164,33 @@
       <c r="D204" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="E204" t="str">
+      <c r="E204" s="7">
+        <v>1</v>
+      </c>
+      <c r="F204" s="7">
+        <v>4639</v>
+      </c>
+      <c r="G204" s="7">
+        <v>4639</v>
+      </c>
+      <c r="H204" t="str">
         <f t="shared" si="12"/>
         <v>'HP12e'</v>
       </c>
-      <c r="F204" t="str">
+      <c r="I204" t="str">
         <f t="shared" si="13"/>
         <v>'REFTIME_DERM'</v>
       </c>
-      <c r="G204" t="str">
+      <c r="J204" t="str">
         <f t="shared" si="14"/>
         <v>'Referral indicated - dermatologic'</v>
       </c>
-      <c r="H204" t="str">
+      <c r="K204" t="str">
         <f t="shared" si="15"/>
         <v>('HP12e','REFTIME_DERM','Referral indicated - dermatologic'),</v>
       </c>
     </row>
-    <row r="205" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
         <v>463</v>
       </c>
@@ -8348,24 +10203,33 @@
       <c r="D205" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="E205" t="str">
+      <c r="E205" s="7">
+        <v>1</v>
+      </c>
+      <c r="F205" s="7">
+        <v>4640</v>
+      </c>
+      <c r="G205" s="7">
+        <v>4640</v>
+      </c>
+      <c r="H205" t="str">
         <f t="shared" si="12"/>
         <v>'HP12e'</v>
       </c>
-      <c r="F205" t="str">
+      <c r="I205" t="str">
         <f t="shared" si="13"/>
         <v>'REFTIME_GYN'</v>
       </c>
-      <c r="G205" t="str">
+      <c r="J205" t="str">
         <f t="shared" si="14"/>
         <v>'Referral indicated - OB/GYN'</v>
       </c>
-      <c r="H205" t="str">
+      <c r="K205" t="str">
         <f t="shared" si="15"/>
         <v>('HP12e','REFTIME_GYN','Referral indicated - OB/GYN'),</v>
       </c>
     </row>
-    <row r="206" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="3" t="s">
         <v>463</v>
       </c>
@@ -8378,24 +10242,33 @@
       <c r="D206" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="E206" t="str">
+      <c r="E206" s="7">
+        <v>1</v>
+      </c>
+      <c r="F206" s="7">
+        <v>4641</v>
+      </c>
+      <c r="G206" s="7">
+        <v>4641</v>
+      </c>
+      <c r="H206" t="str">
         <f t="shared" si="12"/>
         <v>'HP12e'</v>
       </c>
-      <c r="F206" t="str">
+      <c r="I206" t="str">
         <f t="shared" si="13"/>
         <v>'REFTIME_PT'</v>
       </c>
-      <c r="G206" t="str">
+      <c r="J206" t="str">
         <f t="shared" si="14"/>
         <v>'Referral indicated - PT'</v>
       </c>
-      <c r="H206" t="str">
+      <c r="K206" t="str">
         <f t="shared" si="15"/>
         <v>('HP12e','REFTIME_PT','Referral indicated - PT'),</v>
       </c>
     </row>
-    <row r="207" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="3" t="s">
         <v>463</v>
       </c>
@@ -8408,24 +10281,33 @@
       <c r="D207" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="E207" t="str">
+      <c r="E207" s="7">
+        <v>1</v>
+      </c>
+      <c r="F207" s="7">
+        <v>4642</v>
+      </c>
+      <c r="G207" s="7">
+        <v>4642</v>
+      </c>
+      <c r="H207" t="str">
         <f t="shared" si="12"/>
         <v>'HP12e'</v>
       </c>
-      <c r="F207" t="str">
+      <c r="I207" t="str">
         <f t="shared" si="13"/>
         <v>'REFTIME_TBI'</v>
       </c>
-      <c r="G207" t="str">
+      <c r="J207" t="str">
         <f t="shared" si="14"/>
         <v>'Referral indicated -TBI/Rehab Med'</v>
       </c>
-      <c r="H207" t="str">
+      <c r="K207" t="str">
         <f t="shared" si="15"/>
         <v>('HP12e','REFTIME_TBI','Referral indicated -TBI/Rehab Med'),</v>
       </c>
     </row>
-    <row r="208" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="3" t="s">
         <v>463</v>
       </c>
@@ -8438,24 +10320,33 @@
       <c r="D208" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="E208" t="str">
+      <c r="E208" s="7">
+        <v>1</v>
+      </c>
+      <c r="F208" s="7">
+        <v>4643</v>
+      </c>
+      <c r="G208" s="7">
+        <v>4643</v>
+      </c>
+      <c r="H208" t="str">
         <f t="shared" si="12"/>
         <v>'HP12e'</v>
       </c>
-      <c r="F208" t="str">
+      <c r="I208" t="str">
         <f t="shared" si="13"/>
         <v>'REFTIME_PODIATRY'</v>
       </c>
-      <c r="G208" t="str">
+      <c r="J208" t="str">
         <f t="shared" si="14"/>
         <v>'Referral indicated - Podiatry'</v>
       </c>
-      <c r="H208" t="str">
+      <c r="K208" t="str">
         <f t="shared" si="15"/>
         <v>('HP12e','REFTIME_PODIATRY','Referral indicated - Podiatry'),</v>
       </c>
     </row>
-    <row r="209" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
         <v>463</v>
       </c>
@@ -8468,24 +10359,33 @@
       <c r="D209" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="E209" t="str">
+      <c r="E209" s="7">
+        <v>1</v>
+      </c>
+      <c r="F209" s="7">
+        <v>4644</v>
+      </c>
+      <c r="G209" s="7">
+        <v>4644</v>
+      </c>
+      <c r="H209" t="str">
         <f t="shared" si="12"/>
         <v>'HP12e'</v>
       </c>
-      <c r="F209" t="str">
+      <c r="I209" t="str">
         <f t="shared" si="13"/>
         <v>'REFTIME_SPEC_OTHER'</v>
       </c>
-      <c r="G209" t="str">
+      <c r="J209" t="str">
         <f t="shared" si="14"/>
         <v>'Referral to other specialty care listed'</v>
       </c>
-      <c r="H209" t="str">
+      <c r="K209" t="str">
         <f t="shared" si="15"/>
         <v>('HP12e','REFTIME_SPEC_OTHER','Referral to other specialty care listed'),</v>
       </c>
     </row>
-    <row r="210" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="3" t="s">
         <v>463</v>
       </c>
@@ -8498,24 +10398,33 @@
       <c r="D210" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E210" t="str">
+      <c r="E210" s="7">
+        <v>50</v>
+      </c>
+      <c r="F210" s="7">
+        <v>4645</v>
+      </c>
+      <c r="G210" s="7">
+        <v>4694</v>
+      </c>
+      <c r="H210" t="str">
         <f t="shared" si="12"/>
         <v>'HP12e'</v>
       </c>
-      <c r="F210" t="str">
+      <c r="I210" t="str">
         <f t="shared" si="13"/>
         <v>'REFTIME_SPEC_OTH_TEXT'</v>
       </c>
-      <c r="G210" t="str">
+      <c r="J210" t="str">
         <f t="shared" si="14"/>
         <v>'List of other specialty referral'</v>
       </c>
-      <c r="H210" t="str">
+      <c r="K210" t="str">
         <f t="shared" si="15"/>
         <v>('HP12e','REFTIME_SPEC_OTH_TEXT','List of other specialty referral'),</v>
       </c>
     </row>
-    <row r="211" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
         <v>482</v>
       </c>
@@ -8528,24 +10437,33 @@
       <c r="D211" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="E211" t="str">
+      <c r="E211" s="7">
+        <v>1</v>
+      </c>
+      <c r="F211" s="7">
+        <v>4695</v>
+      </c>
+      <c r="G211" s="7">
+        <v>4695</v>
+      </c>
+      <c r="H211" t="str">
         <f t="shared" si="12"/>
         <v>'HP12f'</v>
       </c>
-      <c r="F211" t="str">
+      <c r="I211" t="str">
         <f t="shared" si="13"/>
         <v>'REFTIME_CARE'</v>
       </c>
-      <c r="G211" t="str">
+      <c r="J211" t="str">
         <f t="shared" si="14"/>
         <v>'Referral to Case manager'</v>
       </c>
-      <c r="H211" t="str">
+      <c r="K211" t="str">
         <f t="shared" si="15"/>
         <v>('HP12f','REFTIME_CARE','Referral to Case manager'),</v>
       </c>
     </row>
-    <row r="212" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="3" t="s">
         <v>485</v>
       </c>
@@ -8558,24 +10476,33 @@
       <c r="D212" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="E212" t="str">
+      <c r="E212" s="7">
+        <v>1</v>
+      </c>
+      <c r="F212" s="7">
+        <v>4696</v>
+      </c>
+      <c r="G212" s="7">
+        <v>4696</v>
+      </c>
+      <c r="H212" t="str">
         <f t="shared" si="12"/>
         <v>'HP12g'</v>
       </c>
-      <c r="F212" t="str">
+      <c r="I212" t="str">
         <f t="shared" si="13"/>
         <v>'REFTIME_ABUSE'</v>
       </c>
-      <c r="G212" t="str">
+      <c r="J212" t="str">
         <f t="shared" si="14"/>
         <v>'Referral to Substance abuse program'</v>
       </c>
-      <c r="H212" t="str">
+      <c r="K212" t="str">
         <f t="shared" si="15"/>
         <v>('HP12g','REFTIME_ABUSE','Referral to Substance abuse program'),</v>
       </c>
     </row>
-    <row r="213" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="3" t="s">
         <v>488</v>
       </c>
@@ -8588,24 +10515,33 @@
       <c r="D213" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="E213" t="str">
+      <c r="E213" s="7">
+        <v>1</v>
+      </c>
+      <c r="F213" s="7">
+        <v>4697</v>
+      </c>
+      <c r="G213" s="7">
+        <v>4697</v>
+      </c>
+      <c r="H213" t="str">
         <f t="shared" si="12"/>
         <v>'HP12h'</v>
       </c>
-      <c r="F213" t="str">
+      <c r="I213" t="str">
         <f t="shared" si="13"/>
         <v>'REFTIME_OTHER'</v>
       </c>
-      <c r="G213" t="str">
+      <c r="J213" t="str">
         <f t="shared" si="14"/>
         <v>'Other referral listed'</v>
       </c>
-      <c r="H213" t="str">
+      <c r="K213" t="str">
         <f t="shared" si="15"/>
         <v>('HP12h','REFTIME_OTHER','Other referral listed'),</v>
       </c>
     </row>
-    <row r="214" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="3" t="s">
         <v>488</v>
       </c>
@@ -8618,24 +10554,33 @@
       <c r="D214" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E214" t="str">
+      <c r="E214" s="7">
+        <v>50</v>
+      </c>
+      <c r="F214" s="7">
+        <v>4698</v>
+      </c>
+      <c r="G214" s="7">
+        <v>4747</v>
+      </c>
+      <c r="H214" t="str">
         <f t="shared" si="12"/>
         <v>'HP12h'</v>
       </c>
-      <c r="F214" t="str">
+      <c r="I214" t="str">
         <f t="shared" si="13"/>
         <v>'REFTIME_OTHER_TEXT'</v>
       </c>
-      <c r="G214" t="str">
+      <c r="J214" t="str">
         <f t="shared" si="14"/>
         <v>'List of other specialty referral'</v>
       </c>
-      <c r="H214" t="str">
+      <c r="K214" t="str">
         <f t="shared" si="15"/>
         <v>('HP12h','REFTIME_OTHER_TEXT','List of other specialty referral'),</v>
       </c>
     </row>
-    <row r="215" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="3" t="s">
         <v>492</v>
       </c>
@@ -8648,24 +10593,33 @@
       <c r="D215" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E215" t="str">
+      <c r="E215" s="7">
+        <v>100</v>
+      </c>
+      <c r="F215" s="7">
+        <v>4748</v>
+      </c>
+      <c r="G215" s="7">
+        <v>4847</v>
+      </c>
+      <c r="H215" t="str">
         <f t="shared" si="12"/>
         <v>'HP13'</v>
       </c>
-      <c r="F215" t="str">
+      <c r="I215" t="str">
         <f t="shared" si="13"/>
         <v>'REFTIME_COMMENTS'</v>
       </c>
-      <c r="G215" t="str">
+      <c r="J215" t="str">
         <f t="shared" si="14"/>
         <v>'Referral comments'</v>
       </c>
-      <c r="H215" t="str">
+      <c r="K215" t="str">
         <f t="shared" si="15"/>
         <v>('HP13','REFTIME_COMMENTS','Referral comments'),</v>
       </c>
     </row>
-    <row r="216" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="3" t="s">
         <v>495</v>
       </c>
@@ -8678,24 +10632,33 @@
       <c r="D216" s="3" t="s">
         <v>572</v>
       </c>
-      <c r="E216" t="str">
+      <c r="E216" s="7">
+        <v>1</v>
+      </c>
+      <c r="F216" s="7">
+        <v>4848</v>
+      </c>
+      <c r="G216" s="7">
+        <v>4848</v>
+      </c>
+      <c r="H216" t="str">
         <f t="shared" si="12"/>
         <v>'HP14'</v>
       </c>
-      <c r="F216" t="str">
+      <c r="I216" t="str">
         <f t="shared" si="13"/>
         <v>'MED_DISP'</v>
       </c>
-      <c r="G216" t="str">
+      <c r="J216" t="str">
         <f t="shared" si="14"/>
         <v>'Final Medical Disposition'</v>
       </c>
-      <c r="H216" t="str">
+      <c r="K216" t="str">
         <f t="shared" si="15"/>
         <v>('HP14','MED_DISP','Final Medical Disposition'),</v>
       </c>
     </row>
-    <row r="217" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="3" t="s">
         <v>498</v>
       </c>
@@ -8708,24 +10671,33 @@
       <c r="D217" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="E217" t="str">
+      <c r="E217" s="7">
+        <v>1</v>
+      </c>
+      <c r="F217" s="7">
+        <v>4849</v>
+      </c>
+      <c r="G217" s="7">
+        <v>4849</v>
+      </c>
+      <c r="H217" t="str">
         <f t="shared" si="12"/>
         <v>'HP16'</v>
       </c>
-      <c r="F217" t="str">
+      <c r="I217" t="str">
         <f t="shared" si="13"/>
         <v>'APPOINTMENT_ASSIST'</v>
       </c>
-      <c r="G217" t="str">
+      <c r="J217" t="str">
         <f t="shared" si="14"/>
         <v>'Appointment Assistance'</v>
       </c>
-      <c r="H217" t="str">
+      <c r="K217" t="str">
         <f t="shared" si="15"/>
         <v>('HP16','APPOINTMENT_ASSIST','Appointment Assistance'),</v>
       </c>
     </row>
-    <row r="218" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A218" s="3" t="s">
         <v>498</v>
       </c>
@@ -8738,24 +10710,33 @@
       <c r="D218" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E218" t="str">
+      <c r="E218" s="7">
+        <v>50</v>
+      </c>
+      <c r="F218" s="7">
+        <v>4850</v>
+      </c>
+      <c r="G218" s="7">
+        <v>4899</v>
+      </c>
+      <c r="H218" t="str">
         <f t="shared" si="12"/>
         <v>'HP16'</v>
       </c>
-      <c r="F218" t="str">
+      <c r="I218" t="str">
         <f t="shared" si="13"/>
         <v>'APPOINT_ASSIST_TEXT'</v>
       </c>
-      <c r="G218" t="str">
+      <c r="J218" t="str">
         <f t="shared" si="14"/>
         <v>'Appointment assistance text'</v>
       </c>
-      <c r="H218" t="str">
+      <c r="K218" t="str">
         <f t="shared" si="15"/>
         <v>('HP16','APPOINT_ASSIST_TEXT','Appointment assistance text'),</v>
       </c>
     </row>
-    <row r="219" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A219" s="3" t="s">
         <v>498</v>
       </c>
@@ -8768,24 +10749,33 @@
       <c r="D219" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="E219" t="str">
+      <c r="E219" s="7">
+        <v>1</v>
+      </c>
+      <c r="F219" s="7">
+        <v>4900</v>
+      </c>
+      <c r="G219" s="7">
+        <v>4900</v>
+      </c>
+      <c r="H219" t="str">
         <f t="shared" si="12"/>
         <v>'HP16'</v>
       </c>
-      <c r="F219" t="str">
+      <c r="I219" t="str">
         <f t="shared" si="13"/>
         <v>'CONTRACT_SUP'</v>
       </c>
-      <c r="G219" t="str">
+      <c r="J219" t="str">
         <f t="shared" si="14"/>
         <v>'Contract support'</v>
       </c>
-      <c r="H219" t="str">
+      <c r="K219" t="str">
         <f t="shared" si="15"/>
         <v>('HP16','CONTRACT_SUP','Contract support'),</v>
       </c>
     </row>
-    <row r="220" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="3" t="s">
         <v>498</v>
       </c>
@@ -8798,24 +10788,33 @@
       <c r="D220" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E220" t="str">
+      <c r="E220" s="7">
+        <v>50</v>
+      </c>
+      <c r="F220" s="7">
+        <v>4901</v>
+      </c>
+      <c r="G220" s="7">
+        <v>4950</v>
+      </c>
+      <c r="H220" t="str">
         <f t="shared" si="12"/>
         <v>'HP16'</v>
       </c>
-      <c r="F220" t="str">
+      <c r="I220" t="str">
         <f t="shared" si="13"/>
         <v>'CONTRACT_SUP_TEXT'</v>
       </c>
-      <c r="G220" t="str">
+      <c r="J220" t="str">
         <f t="shared" si="14"/>
         <v>'Contract support text'</v>
       </c>
-      <c r="H220" t="str">
+      <c r="K220" t="str">
         <f t="shared" si="15"/>
         <v>('HP16','CONTRACT_SUP_TEXT','Contract support text'),</v>
       </c>
     </row>
-    <row r="221" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
         <v>498</v>
       </c>
@@ -8828,24 +10827,33 @@
       <c r="D221" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="E221" t="str">
+      <c r="E221" s="7">
+        <v>1</v>
+      </c>
+      <c r="F221" s="7">
+        <v>4951</v>
+      </c>
+      <c r="G221" s="7">
+        <v>4951</v>
+      </c>
+      <c r="H221" t="str">
         <f t="shared" si="12"/>
         <v>'HP16'</v>
       </c>
-      <c r="F221" t="str">
+      <c r="I221" t="str">
         <f t="shared" si="13"/>
         <v>'COMMUNITY'</v>
       </c>
-      <c r="G221" t="str">
+      <c r="J221" t="str">
         <f t="shared" si="14"/>
         <v>'Community Service'</v>
       </c>
-      <c r="H221" t="str">
+      <c r="K221" t="str">
         <f t="shared" si="15"/>
         <v>('HP16','COMMUNITY','Community Service'),</v>
       </c>
     </row>
-    <row r="222" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A222" s="3" t="s">
         <v>498</v>
       </c>
@@ -8858,24 +10866,33 @@
       <c r="D222" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E222" t="str">
+      <c r="E222" s="7">
+        <v>50</v>
+      </c>
+      <c r="F222" s="7">
+        <v>4952</v>
+      </c>
+      <c r="G222" s="7">
+        <v>5001</v>
+      </c>
+      <c r="H222" t="str">
         <f t="shared" si="12"/>
         <v>'HP16'</v>
       </c>
-      <c r="F222" t="str">
+      <c r="I222" t="str">
         <f t="shared" si="13"/>
         <v>'COMMUNITY_TEXT'</v>
       </c>
-      <c r="G222" t="str">
+      <c r="J222" t="str">
         <f t="shared" si="14"/>
         <v>'Community Service text'</v>
       </c>
-      <c r="H222" t="str">
+      <c r="K222" t="str">
         <f t="shared" si="15"/>
         <v>('HP16','COMMUNITY_TEXT','Community Service text'),</v>
       </c>
     </row>
-    <row r="223" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="3" t="s">
         <v>498</v>
       </c>
@@ -8888,24 +10905,33 @@
       <c r="D223" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="E223" t="str">
+      <c r="E223" s="7">
+        <v>1</v>
+      </c>
+      <c r="F223" s="7">
+        <v>5002</v>
+      </c>
+      <c r="G223" s="7">
+        <v>5002</v>
+      </c>
+      <c r="H223" t="str">
         <f t="shared" si="12"/>
         <v>'HP16'</v>
       </c>
-      <c r="F223" t="str">
+      <c r="I223" t="str">
         <f t="shared" si="13"/>
         <v>'CHAPLAIN'</v>
       </c>
-      <c r="G223" t="str">
+      <c r="J223" t="str">
         <f t="shared" si="14"/>
         <v>'Chaplain'</v>
       </c>
-      <c r="H223" t="str">
+      <c r="K223" t="str">
         <f t="shared" si="15"/>
         <v>('HP16','CHAPLAIN','Chaplain'),</v>
       </c>
     </row>
-    <row r="224" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="3" t="s">
         <v>498</v>
       </c>
@@ -8918,24 +10944,33 @@
       <c r="D224" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="E224" t="str">
+      <c r="E224" s="7">
+        <v>1</v>
+      </c>
+      <c r="F224" s="7">
+        <v>5003</v>
+      </c>
+      <c r="G224" s="7">
+        <v>5003</v>
+      </c>
+      <c r="H224" t="str">
         <f t="shared" si="12"/>
         <v>'HP16'</v>
       </c>
-      <c r="F224" t="str">
+      <c r="I224" t="str">
         <f t="shared" si="13"/>
         <v>'HEALTH_ED'</v>
       </c>
-      <c r="G224" t="str">
+      <c r="J224" t="str">
         <f t="shared" si="14"/>
         <v>'Health Education and Information'</v>
       </c>
-      <c r="H224" t="str">
+      <c r="K224" t="str">
         <f t="shared" si="15"/>
         <v>('HP16','HEALTH_ED','Health Education and Information'),</v>
       </c>
     </row>
-    <row r="225" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
         <v>498</v>
       </c>
@@ -8948,24 +10983,33 @@
       <c r="D225" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="E225" t="str">
+      <c r="E225" s="7">
+        <v>1</v>
+      </c>
+      <c r="F225" s="7">
+        <v>5004</v>
+      </c>
+      <c r="G225" s="7">
+        <v>5004</v>
+      </c>
+      <c r="H225" t="str">
         <f t="shared" si="12"/>
         <v>'HP16'</v>
       </c>
-      <c r="F225" t="str">
+      <c r="I225" t="str">
         <f t="shared" si="13"/>
         <v>'HEALTH_RESOURCES'</v>
       </c>
-      <c r="G225" t="str">
+      <c r="J225" t="str">
         <f t="shared" si="14"/>
         <v>'Health Care Benefits and Resources Information'</v>
       </c>
-      <c r="H225" t="str">
+      <c r="K225" t="str">
         <f t="shared" si="15"/>
         <v>('HP16','HEALTH_RESOURCES','Health Care Benefits and Resources Information'),</v>
       </c>
     </row>
-    <row r="226" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="3" t="s">
         <v>498</v>
       </c>
@@ -8978,24 +11022,33 @@
       <c r="D226" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="E226" t="str">
+      <c r="E226" s="7">
+        <v>1</v>
+      </c>
+      <c r="F226" s="7">
+        <v>5005</v>
+      </c>
+      <c r="G226" s="7">
+        <v>5005</v>
+      </c>
+      <c r="H226" t="str">
         <f t="shared" si="12"/>
         <v>'HP16'</v>
       </c>
-      <c r="F226" t="str">
+      <c r="I226" t="str">
         <f t="shared" si="13"/>
         <v>'IN_TRANS'</v>
       </c>
-      <c r="G226" t="str">
+      <c r="J226" t="str">
         <f t="shared" si="14"/>
         <v>'In Transition'</v>
       </c>
-      <c r="H226" t="str">
+      <c r="K226" t="str">
         <f t="shared" si="15"/>
         <v>('HP16','IN_TRANS','In Transition'),</v>
       </c>
     </row>
-    <row r="227" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="3" t="s">
         <v>498</v>
       </c>
@@ -9008,24 +11061,33 @@
       <c r="D227" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="E227" t="str">
+      <c r="E227" s="7">
+        <v>1</v>
+      </c>
+      <c r="F227" s="7">
+        <v>5006</v>
+      </c>
+      <c r="G227" s="7">
+        <v>5006</v>
+      </c>
+      <c r="H227" t="str">
         <f t="shared" si="12"/>
         <v>'HP16'</v>
       </c>
-      <c r="F227" t="str">
+      <c r="I227" t="str">
         <f t="shared" si="13"/>
         <v>'FAM_SUPPORT'</v>
       </c>
-      <c r="G227" t="str">
+      <c r="J227" t="str">
         <f t="shared" si="14"/>
         <v>'Family Support'</v>
       </c>
-      <c r="H227" t="str">
+      <c r="K227" t="str">
         <f t="shared" si="15"/>
         <v>('HP16','FAM_SUPPORT','Family Support'),</v>
       </c>
     </row>
-    <row r="228" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="3" t="s">
         <v>498</v>
       </c>
@@ -9038,24 +11100,33 @@
       <c r="D228" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="E228" t="str">
+      <c r="E228" s="7">
+        <v>1</v>
+      </c>
+      <c r="F228" s="7">
+        <v>5007</v>
+      </c>
+      <c r="G228" s="7">
+        <v>5007</v>
+      </c>
+      <c r="H228" t="str">
         <f t="shared" si="12"/>
         <v>'HP16'</v>
       </c>
-      <c r="F228" t="str">
+      <c r="I228" t="str">
         <f t="shared" si="13"/>
         <v>'ONE_SOURCE'</v>
       </c>
-      <c r="G228" t="str">
+      <c r="J228" t="str">
         <f t="shared" si="14"/>
         <v>'Military one source'</v>
       </c>
-      <c r="H228" t="str">
+      <c r="K228" t="str">
         <f t="shared" si="15"/>
         <v>('HP16','ONE_SOURCE','Military one source'),</v>
       </c>
     </row>
-    <row r="229" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="3" t="s">
         <v>498</v>
       </c>
@@ -9068,24 +11139,33 @@
       <c r="D229" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="E229" t="str">
+      <c r="E229" s="7">
+        <v>1</v>
+      </c>
+      <c r="F229" s="7">
+        <v>5008</v>
+      </c>
+      <c r="G229" s="7">
+        <v>5008</v>
+      </c>
+      <c r="H229" t="str">
         <f t="shared" si="12"/>
         <v>'HP16'</v>
       </c>
-      <c r="F229" t="str">
+      <c r="I229" t="str">
         <f t="shared" si="13"/>
         <v>'TRICARE'</v>
       </c>
-      <c r="G229" t="str">
+      <c r="J229" t="str">
         <f t="shared" si="14"/>
         <v>'TRICARE PROVIDER'</v>
       </c>
-      <c r="H229" t="str">
+      <c r="K229" t="str">
         <f t="shared" si="15"/>
         <v>('HP16','TRICARE','TRICARE PROVIDER'),</v>
       </c>
     </row>
-    <row r="230" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="3" t="s">
         <v>498</v>
       </c>
@@ -9098,24 +11178,33 @@
       <c r="D230" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="E230" t="str">
+      <c r="E230" s="7">
+        <v>1</v>
+      </c>
+      <c r="F230" s="7">
+        <v>5009</v>
+      </c>
+      <c r="G230" s="7">
+        <v>5009</v>
+      </c>
+      <c r="H230" t="str">
         <f t="shared" si="12"/>
         <v>'HP16'</v>
       </c>
-      <c r="F230" t="str">
+      <c r="I230" t="str">
         <f t="shared" si="13"/>
         <v>'VA_MED'</v>
       </c>
-      <c r="G230" t="str">
+      <c r="J230" t="str">
         <f t="shared" si="14"/>
         <v>'VA Medical Center or Community Clinic'</v>
       </c>
-      <c r="H230" t="str">
+      <c r="K230" t="str">
         <f t="shared" si="15"/>
         <v>('HP16','VA_MED','VA Medical Center or Community Clinic'),</v>
       </c>
     </row>
-    <row r="231" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="3" t="s">
         <v>498</v>
       </c>
@@ -9128,24 +11217,33 @@
       <c r="D231" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="E231" t="str">
+      <c r="E231" s="7">
+        <v>1</v>
+      </c>
+      <c r="F231" s="7">
+        <v>5010</v>
+      </c>
+      <c r="G231" s="7">
+        <v>5010</v>
+      </c>
+      <c r="H231" t="str">
         <f t="shared" si="12"/>
         <v>'HP16'</v>
       </c>
-      <c r="F231" t="str">
+      <c r="I231" t="str">
         <f t="shared" si="13"/>
         <v>'VET'</v>
       </c>
-      <c r="G231" t="str">
+      <c r="J231" t="str">
         <f t="shared" si="14"/>
         <v>'Vet Center'</v>
       </c>
-      <c r="H231" t="str">
+      <c r="K231" t="str">
         <f t="shared" si="15"/>
         <v>('HP16','VET','Vet Center'),</v>
       </c>
     </row>
-    <row r="232" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="3" t="s">
         <v>498</v>
       </c>
@@ -9158,24 +11256,33 @@
       <c r="D232" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="E232" t="str">
+      <c r="E232" s="7">
+        <v>1</v>
+      </c>
+      <c r="F232" s="7">
+        <v>5011</v>
+      </c>
+      <c r="G232" s="7">
+        <v>5011</v>
+      </c>
+      <c r="H232" t="str">
         <f t="shared" si="12"/>
         <v>'HP16'</v>
       </c>
-      <c r="F232" t="str">
+      <c r="I232" t="str">
         <f t="shared" si="13"/>
         <v>'OTHER_SUPPORT'</v>
       </c>
-      <c r="G232" t="str">
+      <c r="J232" t="str">
         <f t="shared" si="14"/>
         <v>'Other Supplemental services recommended'</v>
       </c>
-      <c r="H232" t="str">
+      <c r="K232" t="str">
         <f t="shared" si="15"/>
         <v>('HP16','OTHER_SUPPORT','Other Supplemental services recommended'),</v>
       </c>
     </row>
-    <row r="233" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="3" t="s">
         <v>498</v>
       </c>
@@ -9188,24 +11295,33 @@
       <c r="D233" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E233" t="str">
+      <c r="E233" s="7">
+        <v>100</v>
+      </c>
+      <c r="F233" s="7">
+        <v>5012</v>
+      </c>
+      <c r="G233" s="7">
+        <v>5111</v>
+      </c>
+      <c r="H233" t="str">
         <f t="shared" si="12"/>
         <v>'HP16'</v>
       </c>
-      <c r="F233" t="str">
+      <c r="I233" t="str">
         <f t="shared" si="13"/>
         <v>'OTHER_SUPPORT_TEXT'</v>
       </c>
-      <c r="G233" t="str">
+      <c r="J233" t="str">
         <f t="shared" si="14"/>
         <v>'Other Supplemental services recommended text'</v>
       </c>
-      <c r="H233" t="str">
+      <c r="K233" t="str">
         <f t="shared" si="15"/>
         <v>('HP16','OTHER_SUPPORT_TEXT','Other Supplemental services recommended text'),</v>
       </c>
     </row>
-    <row r="234" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="3" t="s">
         <v>498</v>
       </c>
@@ -9218,24 +11334,33 @@
       <c r="D234" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="E234" t="str">
+      <c r="E234" s="7">
+        <v>1</v>
+      </c>
+      <c r="F234" s="7">
+        <v>5112</v>
+      </c>
+      <c r="G234" s="7">
+        <v>5112</v>
+      </c>
+      <c r="H234" t="str">
         <f t="shared" si="12"/>
         <v>'HP16'</v>
       </c>
-      <c r="F234" t="str">
+      <c r="I234" t="str">
         <f t="shared" si="13"/>
         <v>'APPOINTMENT_NONE'</v>
       </c>
-      <c r="G234" t="str">
+      <c r="J234" t="str">
         <f t="shared" si="14"/>
         <v>'No Supplemental Services Required'</v>
       </c>
-      <c r="H234" t="str">
+      <c r="K234" t="str">
         <f t="shared" si="15"/>
         <v>('HP16','APPOINTMENT_NONE','No Supplemental Services Required'),</v>
       </c>
     </row>
-    <row r="235" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="3" t="s">
         <v>498</v>
       </c>
@@ -9248,24 +11373,33 @@
       <c r="D235" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E235" t="str">
+      <c r="E235" s="7">
+        <v>50</v>
+      </c>
+      <c r="F235" s="7">
+        <v>5113</v>
+      </c>
+      <c r="G235" s="7">
+        <v>5162</v>
+      </c>
+      <c r="H235" t="str">
         <f t="shared" si="12"/>
         <v>'HP16'</v>
       </c>
-      <c r="F235" t="str">
+      <c r="I235" t="str">
         <f t="shared" si="13"/>
         <v>'PROVIDER_NAME'</v>
       </c>
-      <c r="G235" t="str">
+      <c r="J235" t="str">
         <f t="shared" si="14"/>
         <v>'Provider''s Name'</v>
       </c>
-      <c r="H235" t="str">
+      <c r="K235" t="str">
         <f t="shared" si="15"/>
         <v>('HP16','PROVIDER_NAME','Provider''s Name'),</v>
       </c>
     </row>
-    <row r="236" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="3" t="s">
         <v>498</v>
       </c>
@@ -9278,24 +11412,33 @@
       <c r="D236" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="E236" t="str">
+      <c r="E236" s="7">
+        <v>8</v>
+      </c>
+      <c r="F236" s="7">
+        <v>5163</v>
+      </c>
+      <c r="G236" s="7">
+        <v>5170</v>
+      </c>
+      <c r="H236" t="str">
         <f t="shared" si="12"/>
         <v>'HP16'</v>
       </c>
-      <c r="F236" t="str">
+      <c r="I236" t="str">
         <f t="shared" si="13"/>
         <v>'CERTIFY_DATE'</v>
       </c>
-      <c r="G236" t="str">
+      <c r="J236" t="str">
         <f t="shared" si="14"/>
         <v>'Date Certified'</v>
       </c>
-      <c r="H236" t="str">
+      <c r="K236" t="str">
         <f t="shared" si="15"/>
         <v>('HP16','CERTIFY_DATE','Date Certified'),</v>
       </c>
     </row>
-    <row r="237" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="3" t="s">
         <v>498</v>
       </c>
@@ -9308,24 +11451,33 @@
       <c r="D237" s="3" t="s">
         <v>574</v>
       </c>
-      <c r="E237" t="str">
+      <c r="E237" s="7">
+        <v>1</v>
+      </c>
+      <c r="F237" s="7">
+        <v>5171</v>
+      </c>
+      <c r="G237" s="7">
+        <v>5171</v>
+      </c>
+      <c r="H237" t="str">
         <f t="shared" si="12"/>
         <v>'HP16'</v>
       </c>
-      <c r="F237" t="str">
+      <c r="I237" t="str">
         <f t="shared" si="13"/>
         <v>'PROVIDER_TITLE'</v>
       </c>
-      <c r="G237" t="str">
+      <c r="J237" t="str">
         <f t="shared" si="14"/>
         <v>'Provider''s title'</v>
       </c>
-      <c r="H237" t="str">
+      <c r="K237" t="str">
         <f t="shared" si="15"/>
         <v>('HP16','PROVIDER_TITLE','Provider''s title'),</v>
       </c>
     </row>
-    <row r="238" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="3" t="s">
         <v>498</v>
       </c>
@@ -9338,22 +11490,38 @@
       <c r="D238" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="E238" t="str">
+      <c r="E238" s="7">
+        <v>1</v>
+      </c>
+      <c r="F238" s="7">
+        <v>5172</v>
+      </c>
+      <c r="G238" s="7">
+        <v>5172</v>
+      </c>
+      <c r="H238" t="str">
         <f t="shared" si="12"/>
         <v>'HP16'</v>
       </c>
-      <c r="F238" t="str">
+      <c r="I238" t="str">
         <f t="shared" si="13"/>
         <v>'CERT_PROVIDER'</v>
       </c>
-      <c r="G238" t="str">
+      <c r="J238" t="str">
         <f t="shared" si="14"/>
         <v>'Provider''s Signature'</v>
       </c>
-      <c r="H238" t="str">
+      <c r="K238" t="str">
         <f t="shared" si="15"/>
         <v>('HP16','CERT_PROVIDER','Provider''s Signature'),</v>
       </c>
+    </row>
+    <row r="239" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E239" s="7">
+        <v>5172</v>
+      </c>
+      <c r="F239" s="2"/>
+      <c r="G239" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
